--- a/data/bestellingen 7193 2026_latest.xlsx
+++ b/data/bestellingen 7193 2026_latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\R\Bestellingen\shiny\7180\7180\jorgpeter-orders7180\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{228D43B8-832B-4E49-9F5F-30ABAACBF81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CB39E3-9335-4DDA-BE4E-0B0959BB661E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="108">
   <si>
     <t>EUR</t>
   </si>
@@ -301,6 +301,57 @@
   </si>
   <si>
     <t>Chemicals</t>
+  </si>
+  <si>
+    <t>C117993 22.05.2026 7193 Magazijn</t>
+  </si>
+  <si>
+    <t>PIPETPUNT 10 FILTER DS10X96ST</t>
+  </si>
+  <si>
+    <t>TRIPLEA 1250UL FILTER TIPS DS960ST</t>
+  </si>
+  <si>
+    <t>C101257 19.05.2026 7193 Jorn</t>
+  </si>
+  <si>
+    <t>nebnext ultra ii fs dna librar (96 rxns)</t>
+  </si>
+  <si>
+    <t>nebnext multiplex oligos for i (96 rxns)</t>
+  </si>
+  <si>
+    <t>C101257 18.05.2026 7193 Xanthe/Núria</t>
+  </si>
+  <si>
+    <t>Klinion Ultra Comfort Nitrile hs-Small</t>
+  </si>
+  <si>
+    <t>Klinion Ultra Comfort Nitrile hs-Medium</t>
+  </si>
+  <si>
+    <t>Kosten handmatige orderverwerking</t>
+  </si>
+  <si>
+    <t>C117993 13.05.2026 7193 Algemeen</t>
+  </si>
+  <si>
+    <t>C105961 12.05.2026 MICA KP7193</t>
+  </si>
+  <si>
+    <t>Refractive Index Detector, for Semi-micr</t>
+  </si>
+  <si>
+    <t>C105961</t>
+  </si>
+  <si>
+    <t>96-well microplate sample rack</t>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>HPLC</t>
   </si>
 </sst>
 </file>
@@ -730,7 +781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -789,61 +840,61 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
-        <v>1001360515</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="A2">
+        <v>1001362595</v>
+      </c>
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1">
+        <v>128.9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="3">
+        <v>46164</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0.57401620370370365</v>
+      </c>
+      <c r="K2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1001362595</v>
+      </c>
+      <c r="B3">
         <v>2</v>
       </c>
-      <c r="E2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="1">
-        <v>0</v>
-      </c>
-      <c r="G2" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" s="3">
-        <v>46153</v>
-      </c>
-      <c r="J2" s="4">
-        <v>0.43606481481481479</v>
-      </c>
-      <c r="K2" t="s">
-        <v>90</v>
-      </c>
-      <c r="L2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="2">
-        <v>1001359403</v>
-      </c>
-      <c r="B3" s="2">
-        <v>1</v>
-      </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="1">
-        <v>296.16000000000003</v>
+        <v>115.3</v>
       </c>
       <c r="G3" t="s">
         <v>0</v>
@@ -852,10 +903,10 @@
         <v>7</v>
       </c>
       <c r="I3" s="3">
-        <v>46146</v>
+        <v>46164</v>
       </c>
       <c r="J3" s="4">
-        <v>0.35246527777777775</v>
+        <v>0.5740277777777778</v>
       </c>
       <c r="K3" t="s">
         <v>82</v>
@@ -865,23 +916,23 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
-        <v>1001358440</v>
-      </c>
-      <c r="B4" s="2">
+      <c r="A4">
+        <v>1001361760</v>
+      </c>
+      <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="1">
-        <v>8211</v>
+        <v>2706.88</v>
       </c>
       <c r="G4" t="s">
         <v>0</v>
@@ -890,10 +941,10 @@
         <v>4</v>
       </c>
       <c r="I4" s="3">
-        <v>46136</v>
+        <v>46161</v>
       </c>
       <c r="J4" s="4">
-        <v>0.51320601851851855</v>
+        <v>0.40358796296296301</v>
       </c>
       <c r="K4" t="s">
         <v>90</v>
@@ -903,289 +954,289 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
-        <v>1001358139</v>
-      </c>
-      <c r="B5" s="2">
+      <c r="A5">
+        <v>1001361760</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1">
+        <v>477.84</v>
+      </c>
+      <c r="G5" t="s">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5" s="3">
+        <v>46161</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.40358796296296301</v>
+      </c>
+      <c r="K5" t="s">
+        <v>90</v>
+      </c>
+      <c r="L5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1001361434</v>
+      </c>
+      <c r="B6">
         <v>1</v>
       </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="1">
-        <v>296.16000000000003</v>
-      </c>
-      <c r="G5" t="s">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="C6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1">
+        <v>41.1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>4</v>
+      </c>
+      <c r="I6" s="3">
+        <v>46160</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.34767361111111111</v>
+      </c>
+      <c r="K6" t="s">
+        <v>82</v>
+      </c>
+      <c r="L6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1001361434</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1">
+        <v>82.2</v>
+      </c>
+      <c r="G7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>4</v>
+      </c>
+      <c r="I7" s="3">
+        <v>46160</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.34847222222222224</v>
+      </c>
+      <c r="K7" t="s">
+        <v>82</v>
+      </c>
+      <c r="L7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1001361434</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1">
+        <v>6.95</v>
+      </c>
+      <c r="G8" t="s">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3">
+        <v>46160</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.3489814814814815</v>
+      </c>
+      <c r="K8" t="s">
+        <v>82</v>
+      </c>
+      <c r="L8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1001361254</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>101</v>
+      </c>
+      <c r="D9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="1">
+        <v>172.95</v>
+      </c>
+      <c r="G9" t="s">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="3">
-        <v>46135</v>
-      </c>
-      <c r="J5" s="4">
-        <v>0.40256944444444448</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="I9" s="3">
+        <v>46155</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.68266203703703709</v>
+      </c>
+      <c r="K9" t="s">
         <v>82</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L9" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
-        <v>1001357792</v>
-      </c>
-      <c r="B6" s="2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>1001360993</v>
+      </c>
+      <c r="B10">
         <v>1</v>
       </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" s="1">
-        <v>62.02</v>
-      </c>
-      <c r="G6" t="s">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>4</v>
-      </c>
-      <c r="I6" s="3">
-        <v>46133</v>
-      </c>
-      <c r="J6" s="4">
-        <v>0.59369212962962969</v>
-      </c>
-      <c r="K6" t="s">
-        <v>90</v>
-      </c>
-      <c r="L6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
-        <v>1001357548</v>
-      </c>
-      <c r="B7" s="2">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="1">
-        <v>242</v>
-      </c>
-      <c r="G7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H7" t="s">
-        <v>4</v>
-      </c>
-      <c r="I7" s="3">
-        <v>46132</v>
-      </c>
-      <c r="J7" s="4">
-        <v>0.54353009259259266</v>
-      </c>
-      <c r="K7" t="s">
-        <v>89</v>
-      </c>
-      <c r="L7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
-        <v>1001357548</v>
-      </c>
-      <c r="B8" s="2">
+      <c r="C10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="1">
+        <v>8763.34</v>
+      </c>
+      <c r="G10" t="s">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>104</v>
+      </c>
+      <c r="I10" s="3">
+        <v>46154</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.66589120370370369</v>
+      </c>
+      <c r="K10" t="s">
+        <v>106</v>
+      </c>
+      <c r="L10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>1001360993</v>
+      </c>
+      <c r="B11">
         <v>2</v>
       </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="1">
-        <v>25</v>
-      </c>
-      <c r="G8" t="s">
-        <v>0</v>
-      </c>
-      <c r="H8" t="s">
-        <v>4</v>
-      </c>
-      <c r="I8" s="3">
-        <v>46132</v>
-      </c>
-      <c r="J8" s="4">
-        <v>0.54533564814814817</v>
-      </c>
-      <c r="K8" t="s">
-        <v>89</v>
-      </c>
-      <c r="L8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
-        <v>1001357548</v>
-      </c>
-      <c r="B9" s="2">
-        <v>3</v>
-      </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="1">
-        <v>2250</v>
-      </c>
-      <c r="G9" t="s">
-        <v>0</v>
-      </c>
-      <c r="H9" t="s">
-        <v>4</v>
-      </c>
-      <c r="I9" s="3">
-        <v>46132</v>
-      </c>
-      <c r="J9" s="4">
-        <v>0.546412037037037</v>
-      </c>
-      <c r="K9" t="s">
-        <v>89</v>
-      </c>
-      <c r="L9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
-        <v>1001356465</v>
-      </c>
-      <c r="B10" s="2">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="1">
-        <v>17.55</v>
-      </c>
-      <c r="G10" t="s">
-        <v>0</v>
-      </c>
-      <c r="H10" t="s">
-        <v>7</v>
-      </c>
-      <c r="I10" s="3">
-        <v>46125</v>
-      </c>
-      <c r="J10" s="4">
-        <v>0.65668981481481481</v>
-      </c>
-      <c r="K10" t="s">
-        <v>82</v>
-      </c>
-      <c r="L10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
-        <v>1001356465</v>
-      </c>
-      <c r="B11" s="2">
-        <v>2</v>
-      </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="E11" t="s">
         <v>3</v>
       </c>
       <c r="F11" s="1">
-        <v>17.55</v>
+        <v>586.66</v>
       </c>
       <c r="G11" t="s">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>7</v>
+        <v>104</v>
       </c>
       <c r="I11" s="3">
-        <v>46125</v>
+        <v>46154</v>
       </c>
       <c r="J11" s="4">
-        <v>0.65668981481481481</v>
+        <v>0.6667939814814815</v>
       </c>
       <c r="K11" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="L11" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>1001356192</v>
+        <v>1001360515</v>
       </c>
       <c r="B12" s="2">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E12" t="s">
         <v>3</v>
       </c>
       <c r="F12" s="1">
-        <v>270.5</v>
+        <v>0</v>
       </c>
       <c r="G12" t="s">
         <v>0</v>
@@ -1194,74 +1245,74 @@
         <v>4</v>
       </c>
       <c r="I12" s="3">
-        <v>46122</v>
+        <v>46153</v>
       </c>
       <c r="J12" s="4">
-        <v>0.58597222222222223</v>
+        <v>0.43606481481481479</v>
       </c>
       <c r="K12" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>1001356190</v>
+        <v>1001359403</v>
       </c>
       <c r="B13" s="2">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E13" t="s">
         <v>3</v>
       </c>
       <c r="F13" s="1">
-        <v>1359.84</v>
+        <v>296.16000000000003</v>
       </c>
       <c r="G13" t="s">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I13" s="3">
-        <v>46122</v>
+        <v>46146</v>
       </c>
       <c r="J13" s="4">
-        <v>0.58506944444444442</v>
+        <v>0.35246527777777775</v>
       </c>
       <c r="K13" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L13" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>1001355643</v>
+        <v>1001358440</v>
       </c>
       <c r="B14" s="2">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E14" t="s">
         <v>3</v>
       </c>
       <c r="F14" s="1">
-        <v>425.29</v>
+        <v>8211</v>
       </c>
       <c r="G14" t="s">
         <v>0</v>
@@ -1270,36 +1321,36 @@
         <v>4</v>
       </c>
       <c r="I14" s="3">
-        <v>46120</v>
+        <v>46136</v>
       </c>
       <c r="J14" s="4">
-        <v>0.58754629629629629</v>
+        <v>0.51320601851851855</v>
       </c>
       <c r="K14" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>1001354025</v>
+        <v>1001358139</v>
       </c>
       <c r="B15" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="E15" t="s">
         <v>3</v>
       </c>
       <c r="F15" s="1">
-        <v>247</v>
+        <v>296.16000000000003</v>
       </c>
       <c r="G15" t="s">
         <v>0</v>
@@ -1308,10 +1359,10 @@
         <v>7</v>
       </c>
       <c r="I15" s="3">
-        <v>46108</v>
+        <v>46135</v>
       </c>
       <c r="J15" s="4">
-        <v>0.54822916666666666</v>
+        <v>0.40256944444444448</v>
       </c>
       <c r="K15" t="s">
         <v>82</v>
@@ -1322,98 +1373,98 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>1001354025</v>
+        <v>1001357792</v>
       </c>
       <c r="B16" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E16" t="s">
         <v>3</v>
       </c>
       <c r="F16" s="1">
-        <v>41</v>
+        <v>62.02</v>
       </c>
       <c r="G16" t="s">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I16" s="3">
-        <v>46108</v>
+        <v>46133</v>
       </c>
       <c r="J16" s="4">
-        <v>0.54866898148148147</v>
+        <v>0.59369212962962969</v>
       </c>
       <c r="K16" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L16" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>1001354025</v>
+        <v>1001357548</v>
       </c>
       <c r="B17" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E17" t="s">
         <v>3</v>
       </c>
       <c r="F17" s="1">
-        <v>732</v>
+        <v>242</v>
       </c>
       <c r="G17" t="s">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I17" s="3">
-        <v>46108</v>
+        <v>46132</v>
       </c>
       <c r="J17" s="4">
-        <v>0.5505902777777778</v>
+        <v>0.54353009259259266</v>
       </c>
       <c r="K17" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="L17" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>1001351971</v>
+        <v>1001357548</v>
       </c>
       <c r="B18" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E18" t="s">
         <v>3</v>
       </c>
       <c r="F18" s="1">
-        <v>1.9</v>
+        <v>25</v>
       </c>
       <c r="G18" t="s">
         <v>0</v>
@@ -1422,36 +1473,36 @@
         <v>4</v>
       </c>
       <c r="I18" s="3">
-        <v>46098</v>
+        <v>46132</v>
       </c>
       <c r="J18" s="4">
-        <v>0.34575231481481478</v>
+        <v>0.54533564814814817</v>
       </c>
       <c r="K18" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>1001351971</v>
+        <v>1001357548</v>
       </c>
       <c r="B19" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="E19" t="s">
         <v>3</v>
       </c>
       <c r="F19" s="1">
-        <v>1.8</v>
+        <v>2250</v>
       </c>
       <c r="G19" t="s">
         <v>0</v>
@@ -1460,112 +1511,112 @@
         <v>4</v>
       </c>
       <c r="I19" s="3">
-        <v>46098</v>
+        <v>46132</v>
       </c>
       <c r="J19" s="4">
-        <v>0.34575231481481478</v>
+        <v>0.546412037037037</v>
       </c>
       <c r="K19" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>1001351235</v>
+        <v>1001356465</v>
       </c>
       <c r="B20" s="2">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E20" t="s">
         <v>3</v>
       </c>
       <c r="F20" s="1">
-        <v>153.19999999999999</v>
+        <v>17.55</v>
       </c>
       <c r="G20" t="s">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I20" s="3">
-        <v>46092</v>
+        <v>46125</v>
       </c>
       <c r="J20" s="4">
-        <v>0.66688657407407403</v>
+        <v>0.65668981481481481</v>
       </c>
       <c r="K20" t="s">
         <v>82</v>
       </c>
       <c r="L20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>1001351075</v>
+        <v>1001356465</v>
       </c>
       <c r="B21" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E21" t="s">
         <v>3</v>
       </c>
       <c r="F21" s="1">
-        <v>127</v>
+        <v>17.55</v>
       </c>
       <c r="G21" t="s">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I21" s="3">
-        <v>46092</v>
+        <v>46125</v>
       </c>
       <c r="J21" s="4">
-        <v>0.40361111111111114</v>
+        <v>0.65668981481481481</v>
       </c>
       <c r="K21" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L21" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>1001351075</v>
+        <v>1001356192</v>
       </c>
       <c r="B22" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E22" t="s">
         <v>3</v>
       </c>
       <c r="F22" s="1">
-        <v>15</v>
+        <v>270.5</v>
       </c>
       <c r="G22" t="s">
         <v>0</v>
@@ -1574,36 +1625,36 @@
         <v>4</v>
       </c>
       <c r="I22" s="3">
-        <v>46092</v>
+        <v>46122</v>
       </c>
       <c r="J22" s="4">
-        <v>0.6585185185185185</v>
+        <v>0.58597222222222223</v>
       </c>
       <c r="K22" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L22" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>1001351001</v>
+        <v>1001356190</v>
       </c>
       <c r="B23" s="2">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="E23" t="s">
         <v>3</v>
       </c>
       <c r="F23" s="1">
-        <v>598.67999999999995</v>
+        <v>1359.84</v>
       </c>
       <c r="G23" t="s">
         <v>0</v>
@@ -1612,10 +1663,10 @@
         <v>4</v>
       </c>
       <c r="I23" s="3">
-        <v>46091</v>
+        <v>46122</v>
       </c>
       <c r="J23" s="4">
-        <v>0.63434027777777779</v>
+        <v>0.58506944444444442</v>
       </c>
       <c r="K23" t="s">
         <v>90</v>
@@ -1626,22 +1677,22 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>1001350675</v>
+        <v>1001355643</v>
       </c>
       <c r="B24" s="2">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="D24" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E24" t="s">
         <v>3</v>
       </c>
       <c r="F24" s="1">
-        <v>600</v>
+        <v>425.29</v>
       </c>
       <c r="G24" t="s">
         <v>0</v>
@@ -1650,150 +1701,150 @@
         <v>4</v>
       </c>
       <c r="I24" s="3">
-        <v>46090</v>
+        <v>46120</v>
       </c>
       <c r="J24" s="4">
-        <v>0.54053240740740738</v>
+        <v>0.58754629629629629</v>
       </c>
       <c r="K24" t="s">
         <v>82</v>
       </c>
       <c r="L24" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>1001350592</v>
+        <v>1001354025</v>
       </c>
       <c r="B25" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E25" t="s">
         <v>3</v>
       </c>
       <c r="F25" s="1">
-        <v>449.01</v>
+        <v>247</v>
       </c>
       <c r="G25" t="s">
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I25" s="3">
-        <v>46090</v>
+        <v>46108</v>
       </c>
       <c r="J25" s="4">
-        <v>0.37918981481481479</v>
+        <v>0.54822916666666666</v>
       </c>
       <c r="K25" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L25" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>1001350094</v>
+        <v>1001354025</v>
       </c>
       <c r="B26" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="E26" t="s">
         <v>3</v>
       </c>
       <c r="F26" s="1">
-        <v>679.92</v>
+        <v>41</v>
       </c>
       <c r="G26" t="s">
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I26" s="3">
-        <v>46086</v>
+        <v>46108</v>
       </c>
       <c r="J26" s="4">
-        <v>0.39840277777777783</v>
+        <v>0.54866898148148147</v>
       </c>
       <c r="K26" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L26" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>1001350094</v>
+        <v>1001354025</v>
       </c>
       <c r="B27" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E27" t="s">
         <v>3</v>
       </c>
       <c r="F27" s="1">
-        <v>87.14</v>
+        <v>732</v>
       </c>
       <c r="G27" t="s">
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I27" s="3">
-        <v>46086</v>
+        <v>46108</v>
       </c>
       <c r="J27" s="4">
-        <v>0.39840277777777783</v>
+        <v>0.5505902777777778</v>
       </c>
       <c r="K27" t="s">
         <v>82</v>
       </c>
       <c r="L27" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>1001349263</v>
+        <v>1001351971</v>
       </c>
       <c r="B28" s="2">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D28" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="E28" t="s">
         <v>3</v>
       </c>
       <c r="F28" s="1">
-        <v>14.55</v>
+        <v>1.9</v>
       </c>
       <c r="G28" t="s">
         <v>0</v>
@@ -1802,36 +1853,36 @@
         <v>4</v>
       </c>
       <c r="I28" s="3">
-        <v>46083</v>
+        <v>46098</v>
       </c>
       <c r="J28" s="4">
-        <v>0.39340277777777777</v>
+        <v>0.34575231481481478</v>
       </c>
       <c r="K28" t="s">
         <v>84</v>
       </c>
       <c r="L28" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>1001349263</v>
+        <v>1001351971</v>
       </c>
       <c r="B29" s="2">
         <v>2</v>
       </c>
       <c r="C29" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D29" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="E29" t="s">
         <v>3</v>
       </c>
       <c r="F29" s="1">
-        <v>15.15</v>
+        <v>1.8</v>
       </c>
       <c r="G29" t="s">
         <v>0</v>
@@ -1840,36 +1891,36 @@
         <v>4</v>
       </c>
       <c r="I29" s="3">
-        <v>46083</v>
+        <v>46098</v>
       </c>
       <c r="J29" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.34575231481481478</v>
       </c>
       <c r="K29" t="s">
         <v>84</v>
       </c>
       <c r="L29" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>1001349263</v>
+        <v>1001351235</v>
       </c>
       <c r="B30" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D30" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E30" t="s">
         <v>3</v>
       </c>
       <c r="F30" s="1">
-        <v>15.15</v>
+        <v>153.19999999999999</v>
       </c>
       <c r="G30" t="s">
         <v>0</v>
@@ -1878,36 +1929,36 @@
         <v>4</v>
       </c>
       <c r="I30" s="3">
-        <v>46083</v>
+        <v>46092</v>
       </c>
       <c r="J30" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.66688657407407403</v>
       </c>
       <c r="K30" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L30" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>1001349263</v>
+        <v>1001351075</v>
       </c>
       <c r="B31" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D31" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="E31" t="s">
         <v>3</v>
       </c>
       <c r="F31" s="1">
-        <v>14.55</v>
+        <v>127</v>
       </c>
       <c r="G31" t="s">
         <v>0</v>
@@ -1916,36 +1967,36 @@
         <v>4</v>
       </c>
       <c r="I31" s="3">
-        <v>46083</v>
+        <v>46092</v>
       </c>
       <c r="J31" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.40361111111111114</v>
       </c>
       <c r="K31" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>1001349263</v>
+        <v>1001351075</v>
       </c>
       <c r="B32" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C32" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D32" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E32" t="s">
         <v>3</v>
       </c>
       <c r="F32" s="1">
-        <v>14.85</v>
+        <v>15</v>
       </c>
       <c r="G32" t="s">
         <v>0</v>
@@ -1954,36 +2005,36 @@
         <v>4</v>
       </c>
       <c r="I32" s="3">
-        <v>46083</v>
+        <v>46092</v>
       </c>
       <c r="J32" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.6585185185185185</v>
       </c>
       <c r="K32" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L32" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>1001349263</v>
+        <v>1001351001</v>
       </c>
       <c r="B33" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D33" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="E33" t="s">
         <v>3</v>
       </c>
       <c r="F33" s="1">
-        <v>15</v>
+        <v>598.67999999999995</v>
       </c>
       <c r="G33" t="s">
         <v>0</v>
@@ -1992,13 +2043,13 @@
         <v>4</v>
       </c>
       <c r="I33" s="3">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="J33" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.63434027777777779</v>
       </c>
       <c r="K33" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L33" t="s">
         <v>79</v>
@@ -2006,22 +2057,22 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>1001349263</v>
+        <v>1001350675</v>
       </c>
       <c r="B34" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D34" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E34" t="s">
         <v>3</v>
       </c>
       <c r="F34" s="1">
-        <v>15</v>
+        <v>600</v>
       </c>
       <c r="G34" t="s">
         <v>0</v>
@@ -2030,36 +2081,36 @@
         <v>4</v>
       </c>
       <c r="I34" s="3">
-        <v>46083</v>
+        <v>46090</v>
       </c>
       <c r="J34" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.54053240740740738</v>
       </c>
       <c r="K34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L34" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>1001349263</v>
+        <v>1001350592</v>
       </c>
       <c r="B35" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D35" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E35" t="s">
         <v>3</v>
       </c>
       <c r="F35" s="1">
-        <v>14.85</v>
+        <v>449.01</v>
       </c>
       <c r="G35" t="s">
         <v>0</v>
@@ -2068,13 +2119,13 @@
         <v>4</v>
       </c>
       <c r="I35" s="3">
-        <v>46083</v>
+        <v>46090</v>
       </c>
       <c r="J35" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.37918981481481479</v>
       </c>
       <c r="K35" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L35" t="s">
         <v>79</v>
@@ -2082,22 +2133,22 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>1001345614</v>
+        <v>1001350094</v>
       </c>
       <c r="B36" s="2">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D36" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E36" t="s">
         <v>3</v>
       </c>
       <c r="F36" s="1">
-        <v>605</v>
+        <v>679.92</v>
       </c>
       <c r="G36" t="s">
         <v>0</v>
@@ -2106,13 +2157,13 @@
         <v>4</v>
       </c>
       <c r="I36" s="3">
-        <v>46059</v>
+        <v>46086</v>
       </c>
       <c r="J36" s="4">
-        <v>0.6586805555555556</v>
+        <v>0.39840277777777783</v>
       </c>
       <c r="K36" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L36" t="s">
         <v>81</v>
@@ -2120,22 +2171,22 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>1001345614</v>
+        <v>1001350094</v>
       </c>
       <c r="B37" s="2">
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D37" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E37" t="s">
         <v>3</v>
       </c>
       <c r="F37" s="1">
-        <v>154</v>
+        <v>87.14</v>
       </c>
       <c r="G37" t="s">
         <v>0</v>
@@ -2144,10 +2195,10 @@
         <v>4</v>
       </c>
       <c r="I37" s="3">
-        <v>46059</v>
+        <v>46086</v>
       </c>
       <c r="J37" s="4">
-        <v>0.66027777777777774</v>
+        <v>0.39840277777777783</v>
       </c>
       <c r="K37" t="s">
         <v>82</v>
@@ -2158,22 +2209,22 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>1001343034</v>
+        <v>1001349263</v>
       </c>
       <c r="B38" s="2">
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D38" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E38" t="s">
         <v>3</v>
       </c>
       <c r="F38" s="1">
-        <v>208.6</v>
+        <v>14.55</v>
       </c>
       <c r="G38" t="s">
         <v>0</v>
@@ -2182,36 +2233,36 @@
         <v>4</v>
       </c>
       <c r="I38" s="3">
-        <v>46044</v>
+        <v>46083</v>
       </c>
       <c r="J38" s="4">
-        <v>0.65900462962962958</v>
+        <v>0.39340277777777777</v>
       </c>
       <c r="K38" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L38" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>1001343034</v>
+        <v>1001349263</v>
       </c>
       <c r="B39" s="2">
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D39" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="E39" t="s">
         <v>3</v>
       </c>
       <c r="F39" s="1">
-        <v>20</v>
+        <v>15.15</v>
       </c>
       <c r="G39" t="s">
         <v>0</v>
@@ -2220,36 +2271,36 @@
         <v>4</v>
       </c>
       <c r="I39" s="3">
-        <v>46044</v>
+        <v>46083</v>
       </c>
       <c r="J39" s="4">
-        <v>0.66190972222222222</v>
+        <v>0.39341435185185186</v>
       </c>
       <c r="K39" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L39" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>1001342447</v>
+        <v>1001349263</v>
       </c>
       <c r="B40" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C40" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D40" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="E40" t="s">
         <v>3</v>
       </c>
       <c r="F40" s="1">
-        <v>240</v>
+        <v>15.15</v>
       </c>
       <c r="G40" t="s">
         <v>0</v>
@@ -2258,36 +2309,36 @@
         <v>4</v>
       </c>
       <c r="I40" s="3">
-        <v>46042</v>
+        <v>46083</v>
       </c>
       <c r="J40" s="4">
-        <v>0.54805555555555552</v>
+        <v>0.39341435185185186</v>
       </c>
       <c r="K40" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>1001342447</v>
+        <v>1001349263</v>
       </c>
       <c r="B41" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C41" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D41" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="E41" t="s">
         <v>3</v>
       </c>
       <c r="F41" s="1">
-        <v>8.9499999999999993</v>
+        <v>14.55</v>
       </c>
       <c r="G41" t="s">
         <v>0</v>
@@ -2296,36 +2347,36 @@
         <v>4</v>
       </c>
       <c r="I41" s="3">
-        <v>46042</v>
+        <v>46083</v>
       </c>
       <c r="J41" s="4">
-        <v>0.54859953703703701</v>
+        <v>0.39341435185185186</v>
       </c>
       <c r="K41" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L41" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>1001340933</v>
+        <v>1001349263</v>
       </c>
       <c r="B42" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C42" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D42" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E42" t="s">
         <v>3</v>
       </c>
       <c r="F42" s="1">
-        <v>150.47999999999999</v>
+        <v>14.85</v>
       </c>
       <c r="G42" t="s">
         <v>0</v>
@@ -2334,20 +2385,404 @@
         <v>4</v>
       </c>
       <c r="I42" s="3">
-        <v>46034</v>
+        <v>46083</v>
       </c>
       <c r="J42" s="4">
-        <v>0.40950231481481486</v>
+        <v>0.39341435185185186</v>
       </c>
       <c r="K42" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L42" t="s">
         <v>79</v>
       </c>
     </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A43" s="2">
+        <v>1001349263</v>
+      </c>
+      <c r="B43" s="2">
+        <v>6</v>
+      </c>
+      <c r="C43" t="s">
+        <v>45</v>
+      </c>
+      <c r="D43" t="s">
+        <v>51</v>
+      </c>
+      <c r="E43" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="1">
+        <v>15</v>
+      </c>
+      <c r="G43" t="s">
+        <v>0</v>
+      </c>
+      <c r="H43" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3">
+        <v>46083</v>
+      </c>
+      <c r="J43" s="4">
+        <v>0.39341435185185186</v>
+      </c>
+      <c r="K43" t="s">
+        <v>84</v>
+      </c>
+      <c r="L43" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A44" s="2">
+        <v>1001349263</v>
+      </c>
+      <c r="B44" s="2">
+        <v>7</v>
+      </c>
+      <c r="C44" t="s">
+        <v>45</v>
+      </c>
+      <c r="D44" t="s">
+        <v>52</v>
+      </c>
+      <c r="E44" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="1">
+        <v>15</v>
+      </c>
+      <c r="G44" t="s">
+        <v>0</v>
+      </c>
+      <c r="H44" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3">
+        <v>46083</v>
+      </c>
+      <c r="J44" s="4">
+        <v>0.39341435185185186</v>
+      </c>
+      <c r="K44" t="s">
+        <v>84</v>
+      </c>
+      <c r="L44" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A45" s="2">
+        <v>1001349263</v>
+      </c>
+      <c r="B45" s="2">
+        <v>8</v>
+      </c>
+      <c r="C45" t="s">
+        <v>45</v>
+      </c>
+      <c r="D45" t="s">
+        <v>53</v>
+      </c>
+      <c r="E45" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="1">
+        <v>14.85</v>
+      </c>
+      <c r="G45" t="s">
+        <v>0</v>
+      </c>
+      <c r="H45" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3">
+        <v>46083</v>
+      </c>
+      <c r="J45" s="4">
+        <v>0.39341435185185186</v>
+      </c>
+      <c r="K45" t="s">
+        <v>84</v>
+      </c>
+      <c r="L45" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A46" s="2">
+        <v>1001345614</v>
+      </c>
+      <c r="B46" s="2">
+        <v>1</v>
+      </c>
+      <c r="C46" t="s">
+        <v>54</v>
+      </c>
+      <c r="D46" t="s">
+        <v>55</v>
+      </c>
+      <c r="E46" t="s">
+        <v>3</v>
+      </c>
+      <c r="F46" s="1">
+        <v>605</v>
+      </c>
+      <c r="G46" t="s">
+        <v>0</v>
+      </c>
+      <c r="H46" t="s">
+        <v>4</v>
+      </c>
+      <c r="I46" s="3">
+        <v>46059</v>
+      </c>
+      <c r="J46" s="4">
+        <v>0.6586805555555556</v>
+      </c>
+      <c r="K46" t="s">
+        <v>82</v>
+      </c>
+      <c r="L46" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A47" s="2">
+        <v>1001345614</v>
+      </c>
+      <c r="B47" s="2">
+        <v>2</v>
+      </c>
+      <c r="C47" t="s">
+        <v>54</v>
+      </c>
+      <c r="D47" t="s">
+        <v>56</v>
+      </c>
+      <c r="E47" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="1">
+        <v>154</v>
+      </c>
+      <c r="G47" t="s">
+        <v>0</v>
+      </c>
+      <c r="H47" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3">
+        <v>46059</v>
+      </c>
+      <c r="J47" s="4">
+        <v>0.66027777777777774</v>
+      </c>
+      <c r="K47" t="s">
+        <v>82</v>
+      </c>
+      <c r="L47" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A48" s="2">
+        <v>1001343034</v>
+      </c>
+      <c r="B48" s="2">
+        <v>1</v>
+      </c>
+      <c r="C48" t="s">
+        <v>57</v>
+      </c>
+      <c r="D48" t="s">
+        <v>58</v>
+      </c>
+      <c r="E48" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="1">
+        <v>208.6</v>
+      </c>
+      <c r="G48" t="s">
+        <v>0</v>
+      </c>
+      <c r="H48" t="s">
+        <v>4</v>
+      </c>
+      <c r="I48" s="3">
+        <v>46044</v>
+      </c>
+      <c r="J48" s="4">
+        <v>0.65900462962962958</v>
+      </c>
+      <c r="K48" t="s">
+        <v>88</v>
+      </c>
+      <c r="L48" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A49" s="2">
+        <v>1001343034</v>
+      </c>
+      <c r="B49" s="2">
+        <v>2</v>
+      </c>
+      <c r="C49" t="s">
+        <v>57</v>
+      </c>
+      <c r="D49" t="s">
+        <v>59</v>
+      </c>
+      <c r="E49" t="s">
+        <v>3</v>
+      </c>
+      <c r="F49" s="1">
+        <v>20</v>
+      </c>
+      <c r="G49" t="s">
+        <v>0</v>
+      </c>
+      <c r="H49" t="s">
+        <v>4</v>
+      </c>
+      <c r="I49" s="3">
+        <v>46044</v>
+      </c>
+      <c r="J49" s="4">
+        <v>0.66190972222222222</v>
+      </c>
+      <c r="K49" t="s">
+        <v>88</v>
+      </c>
+      <c r="L49" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A50" s="2">
+        <v>1001342447</v>
+      </c>
+      <c r="B50" s="2">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>60</v>
+      </c>
+      <c r="D50" t="s">
+        <v>61</v>
+      </c>
+      <c r="E50" t="s">
+        <v>3</v>
+      </c>
+      <c r="F50" s="1">
+        <v>240</v>
+      </c>
+      <c r="G50" t="s">
+        <v>0</v>
+      </c>
+      <c r="H50" t="s">
+        <v>4</v>
+      </c>
+      <c r="I50" s="3">
+        <v>46042</v>
+      </c>
+      <c r="J50" s="4">
+        <v>0.54805555555555552</v>
+      </c>
+      <c r="K50" t="s">
+        <v>88</v>
+      </c>
+      <c r="L50" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A51" s="2">
+        <v>1001342447</v>
+      </c>
+      <c r="B51" s="2">
+        <v>2</v>
+      </c>
+      <c r="C51" t="s">
+        <v>60</v>
+      </c>
+      <c r="D51" t="s">
+        <v>62</v>
+      </c>
+      <c r="E51" t="s">
+        <v>3</v>
+      </c>
+      <c r="F51" s="1">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="G51" t="s">
+        <v>0</v>
+      </c>
+      <c r="H51" t="s">
+        <v>4</v>
+      </c>
+      <c r="I51" s="3">
+        <v>46042</v>
+      </c>
+      <c r="J51" s="4">
+        <v>0.54859953703703701</v>
+      </c>
+      <c r="K51" t="s">
+        <v>88</v>
+      </c>
+      <c r="L51" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A52" s="2">
+        <v>1001340933</v>
+      </c>
+      <c r="B52" s="2">
+        <v>1</v>
+      </c>
+      <c r="C52" t="s">
+        <v>63</v>
+      </c>
+      <c r="D52" t="s">
+        <v>64</v>
+      </c>
+      <c r="E52" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="1">
+        <v>150.47999999999999</v>
+      </c>
+      <c r="G52" t="s">
+        <v>0</v>
+      </c>
+      <c r="H52" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3">
+        <v>46034</v>
+      </c>
+      <c r="J52" s="4">
+        <v>0.40950231481481486</v>
+      </c>
+      <c r="K52" t="s">
+        <v>90</v>
+      </c>
+      <c r="L52" t="s">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M42" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:M42" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M52">
+      <sortCondition descending="1" ref="A1:A42"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter alignWithMargins="0"/>

--- a/data/bestellingen 7193 2026_latest.xlsx
+++ b/data/bestellingen 7193 2026_latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\R\Bestellingen\shiny\7180\7180\jorgpeter-orders7180\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CB39E3-9335-4DDA-BE4E-0B0959BB661E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D41EEAE-11A4-49F8-90CA-C1AE1799FB34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="123">
   <si>
     <t>EUR</t>
   </si>
@@ -352,6 +352,51 @@
   </si>
   <si>
     <t>HPLC</t>
+  </si>
+  <si>
+    <t>C101257 11.06.2026 7193 Xanthe</t>
+  </si>
+  <si>
+    <t>Accustart II Geltrack PCR Supermix500AS</t>
+  </si>
+  <si>
+    <t>C117993 09.06.2026 7193 magazijn</t>
+  </si>
+  <si>
+    <t>C101257 08.06.2026 7193 Mark</t>
+  </si>
+  <si>
+    <t>( )-sodium 3-hydroxybutyrate, (EA)</t>
+  </si>
+  <si>
+    <t>poly(3-hydroxybutyric acid), n (EA)</t>
+  </si>
+  <si>
+    <t>transportation and handling ch (EA)</t>
+  </si>
+  <si>
+    <t>C101257 05.06.2026 7193 Jorn</t>
+  </si>
+  <si>
+    <t>amplistar-ii 8-strip 0.2ml pcr (BX)</t>
+  </si>
+  <si>
+    <t>Quantitation and cluster generation</t>
+  </si>
+  <si>
+    <t>Illumina MiSeq 2x250 bp sequencing</t>
+  </si>
+  <si>
+    <t>Data delivery, sFTP</t>
+  </si>
+  <si>
+    <t>C101257 04.06.2026 7193 Nam</t>
+  </si>
+  <si>
+    <t>titansphere (tio2) 100a 5um, b (PK)</t>
+  </si>
+  <si>
+    <t>Mark</t>
   </si>
 </sst>
 </file>
@@ -361,7 +406,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -372,6 +417,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -415,7 +465,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -444,6 +494,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -781,7 +834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -841,51 +894,51 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>1001362595</v>
+        <v>1001365392</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="1">
-        <v>128.9</v>
+        <v>1048</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I2" s="3">
-        <v>46164</v>
+        <v>46184</v>
       </c>
       <c r="J2" s="4">
-        <v>0.57401620370370365</v>
-      </c>
-      <c r="K2" t="s">
-        <v>82</v>
-      </c>
-      <c r="L2" t="s">
-        <v>83</v>
+        <v>0.33641203703703698</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>1001362595</v>
+        <v>1001365168</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="D3" t="s">
         <v>93</v>
@@ -894,7 +947,7 @@
         <v>3</v>
       </c>
       <c r="F3" s="1">
-        <v>115.3</v>
+        <v>288.25</v>
       </c>
       <c r="G3" t="s">
         <v>0</v>
@@ -903,36 +956,36 @@
         <v>7</v>
       </c>
       <c r="I3" s="3">
-        <v>46164</v>
+        <v>46182</v>
       </c>
       <c r="J3" s="4">
-        <v>0.5740277777777778</v>
-      </c>
-      <c r="K3" t="s">
+        <v>0.65709490740740739</v>
+      </c>
+      <c r="K3" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>1001361760</v>
+        <v>1001364804</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="E4" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="1">
-        <v>2706.88</v>
+        <v>208.6</v>
       </c>
       <c r="G4" t="s">
         <v>0</v>
@@ -941,36 +994,36 @@
         <v>4</v>
       </c>
       <c r="I4" s="3">
-        <v>46161</v>
+        <v>46181</v>
       </c>
       <c r="J4" s="4">
-        <v>0.40358796296296301</v>
-      </c>
-      <c r="K4" t="s">
+        <v>0.45427083333333335</v>
+      </c>
+      <c r="K4" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="L4" t="s">
-        <v>79</v>
+      <c r="L4" s="10" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>1001361760</v>
+        <v>1001364804</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="E5" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="1">
-        <v>477.84</v>
+        <v>155.69999999999999</v>
       </c>
       <c r="G5" t="s">
         <v>0</v>
@@ -979,36 +1032,36 @@
         <v>4</v>
       </c>
       <c r="I5" s="3">
-        <v>46161</v>
+        <v>46181</v>
       </c>
       <c r="J5" s="4">
-        <v>0.40358796296296301</v>
-      </c>
-      <c r="K5" t="s">
+        <v>0.45427083333333335</v>
+      </c>
+      <c r="K5" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="L5" t="s">
-        <v>79</v>
+      <c r="L5" s="10" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>1001361434</v>
+        <v>1001364804</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="E6" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="1">
-        <v>41.1</v>
+        <v>5</v>
       </c>
       <c r="G6" t="s">
         <v>0</v>
@@ -1017,36 +1070,36 @@
         <v>4</v>
       </c>
       <c r="I6" s="3">
-        <v>46160</v>
+        <v>46181</v>
       </c>
       <c r="J6" s="4">
-        <v>0.34767361111111111</v>
-      </c>
-      <c r="K6" t="s">
-        <v>82</v>
-      </c>
-      <c r="L6" t="s">
-        <v>86</v>
+        <v>0.45427083333333335</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="L6" s="10" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>1001361434</v>
+        <v>1001364684</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="E7" t="s">
         <v>3</v>
       </c>
       <c r="F7" s="1">
-        <v>82.2</v>
+        <v>708.95</v>
       </c>
       <c r="G7" t="s">
         <v>0</v>
@@ -1055,36 +1108,36 @@
         <v>4</v>
       </c>
       <c r="I7" s="3">
-        <v>46160</v>
+        <v>46178</v>
       </c>
       <c r="J7" s="4">
-        <v>0.34847222222222224</v>
-      </c>
-      <c r="K7" t="s">
+        <v>0.55635416666666659</v>
+      </c>
+      <c r="K7" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="L7" t="s">
-        <v>86</v>
+      <c r="L7" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>1001361434</v>
+        <v>1001364656</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
         <v>3</v>
       </c>
       <c r="F8" s="1">
-        <v>6.95</v>
+        <v>242</v>
       </c>
       <c r="G8" t="s">
         <v>0</v>
@@ -1093,150 +1146,150 @@
         <v>4</v>
       </c>
       <c r="I8" s="3">
-        <v>46160</v>
+        <v>46178</v>
       </c>
       <c r="J8" s="4">
-        <v>0.3489814814814815</v>
-      </c>
-      <c r="K8" t="s">
-        <v>82</v>
-      </c>
-      <c r="L8" t="s">
-        <v>85</v>
+        <v>0.48500000000000004</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>1001361254</v>
+        <v>1001364656</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="E9" t="s">
         <v>3</v>
       </c>
       <c r="F9" s="1">
-        <v>172.95</v>
+        <v>25</v>
       </c>
       <c r="G9" t="s">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I9" s="3">
-        <v>46155</v>
+        <v>46178</v>
       </c>
       <c r="J9" s="4">
-        <v>0.68266203703703709</v>
-      </c>
-      <c r="K9" t="s">
-        <v>82</v>
-      </c>
-      <c r="L9" t="s">
-        <v>83</v>
+        <v>0.48591435185185183</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>1001360993</v>
+        <v>1001364656</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="E10" t="s">
         <v>3</v>
       </c>
       <c r="F10" s="1">
-        <v>8763.34</v>
+        <v>2250</v>
       </c>
       <c r="G10" t="s">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="I10" s="3">
-        <v>46154</v>
+        <v>46178</v>
       </c>
       <c r="J10" s="4">
-        <v>0.66589120370370369</v>
-      </c>
-      <c r="K10" t="s">
-        <v>106</v>
-      </c>
-      <c r="L10" t="s">
-        <v>107</v>
+        <v>0.48841435185185184</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>1001360993</v>
+        <v>1001364656</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="D11" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="E11" t="s">
         <v>3</v>
       </c>
       <c r="F11" s="1">
-        <v>586.66</v>
+        <v>0</v>
       </c>
       <c r="G11" t="s">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="I11" s="3">
-        <v>46154</v>
+        <v>46178</v>
       </c>
       <c r="J11" s="4">
-        <v>0.6667939814814815</v>
-      </c>
-      <c r="K11" t="s">
-        <v>106</v>
-      </c>
-      <c r="L11" t="s">
-        <v>107</v>
+        <v>0.48898148148148146</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
-        <v>1001360515</v>
-      </c>
-      <c r="B12" s="2">
+      <c r="A12">
+        <v>1001364511</v>
+      </c>
+      <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="D12" t="s">
-        <v>2</v>
+        <v>121</v>
       </c>
       <c r="E12" t="s">
         <v>3</v>
       </c>
       <c r="F12" s="1">
-        <v>0</v>
+        <v>738</v>
       </c>
       <c r="G12" t="s">
         <v>0</v>
@@ -1245,36 +1298,36 @@
         <v>4</v>
       </c>
       <c r="I12" s="3">
-        <v>46153</v>
+        <v>46177</v>
       </c>
       <c r="J12" s="4">
-        <v>0.43606481481481479</v>
+        <v>0.63017361111111114</v>
       </c>
       <c r="K12" t="s">
-        <v>90</v>
-      </c>
-      <c r="L12" t="s">
+        <v>82</v>
+      </c>
+      <c r="L12" s="10" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="2">
-        <v>1001359403</v>
-      </c>
-      <c r="B13" s="2">
+      <c r="A13">
+        <v>1001362595</v>
+      </c>
+      <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>6</v>
+        <v>92</v>
       </c>
       <c r="E13" t="s">
         <v>3</v>
       </c>
       <c r="F13" s="1">
-        <v>296.16000000000003</v>
+        <v>128.9</v>
       </c>
       <c r="G13" t="s">
         <v>0</v>
@@ -1283,10 +1336,10 @@
         <v>7</v>
       </c>
       <c r="I13" s="3">
-        <v>46146</v>
+        <v>46164</v>
       </c>
       <c r="J13" s="4">
-        <v>0.35246527777777775</v>
+        <v>0.57401620370370365</v>
       </c>
       <c r="K13" t="s">
         <v>82</v>
@@ -1296,99 +1349,99 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="2">
-        <v>1001358440</v>
-      </c>
-      <c r="B14" s="2">
-        <v>1</v>
+      <c r="A14">
+        <v>1001362595</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="E14" t="s">
         <v>3</v>
       </c>
       <c r="F14" s="1">
-        <v>8211</v>
+        <v>115.3</v>
       </c>
       <c r="G14" t="s">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I14" s="3">
-        <v>46136</v>
+        <v>46164</v>
       </c>
       <c r="J14" s="4">
-        <v>0.51320601851851855</v>
+        <v>0.5740277777777778</v>
       </c>
       <c r="K14" t="s">
+        <v>82</v>
+      </c>
+      <c r="L14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>1001361760</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" t="s">
+        <v>95</v>
+      </c>
+      <c r="E15" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="1">
+        <v>2706.88</v>
+      </c>
+      <c r="G15" t="s">
+        <v>0</v>
+      </c>
+      <c r="H15" t="s">
+        <v>4</v>
+      </c>
+      <c r="I15" s="3">
+        <v>46161</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.40358796296296301</v>
+      </c>
+      <c r="K15" t="s">
         <v>90</v>
       </c>
-      <c r="L14" t="s">
+      <c r="L15" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="2">
-        <v>1001358139</v>
-      </c>
-      <c r="B15" s="2">
-        <v>1</v>
-      </c>
-      <c r="C15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="1">
-        <v>296.16000000000003</v>
-      </c>
-      <c r="G15" t="s">
-        <v>0</v>
-      </c>
-      <c r="H15" t="s">
-        <v>7</v>
-      </c>
-      <c r="I15" s="3">
-        <v>46135</v>
-      </c>
-      <c r="J15" s="4">
-        <v>0.40256944444444448</v>
-      </c>
-      <c r="K15" t="s">
-        <v>82</v>
-      </c>
-      <c r="L15" t="s">
-        <v>83</v>
-      </c>
-    </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="2">
-        <v>1001357792</v>
-      </c>
-      <c r="B16" s="2">
-        <v>1</v>
+      <c r="A16">
+        <v>1001361760</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="E16" t="s">
         <v>3</v>
       </c>
       <c r="F16" s="1">
-        <v>62.02</v>
+        <v>477.84</v>
       </c>
       <c r="G16" t="s">
         <v>0</v>
@@ -1397,10 +1450,10 @@
         <v>4</v>
       </c>
       <c r="I16" s="3">
-        <v>46133</v>
+        <v>46161</v>
       </c>
       <c r="J16" s="4">
-        <v>0.59369212962962969</v>
+        <v>0.40358796296296301</v>
       </c>
       <c r="K16" t="s">
         <v>90</v>
@@ -1410,23 +1463,23 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="2">
-        <v>1001357548</v>
-      </c>
-      <c r="B17" s="2">
+      <c r="A17">
+        <v>1001361434</v>
+      </c>
+      <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="E17" t="s">
         <v>3</v>
       </c>
       <c r="F17" s="1">
-        <v>242</v>
+        <v>41.1</v>
       </c>
       <c r="G17" t="s">
         <v>0</v>
@@ -1435,36 +1488,36 @@
         <v>4</v>
       </c>
       <c r="I17" s="3">
-        <v>46132</v>
+        <v>46160</v>
       </c>
       <c r="J17" s="4">
-        <v>0.54353009259259266</v>
+        <v>0.34767361111111111</v>
       </c>
       <c r="K17" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L17" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="2">
-        <v>1001357548</v>
-      </c>
-      <c r="B18" s="2">
+      <c r="A18">
+        <v>1001361434</v>
+      </c>
+      <c r="B18">
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="E18" t="s">
         <v>3</v>
       </c>
       <c r="F18" s="1">
-        <v>25</v>
+        <v>82.2</v>
       </c>
       <c r="G18" t="s">
         <v>0</v>
@@ -1473,36 +1526,36 @@
         <v>4</v>
       </c>
       <c r="I18" s="3">
-        <v>46132</v>
+        <v>46160</v>
       </c>
       <c r="J18" s="4">
-        <v>0.54533564814814817</v>
+        <v>0.34847222222222224</v>
       </c>
       <c r="K18" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L18" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="2">
-        <v>1001357548</v>
-      </c>
-      <c r="B19" s="2">
+      <c r="A19">
+        <v>1001361434</v>
+      </c>
+      <c r="B19">
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="E19" t="s">
         <v>3</v>
       </c>
       <c r="F19" s="1">
-        <v>2250</v>
+        <v>6.95</v>
       </c>
       <c r="G19" t="s">
         <v>0</v>
@@ -1511,36 +1564,36 @@
         <v>4</v>
       </c>
       <c r="I19" s="3">
-        <v>46132</v>
+        <v>46160</v>
       </c>
       <c r="J19" s="4">
-        <v>0.546412037037037</v>
+        <v>0.3489814814814815</v>
       </c>
       <c r="K19" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L19" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="2">
-        <v>1001356465</v>
-      </c>
-      <c r="B20" s="2">
+      <c r="A20">
+        <v>1001361254</v>
+      </c>
+      <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>101</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="E20" t="s">
         <v>3</v>
       </c>
       <c r="F20" s="1">
-        <v>17.55</v>
+        <v>172.95</v>
       </c>
       <c r="G20" t="s">
         <v>0</v>
@@ -1549,112 +1602,112 @@
         <v>7</v>
       </c>
       <c r="I20" s="3">
-        <v>46125</v>
+        <v>46155</v>
       </c>
       <c r="J20" s="4">
-        <v>0.65668981481481481</v>
+        <v>0.68266203703703709</v>
       </c>
       <c r="K20" t="s">
         <v>82</v>
       </c>
       <c r="L20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="2">
-        <v>1001356465</v>
-      </c>
-      <c r="B21" s="2">
+      <c r="A21">
+        <v>1001360993</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" t="s">
+        <v>103</v>
+      </c>
+      <c r="E21" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="1">
+        <v>8763.34</v>
+      </c>
+      <c r="G21" t="s">
+        <v>0</v>
+      </c>
+      <c r="H21" t="s">
+        <v>104</v>
+      </c>
+      <c r="I21" s="3">
+        <v>46154</v>
+      </c>
+      <c r="J21" s="4">
+        <v>0.66589120370370369</v>
+      </c>
+      <c r="K21" t="s">
+        <v>106</v>
+      </c>
+      <c r="L21" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>1001360993</v>
+      </c>
+      <c r="B22">
         <v>2</v>
       </c>
-      <c r="C21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="1">
-        <v>17.55</v>
-      </c>
-      <c r="G21" t="s">
-        <v>0</v>
-      </c>
-      <c r="H21" t="s">
-        <v>7</v>
-      </c>
-      <c r="I21" s="3">
-        <v>46125</v>
-      </c>
-      <c r="J21" s="4">
-        <v>0.65668981481481481</v>
-      </c>
-      <c r="K21" t="s">
-        <v>82</v>
-      </c>
-      <c r="L21" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="2">
-        <v>1001356192</v>
-      </c>
-      <c r="B22" s="2">
-        <v>1</v>
-      </c>
       <c r="C22" t="s">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="E22" t="s">
         <v>3</v>
       </c>
       <c r="F22" s="1">
-        <v>270.5</v>
+        <v>586.66</v>
       </c>
       <c r="G22" t="s">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="I22" s="3">
-        <v>46122</v>
+        <v>46154</v>
       </c>
       <c r="J22" s="4">
-        <v>0.58597222222222223</v>
+        <v>0.6667939814814815</v>
       </c>
       <c r="K22" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="L22" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>1001356190</v>
+        <v>1001360515</v>
       </c>
       <c r="B23" s="2">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="E23" t="s">
         <v>3</v>
       </c>
       <c r="F23" s="1">
-        <v>1359.84</v>
+        <v>0</v>
       </c>
       <c r="G23" t="s">
         <v>0</v>
@@ -1663,112 +1716,112 @@
         <v>4</v>
       </c>
       <c r="I23" s="3">
-        <v>46122</v>
+        <v>46153</v>
       </c>
       <c r="J23" s="4">
-        <v>0.58506944444444442</v>
+        <v>0.43606481481481479</v>
       </c>
       <c r="K23" t="s">
         <v>90</v>
       </c>
       <c r="L23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>1001355643</v>
+        <v>1001359403</v>
       </c>
       <c r="B24" s="2">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E24" t="s">
         <v>3</v>
       </c>
       <c r="F24" s="1">
-        <v>425.29</v>
+        <v>296.16000000000003</v>
       </c>
       <c r="G24" t="s">
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I24" s="3">
-        <v>46120</v>
+        <v>46146</v>
       </c>
       <c r="J24" s="4">
-        <v>0.58754629629629629</v>
+        <v>0.35246527777777775</v>
       </c>
       <c r="K24" t="s">
         <v>82</v>
       </c>
       <c r="L24" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>1001354025</v>
+        <v>1001358440</v>
       </c>
       <c r="B25" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D25" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="E25" t="s">
         <v>3</v>
       </c>
       <c r="F25" s="1">
-        <v>247</v>
+        <v>8211</v>
       </c>
       <c r="G25" t="s">
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I25" s="3">
-        <v>46108</v>
+        <v>46136</v>
       </c>
       <c r="J25" s="4">
-        <v>0.54822916666666666</v>
+        <v>0.51320601851851855</v>
       </c>
       <c r="K25" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L25" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>1001354025</v>
+        <v>1001358139</v>
       </c>
       <c r="B26" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D26" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E26" t="s">
         <v>3</v>
       </c>
       <c r="F26" s="1">
-        <v>41</v>
+        <v>296.16000000000003</v>
       </c>
       <c r="G26" t="s">
         <v>0</v>
@@ -1777,74 +1830,74 @@
         <v>7</v>
       </c>
       <c r="I26" s="3">
-        <v>46108</v>
+        <v>46135</v>
       </c>
       <c r="J26" s="4">
-        <v>0.54866898148148147</v>
+        <v>0.40256944444444448</v>
       </c>
       <c r="K26" t="s">
         <v>82</v>
       </c>
       <c r="L26" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>1001354025</v>
+        <v>1001357792</v>
       </c>
       <c r="B27" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D27" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E27" t="s">
         <v>3</v>
       </c>
       <c r="F27" s="1">
-        <v>732</v>
+        <v>62.02</v>
       </c>
       <c r="G27" t="s">
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I27" s="3">
-        <v>46108</v>
+        <v>46133</v>
       </c>
       <c r="J27" s="4">
-        <v>0.5505902777777778</v>
+        <v>0.59369212962962969</v>
       </c>
       <c r="K27" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L27" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>1001351971</v>
+        <v>1001357548</v>
       </c>
       <c r="B28" s="2">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="E28" t="s">
         <v>3</v>
       </c>
       <c r="F28" s="1">
-        <v>1.9</v>
+        <v>242</v>
       </c>
       <c r="G28" t="s">
         <v>0</v>
@@ -1853,36 +1906,36 @@
         <v>4</v>
       </c>
       <c r="I28" s="3">
-        <v>46098</v>
+        <v>46132</v>
       </c>
       <c r="J28" s="4">
-        <v>0.34575231481481478</v>
+        <v>0.54353009259259266</v>
       </c>
       <c r="K28" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>1001351971</v>
+        <v>1001357548</v>
       </c>
       <c r="B29" s="2">
         <v>2</v>
       </c>
       <c r="C29" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E29" t="s">
         <v>3</v>
       </c>
       <c r="F29" s="1">
-        <v>1.8</v>
+        <v>25</v>
       </c>
       <c r="G29" t="s">
         <v>0</v>
@@ -1891,36 +1944,36 @@
         <v>4</v>
       </c>
       <c r="I29" s="3">
-        <v>46098</v>
+        <v>46132</v>
       </c>
       <c r="J29" s="4">
-        <v>0.34575231481481478</v>
+        <v>0.54533564814814817</v>
       </c>
       <c r="K29" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L29" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>1001351235</v>
+        <v>1001357548</v>
       </c>
       <c r="B30" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C30" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="E30" t="s">
         <v>3</v>
       </c>
       <c r="F30" s="1">
-        <v>153.19999999999999</v>
+        <v>2250</v>
       </c>
       <c r="G30" t="s">
         <v>0</v>
@@ -1929,112 +1982,112 @@
         <v>4</v>
       </c>
       <c r="I30" s="3">
-        <v>46092</v>
+        <v>46132</v>
       </c>
       <c r="J30" s="4">
-        <v>0.66688657407407403</v>
+        <v>0.546412037037037</v>
       </c>
       <c r="K30" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="L30" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>1001351075</v>
+        <v>1001356465</v>
       </c>
       <c r="B31" s="2">
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D31" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="E31" t="s">
         <v>3</v>
       </c>
       <c r="F31" s="1">
-        <v>127</v>
+        <v>17.55</v>
       </c>
       <c r="G31" t="s">
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I31" s="3">
-        <v>46092</v>
+        <v>46125</v>
       </c>
       <c r="J31" s="4">
-        <v>0.40361111111111114</v>
+        <v>0.65668981481481481</v>
       </c>
       <c r="K31" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L31" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>1001351075</v>
+        <v>1001356465</v>
       </c>
       <c r="B32" s="2">
         <v>2</v>
       </c>
       <c r="C32" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D32" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E32" t="s">
         <v>3</v>
       </c>
       <c r="F32" s="1">
-        <v>15</v>
+        <v>17.55</v>
       </c>
       <c r="G32" t="s">
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I32" s="3">
-        <v>46092</v>
+        <v>46125</v>
       </c>
       <c r="J32" s="4">
-        <v>0.6585185185185185</v>
+        <v>0.65668981481481481</v>
       </c>
       <c r="K32" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L32" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>1001351001</v>
+        <v>1001356192</v>
       </c>
       <c r="B33" s="2">
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="E33" t="s">
         <v>3</v>
       </c>
       <c r="F33" s="1">
-        <v>598.67999999999995</v>
+        <v>270.5</v>
       </c>
       <c r="G33" t="s">
         <v>0</v>
@@ -2043,13 +2096,13 @@
         <v>4</v>
       </c>
       <c r="I33" s="3">
-        <v>46091</v>
+        <v>46122</v>
       </c>
       <c r="J33" s="4">
-        <v>0.63434027777777779</v>
+        <v>0.58597222222222223</v>
       </c>
       <c r="K33" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L33" t="s">
         <v>79</v>
@@ -2057,22 +2110,22 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>1001350675</v>
+        <v>1001356190</v>
       </c>
       <c r="B34" s="2">
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D34" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E34" t="s">
         <v>3</v>
       </c>
       <c r="F34" s="1">
-        <v>600</v>
+        <v>1359.84</v>
       </c>
       <c r="G34" t="s">
         <v>0</v>
@@ -2081,36 +2134,36 @@
         <v>4</v>
       </c>
       <c r="I34" s="3">
-        <v>46090</v>
+        <v>46122</v>
       </c>
       <c r="J34" s="4">
-        <v>0.54053240740740738</v>
+        <v>0.58506944444444442</v>
       </c>
       <c r="K34" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L34" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>1001350592</v>
+        <v>1001355643</v>
       </c>
       <c r="B35" s="2">
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="D35" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E35" t="s">
         <v>3</v>
       </c>
       <c r="F35" s="1">
-        <v>449.01</v>
+        <v>425.29</v>
       </c>
       <c r="G35" t="s">
         <v>0</v>
@@ -2119,150 +2172,150 @@
         <v>4</v>
       </c>
       <c r="I35" s="3">
-        <v>46090</v>
+        <v>46120</v>
       </c>
       <c r="J35" s="4">
-        <v>0.37918981481481479</v>
+        <v>0.58754629629629629</v>
       </c>
       <c r="K35" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>1001350094</v>
+        <v>1001354025</v>
       </c>
       <c r="B36" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D36" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="E36" t="s">
         <v>3</v>
       </c>
       <c r="F36" s="1">
-        <v>679.92</v>
+        <v>247</v>
       </c>
       <c r="G36" t="s">
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I36" s="3">
-        <v>46086</v>
+        <v>46108</v>
       </c>
       <c r="J36" s="4">
-        <v>0.39840277777777783</v>
+        <v>0.54822916666666666</v>
       </c>
       <c r="K36" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>1001350094</v>
+        <v>1001354025</v>
       </c>
       <c r="B37" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="E37" t="s">
         <v>3</v>
       </c>
       <c r="F37" s="1">
-        <v>87.14</v>
+        <v>41</v>
       </c>
       <c r="G37" t="s">
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I37" s="3">
-        <v>46086</v>
+        <v>46108</v>
       </c>
       <c r="J37" s="4">
-        <v>0.39840277777777783</v>
+        <v>0.54866898148148147</v>
       </c>
       <c r="K37" t="s">
         <v>82</v>
       </c>
       <c r="L37" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>1001349263</v>
+        <v>1001354025</v>
       </c>
       <c r="B38" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C38" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D38" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E38" t="s">
         <v>3</v>
       </c>
       <c r="F38" s="1">
-        <v>14.55</v>
+        <v>732</v>
       </c>
       <c r="G38" t="s">
         <v>0</v>
       </c>
       <c r="H38" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I38" s="3">
-        <v>46083</v>
+        <v>46108</v>
       </c>
       <c r="J38" s="4">
-        <v>0.39340277777777777</v>
+        <v>0.5505902777777778</v>
       </c>
       <c r="K38" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L38" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>1001349263</v>
+        <v>1001351971</v>
       </c>
       <c r="B39" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D39" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E39" t="s">
         <v>3</v>
       </c>
       <c r="F39" s="1">
-        <v>15.15</v>
+        <v>1.9</v>
       </c>
       <c r="G39" t="s">
         <v>0</v>
@@ -2271,36 +2324,36 @@
         <v>4</v>
       </c>
       <c r="I39" s="3">
-        <v>46083</v>
+        <v>46098</v>
       </c>
       <c r="J39" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.34575231481481478</v>
       </c>
       <c r="K39" t="s">
         <v>84</v>
       </c>
       <c r="L39" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>1001349263</v>
+        <v>1001351971</v>
       </c>
       <c r="B40" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D40" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="E40" t="s">
         <v>3</v>
       </c>
       <c r="F40" s="1">
-        <v>15.15</v>
+        <v>1.8</v>
       </c>
       <c r="G40" t="s">
         <v>0</v>
@@ -2309,36 +2362,36 @@
         <v>4</v>
       </c>
       <c r="I40" s="3">
-        <v>46083</v>
+        <v>46098</v>
       </c>
       <c r="J40" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.34575231481481478</v>
       </c>
       <c r="K40" t="s">
         <v>84</v>
       </c>
       <c r="L40" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>1001349263</v>
+        <v>1001351235</v>
       </c>
       <c r="B41" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D41" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E41" t="s">
         <v>3</v>
       </c>
       <c r="F41" s="1">
-        <v>14.55</v>
+        <v>153.19999999999999</v>
       </c>
       <c r="G41" t="s">
         <v>0</v>
@@ -2347,36 +2400,36 @@
         <v>4</v>
       </c>
       <c r="I41" s="3">
-        <v>46083</v>
+        <v>46092</v>
       </c>
       <c r="J41" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.66688657407407403</v>
       </c>
       <c r="K41" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L41" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>1001349263</v>
+        <v>1001351075</v>
       </c>
       <c r="B42" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D42" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E42" t="s">
         <v>3</v>
       </c>
       <c r="F42" s="1">
-        <v>14.85</v>
+        <v>127</v>
       </c>
       <c r="G42" t="s">
         <v>0</v>
@@ -2385,30 +2438,30 @@
         <v>4</v>
       </c>
       <c r="I42" s="3">
-        <v>46083</v>
+        <v>46092</v>
       </c>
       <c r="J42" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.40361111111111114</v>
       </c>
       <c r="K42" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L42" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>1001349263</v>
+        <v>1001351075</v>
       </c>
       <c r="B43" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D43" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="E43" t="s">
         <v>3</v>
@@ -2423,36 +2476,36 @@
         <v>4</v>
       </c>
       <c r="I43" s="3">
-        <v>46083</v>
+        <v>46092</v>
       </c>
       <c r="J43" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.6585185185185185</v>
       </c>
       <c r="K43" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L43" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>1001349263</v>
+        <v>1001351001</v>
       </c>
       <c r="B44" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D44" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="E44" t="s">
         <v>3</v>
       </c>
       <c r="F44" s="1">
-        <v>15</v>
+        <v>598.67999999999995</v>
       </c>
       <c r="G44" t="s">
         <v>0</v>
@@ -2461,13 +2514,13 @@
         <v>4</v>
       </c>
       <c r="I44" s="3">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="J44" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.63434027777777779</v>
       </c>
       <c r="K44" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L44" t="s">
         <v>79</v>
@@ -2475,22 +2528,22 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>1001349263</v>
+        <v>1001350675</v>
       </c>
       <c r="B45" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D45" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="E45" t="s">
         <v>3</v>
       </c>
       <c r="F45" s="1">
-        <v>14.85</v>
+        <v>600</v>
       </c>
       <c r="G45" t="s">
         <v>0</v>
@@ -2499,36 +2552,36 @@
         <v>4</v>
       </c>
       <c r="I45" s="3">
-        <v>46083</v>
+        <v>46090</v>
       </c>
       <c r="J45" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.54053240740740738</v>
       </c>
       <c r="K45" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L45" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>1001345614</v>
+        <v>1001350592</v>
       </c>
       <c r="B46" s="2">
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D46" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="E46" t="s">
         <v>3</v>
       </c>
       <c r="F46" s="1">
-        <v>605</v>
+        <v>449.01</v>
       </c>
       <c r="G46" t="s">
         <v>0</v>
@@ -2537,36 +2590,36 @@
         <v>4</v>
       </c>
       <c r="I46" s="3">
-        <v>46059</v>
+        <v>46090</v>
       </c>
       <c r="J46" s="4">
-        <v>0.6586805555555556</v>
+        <v>0.37918981481481479</v>
       </c>
       <c r="K46" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L46" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>1001345614</v>
+        <v>1001350094</v>
       </c>
       <c r="B47" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D47" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="E47" t="s">
         <v>3</v>
       </c>
       <c r="F47" s="1">
-        <v>154</v>
+        <v>679.92</v>
       </c>
       <c r="G47" t="s">
         <v>0</v>
@@ -2575,13 +2628,13 @@
         <v>4</v>
       </c>
       <c r="I47" s="3">
-        <v>46059</v>
+        <v>46086</v>
       </c>
       <c r="J47" s="4">
-        <v>0.66027777777777774</v>
+        <v>0.39840277777777783</v>
       </c>
       <c r="K47" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L47" t="s">
         <v>81</v>
@@ -2589,22 +2642,22 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>1001343034</v>
+        <v>1001350094</v>
       </c>
       <c r="B48" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D48" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="E48" t="s">
         <v>3</v>
       </c>
       <c r="F48" s="1">
-        <v>208.6</v>
+        <v>87.14</v>
       </c>
       <c r="G48" t="s">
         <v>0</v>
@@ -2613,36 +2666,36 @@
         <v>4</v>
       </c>
       <c r="I48" s="3">
-        <v>46044</v>
+        <v>46086</v>
       </c>
       <c r="J48" s="4">
-        <v>0.65900462962962958</v>
+        <v>0.39840277777777783</v>
       </c>
       <c r="K48" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L48" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>1001343034</v>
+        <v>1001349263</v>
       </c>
       <c r="B49" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D49" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E49" t="s">
         <v>3</v>
       </c>
       <c r="F49" s="1">
-        <v>20</v>
+        <v>14.55</v>
       </c>
       <c r="G49" t="s">
         <v>0</v>
@@ -2651,36 +2704,36 @@
         <v>4</v>
       </c>
       <c r="I49" s="3">
-        <v>46044</v>
+        <v>46083</v>
       </c>
       <c r="J49" s="4">
-        <v>0.66190972222222222</v>
+        <v>0.39340277777777777</v>
       </c>
       <c r="K49" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L49" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>1001342447</v>
+        <v>1001349263</v>
       </c>
       <c r="B50" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D50" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E50" t="s">
         <v>3</v>
       </c>
       <c r="F50" s="1">
-        <v>240</v>
+        <v>15.15</v>
       </c>
       <c r="G50" t="s">
         <v>0</v>
@@ -2689,36 +2742,36 @@
         <v>4</v>
       </c>
       <c r="I50" s="3">
-        <v>46042</v>
+        <v>46083</v>
       </c>
       <c r="J50" s="4">
-        <v>0.54805555555555552</v>
+        <v>0.39341435185185186</v>
       </c>
       <c r="K50" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>1001342447</v>
+        <v>1001349263</v>
       </c>
       <c r="B51" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C51" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D51" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="E51" t="s">
         <v>3</v>
       </c>
       <c r="F51" s="1">
-        <v>8.9499999999999993</v>
+        <v>15.15</v>
       </c>
       <c r="G51" t="s">
         <v>0</v>
@@ -2727,36 +2780,36 @@
         <v>4</v>
       </c>
       <c r="I51" s="3">
-        <v>46042</v>
+        <v>46083</v>
       </c>
       <c r="J51" s="4">
-        <v>0.54859953703703701</v>
+        <v>0.39341435185185186</v>
       </c>
       <c r="K51" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L51" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>1001340933</v>
+        <v>1001349263</v>
       </c>
       <c r="B52" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C52" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D52" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E52" t="s">
         <v>3</v>
       </c>
       <c r="F52" s="1">
-        <v>150.47999999999999</v>
+        <v>14.55</v>
       </c>
       <c r="G52" t="s">
         <v>0</v>
@@ -2765,21 +2818,439 @@
         <v>4</v>
       </c>
       <c r="I52" s="3">
-        <v>46034</v>
+        <v>46083</v>
       </c>
       <c r="J52" s="4">
-        <v>0.40950231481481486</v>
+        <v>0.39341435185185186</v>
       </c>
       <c r="K52" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L52" t="s">
         <v>79</v>
       </c>
     </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A53" s="2">
+        <v>1001349263</v>
+      </c>
+      <c r="B53" s="2">
+        <v>5</v>
+      </c>
+      <c r="C53" t="s">
+        <v>45</v>
+      </c>
+      <c r="D53" t="s">
+        <v>50</v>
+      </c>
+      <c r="E53" t="s">
+        <v>3</v>
+      </c>
+      <c r="F53" s="1">
+        <v>14.85</v>
+      </c>
+      <c r="G53" t="s">
+        <v>0</v>
+      </c>
+      <c r="H53" t="s">
+        <v>4</v>
+      </c>
+      <c r="I53" s="3">
+        <v>46083</v>
+      </c>
+      <c r="J53" s="4">
+        <v>0.39341435185185186</v>
+      </c>
+      <c r="K53" t="s">
+        <v>84</v>
+      </c>
+      <c r="L53" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A54" s="2">
+        <v>1001349263</v>
+      </c>
+      <c r="B54" s="2">
+        <v>6</v>
+      </c>
+      <c r="C54" t="s">
+        <v>45</v>
+      </c>
+      <c r="D54" t="s">
+        <v>51</v>
+      </c>
+      <c r="E54" t="s">
+        <v>3</v>
+      </c>
+      <c r="F54" s="1">
+        <v>15</v>
+      </c>
+      <c r="G54" t="s">
+        <v>0</v>
+      </c>
+      <c r="H54" t="s">
+        <v>4</v>
+      </c>
+      <c r="I54" s="3">
+        <v>46083</v>
+      </c>
+      <c r="J54" s="4">
+        <v>0.39341435185185186</v>
+      </c>
+      <c r="K54" t="s">
+        <v>84</v>
+      </c>
+      <c r="L54" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A55" s="2">
+        <v>1001349263</v>
+      </c>
+      <c r="B55" s="2">
+        <v>7</v>
+      </c>
+      <c r="C55" t="s">
+        <v>45</v>
+      </c>
+      <c r="D55" t="s">
+        <v>52</v>
+      </c>
+      <c r="E55" t="s">
+        <v>3</v>
+      </c>
+      <c r="F55" s="1">
+        <v>15</v>
+      </c>
+      <c r="G55" t="s">
+        <v>0</v>
+      </c>
+      <c r="H55" t="s">
+        <v>4</v>
+      </c>
+      <c r="I55" s="3">
+        <v>46083</v>
+      </c>
+      <c r="J55" s="4">
+        <v>0.39341435185185186</v>
+      </c>
+      <c r="K55" t="s">
+        <v>84</v>
+      </c>
+      <c r="L55" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A56" s="2">
+        <v>1001349263</v>
+      </c>
+      <c r="B56" s="2">
+        <v>8</v>
+      </c>
+      <c r="C56" t="s">
+        <v>45</v>
+      </c>
+      <c r="D56" t="s">
+        <v>53</v>
+      </c>
+      <c r="E56" t="s">
+        <v>3</v>
+      </c>
+      <c r="F56" s="1">
+        <v>14.85</v>
+      </c>
+      <c r="G56" t="s">
+        <v>0</v>
+      </c>
+      <c r="H56" t="s">
+        <v>4</v>
+      </c>
+      <c r="I56" s="3">
+        <v>46083</v>
+      </c>
+      <c r="J56" s="4">
+        <v>0.39341435185185186</v>
+      </c>
+      <c r="K56" t="s">
+        <v>84</v>
+      </c>
+      <c r="L56" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A57" s="2">
+        <v>1001345614</v>
+      </c>
+      <c r="B57" s="2">
+        <v>1</v>
+      </c>
+      <c r="C57" t="s">
+        <v>54</v>
+      </c>
+      <c r="D57" t="s">
+        <v>55</v>
+      </c>
+      <c r="E57" t="s">
+        <v>3</v>
+      </c>
+      <c r="F57" s="1">
+        <v>605</v>
+      </c>
+      <c r="G57" t="s">
+        <v>0</v>
+      </c>
+      <c r="H57" t="s">
+        <v>4</v>
+      </c>
+      <c r="I57" s="3">
+        <v>46059</v>
+      </c>
+      <c r="J57" s="4">
+        <v>0.6586805555555556</v>
+      </c>
+      <c r="K57" t="s">
+        <v>82</v>
+      </c>
+      <c r="L57" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A58" s="2">
+        <v>1001345614</v>
+      </c>
+      <c r="B58" s="2">
+        <v>2</v>
+      </c>
+      <c r="C58" t="s">
+        <v>54</v>
+      </c>
+      <c r="D58" t="s">
+        <v>56</v>
+      </c>
+      <c r="E58" t="s">
+        <v>3</v>
+      </c>
+      <c r="F58" s="1">
+        <v>154</v>
+      </c>
+      <c r="G58" t="s">
+        <v>0</v>
+      </c>
+      <c r="H58" t="s">
+        <v>4</v>
+      </c>
+      <c r="I58" s="3">
+        <v>46059</v>
+      </c>
+      <c r="J58" s="4">
+        <v>0.66027777777777774</v>
+      </c>
+      <c r="K58" t="s">
+        <v>82</v>
+      </c>
+      <c r="L58" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A59" s="2">
+        <v>1001343034</v>
+      </c>
+      <c r="B59" s="2">
+        <v>1</v>
+      </c>
+      <c r="C59" t="s">
+        <v>57</v>
+      </c>
+      <c r="D59" t="s">
+        <v>58</v>
+      </c>
+      <c r="E59" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="1">
+        <v>208.6</v>
+      </c>
+      <c r="G59" t="s">
+        <v>0</v>
+      </c>
+      <c r="H59" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3">
+        <v>46044</v>
+      </c>
+      <c r="J59" s="4">
+        <v>0.65900462962962958</v>
+      </c>
+      <c r="K59" t="s">
+        <v>88</v>
+      </c>
+      <c r="L59" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A60" s="2">
+        <v>1001343034</v>
+      </c>
+      <c r="B60" s="2">
+        <v>2</v>
+      </c>
+      <c r="C60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D60" t="s">
+        <v>59</v>
+      </c>
+      <c r="E60" t="s">
+        <v>3</v>
+      </c>
+      <c r="F60" s="1">
+        <v>20</v>
+      </c>
+      <c r="G60" t="s">
+        <v>0</v>
+      </c>
+      <c r="H60" t="s">
+        <v>4</v>
+      </c>
+      <c r="I60" s="3">
+        <v>46044</v>
+      </c>
+      <c r="J60" s="4">
+        <v>0.66190972222222222</v>
+      </c>
+      <c r="K60" t="s">
+        <v>88</v>
+      </c>
+      <c r="L60" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A61" s="2">
+        <v>1001342447</v>
+      </c>
+      <c r="B61" s="2">
+        <v>1</v>
+      </c>
+      <c r="C61" t="s">
+        <v>60</v>
+      </c>
+      <c r="D61" t="s">
+        <v>61</v>
+      </c>
+      <c r="E61" t="s">
+        <v>3</v>
+      </c>
+      <c r="F61" s="1">
+        <v>240</v>
+      </c>
+      <c r="G61" t="s">
+        <v>0</v>
+      </c>
+      <c r="H61" t="s">
+        <v>4</v>
+      </c>
+      <c r="I61" s="3">
+        <v>46042</v>
+      </c>
+      <c r="J61" s="4">
+        <v>0.54805555555555552</v>
+      </c>
+      <c r="K61" t="s">
+        <v>88</v>
+      </c>
+      <c r="L61" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A62" s="2">
+        <v>1001342447</v>
+      </c>
+      <c r="B62" s="2">
+        <v>2</v>
+      </c>
+      <c r="C62" t="s">
+        <v>60</v>
+      </c>
+      <c r="D62" t="s">
+        <v>62</v>
+      </c>
+      <c r="E62" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="1">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="G62" t="s">
+        <v>0</v>
+      </c>
+      <c r="H62" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3">
+        <v>46042</v>
+      </c>
+      <c r="J62" s="4">
+        <v>0.54859953703703701</v>
+      </c>
+      <c r="K62" t="s">
+        <v>88</v>
+      </c>
+      <c r="L62" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A63" s="2">
+        <v>1001340933</v>
+      </c>
+      <c r="B63" s="2">
+        <v>1</v>
+      </c>
+      <c r="C63" t="s">
+        <v>63</v>
+      </c>
+      <c r="D63" t="s">
+        <v>64</v>
+      </c>
+      <c r="E63" t="s">
+        <v>3</v>
+      </c>
+      <c r="F63" s="1">
+        <v>150.47999999999999</v>
+      </c>
+      <c r="G63" t="s">
+        <v>0</v>
+      </c>
+      <c r="H63" t="s">
+        <v>4</v>
+      </c>
+      <c r="I63" s="3">
+        <v>46034</v>
+      </c>
+      <c r="J63" s="4">
+        <v>0.40950231481481486</v>
+      </c>
+      <c r="K63" t="s">
+        <v>90</v>
+      </c>
+      <c r="L63" t="s">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M42" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M52">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M63">
       <sortCondition descending="1" ref="A1:A42"/>
     </sortState>
   </autoFilter>

--- a/data/bestellingen 7193 2026_latest.xlsx
+++ b/data/bestellingen 7193 2026_latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\R\Bestellingen\shiny\7180\7180\jorgpeter-orders7180\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D41EEAE-11A4-49F8-90CA-C1AE1799FB34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A364DBBA-47B2-42B5-A1F5-270AE3F94EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$66</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="127">
   <si>
     <t>EUR</t>
   </si>
@@ -397,6 +397,18 @@
   </si>
   <si>
     <t>Mark</t>
+  </si>
+  <si>
+    <t>C101257 22.06.2026 7193 Hilde</t>
+  </si>
+  <si>
+    <t>Shotgun Metagenomics (WOBI)</t>
+  </si>
+  <si>
+    <t>Cloud Delivery</t>
+  </si>
+  <si>
+    <t>C117993 17.06.2026 7193 Magazijn</t>
   </si>
 </sst>
 </file>
@@ -834,7 +846,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -894,22 +906,22 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>1001365392</v>
+        <v>1001366912</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="1">
-        <v>1048</v>
+        <v>704</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
@@ -918,112 +930,112 @@
         <v>4</v>
       </c>
       <c r="I2" s="3">
-        <v>46184</v>
+        <v>46195</v>
       </c>
       <c r="J2" s="4">
-        <v>0.33641203703703698</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>81</v>
+        <v>0.63238425925925923</v>
+      </c>
+      <c r="K2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L2" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>1001365168</v>
+        <v>1001366912</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="E3" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="1">
-        <v>288.25</v>
+        <v>28</v>
       </c>
       <c r="G3" t="s">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I3" s="3">
-        <v>46182</v>
+        <v>46195</v>
       </c>
       <c r="J3" s="4">
-        <v>0.65709490740740739</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="L3" s="10" t="s">
-        <v>83</v>
+        <v>0.6334953703703704</v>
+      </c>
+      <c r="K3" t="s">
+        <v>89</v>
+      </c>
+      <c r="L3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>1001364804</v>
+        <v>1001366367</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="D4" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="1">
-        <v>208.6</v>
+        <v>322.25</v>
       </c>
       <c r="G4" t="s">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I4" s="3">
-        <v>46181</v>
+        <v>46190</v>
       </c>
       <c r="J4" s="4">
-        <v>0.45427083333333335</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>122</v>
+        <v>0.64398148148148149</v>
+      </c>
+      <c r="K4" t="s">
+        <v>82</v>
+      </c>
+      <c r="L4" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>1001364804</v>
+        <v>1001365392</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="1">
-        <v>155.69999999999999</v>
+        <v>1048</v>
       </c>
       <c r="G5" t="s">
         <v>0</v>
@@ -1032,74 +1044,74 @@
         <v>4</v>
       </c>
       <c r="I5" s="3">
-        <v>46181</v>
+        <v>46184</v>
       </c>
       <c r="J5" s="4">
-        <v>0.45427083333333335</v>
+        <v>0.33641203703703698</v>
       </c>
       <c r="K5" s="10" t="s">
         <v>90</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>1001364804</v>
+        <v>1001365168</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="E6" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="1">
-        <v>5</v>
+        <v>288.25</v>
       </c>
       <c r="G6" t="s">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I6" s="3">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="J6" s="4">
-        <v>0.45427083333333335</v>
+        <v>0.65709490740740739</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>1001364684</v>
+        <v>1001364804</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E7" t="s">
         <v>3</v>
       </c>
       <c r="F7" s="1">
-        <v>708.95</v>
+        <v>208.6</v>
       </c>
       <c r="G7" t="s">
         <v>0</v>
@@ -1108,36 +1120,36 @@
         <v>4</v>
       </c>
       <c r="I7" s="3">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="J7" s="4">
-        <v>0.55635416666666659</v>
+        <v>0.45427083333333335</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>1001364656</v>
+        <v>1001364804</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>113</v>
       </c>
       <c r="E8" t="s">
         <v>3</v>
       </c>
       <c r="F8" s="1">
-        <v>242</v>
+        <v>155.69999999999999</v>
       </c>
       <c r="G8" t="s">
         <v>0</v>
@@ -1146,36 +1158,36 @@
         <v>4</v>
       </c>
       <c r="I8" s="3">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="J8" s="4">
-        <v>0.48500000000000004</v>
+        <v>0.45427083333333335</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>1001364656</v>
+        <v>1001364804</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E9" t="s">
         <v>3</v>
       </c>
       <c r="F9" s="1">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G9" t="s">
         <v>0</v>
@@ -1184,36 +1196,36 @@
         <v>4</v>
       </c>
       <c r="I9" s="3">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="J9" s="4">
-        <v>0.48591435185185183</v>
+        <v>0.45427083333333335</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>1001364656</v>
+        <v>1001364684</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
         <v>115</v>
       </c>
       <c r="D10" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E10" t="s">
         <v>3</v>
       </c>
       <c r="F10" s="1">
-        <v>2250</v>
+        <v>708.95</v>
       </c>
       <c r="G10" t="s">
         <v>0</v>
@@ -1225,10 +1237,10 @@
         <v>46178</v>
       </c>
       <c r="J10" s="4">
-        <v>0.48841435185185184</v>
+        <v>0.55635416666666659</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L10" s="10" t="s">
         <v>79</v>
@@ -1239,19 +1251,19 @@
         <v>1001364656</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="s">
         <v>115</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>14</v>
       </c>
       <c r="E11" t="s">
         <v>3</v>
       </c>
       <c r="F11" s="1">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="G11" t="s">
         <v>0</v>
@@ -1263,7 +1275,7 @@
         <v>46178</v>
       </c>
       <c r="J11" s="4">
-        <v>0.48898148148148146</v>
+        <v>0.48500000000000004</v>
       </c>
       <c r="K11" s="10" t="s">
         <v>89</v>
@@ -1274,22 +1286,22 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>1001364511</v>
+        <v>1001364656</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E12" t="s">
         <v>3</v>
       </c>
       <c r="F12" s="1">
-        <v>738</v>
+        <v>25</v>
       </c>
       <c r="G12" t="s">
         <v>0</v>
@@ -1298,16 +1310,16 @@
         <v>4</v>
       </c>
       <c r="I12" s="3">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="J12" s="4">
-        <v>0.63017361111111114</v>
-      </c>
-      <c r="K12" t="s">
-        <v>82</v>
+        <v>0.48591435185185183</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>89</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
@@ -3248,10 +3260,124 @@
         <v>79</v>
       </c>
     </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>1001364656</v>
+      </c>
+      <c r="B64">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>115</v>
+      </c>
+      <c r="D64" t="s">
+        <v>118</v>
+      </c>
+      <c r="E64" t="s">
+        <v>3</v>
+      </c>
+      <c r="F64" s="1">
+        <v>2250</v>
+      </c>
+      <c r="G64" t="s">
+        <v>0</v>
+      </c>
+      <c r="H64" t="s">
+        <v>4</v>
+      </c>
+      <c r="I64" s="3">
+        <v>46178</v>
+      </c>
+      <c r="J64" s="4">
+        <v>0.48841435185185184</v>
+      </c>
+      <c r="K64" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L64" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>1001364656</v>
+      </c>
+      <c r="B65">
+        <v>4</v>
+      </c>
+      <c r="C65" t="s">
+        <v>115</v>
+      </c>
+      <c r="D65" t="s">
+        <v>119</v>
+      </c>
+      <c r="E65" t="s">
+        <v>3</v>
+      </c>
+      <c r="F65" s="1">
+        <v>0</v>
+      </c>
+      <c r="G65" t="s">
+        <v>0</v>
+      </c>
+      <c r="H65" t="s">
+        <v>4</v>
+      </c>
+      <c r="I65" s="3">
+        <v>46178</v>
+      </c>
+      <c r="J65" s="4">
+        <v>0.48898148148148146</v>
+      </c>
+      <c r="K65" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L65" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>1001364511</v>
+      </c>
+      <c r="B66">
+        <v>1</v>
+      </c>
+      <c r="C66" t="s">
+        <v>120</v>
+      </c>
+      <c r="D66" t="s">
+        <v>121</v>
+      </c>
+      <c r="E66" t="s">
+        <v>3</v>
+      </c>
+      <c r="F66" s="1">
+        <v>738</v>
+      </c>
+      <c r="G66" t="s">
+        <v>0</v>
+      </c>
+      <c r="H66" t="s">
+        <v>4</v>
+      </c>
+      <c r="I66" s="3">
+        <v>46177</v>
+      </c>
+      <c r="J66" s="4">
+        <v>0.63017361111111114</v>
+      </c>
+      <c r="K66" t="s">
+        <v>82</v>
+      </c>
+      <c r="L66" s="10" t="s">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M42" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M63">
-      <sortCondition descending="1" ref="A1:A42"/>
+  <autoFilter ref="A1:M66" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M66">
+      <sortCondition descending="1" ref="A1:A63"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="0" type="noConversion"/>

--- a/data/bestellingen 7193 2026_latest.xlsx
+++ b/data/bestellingen 7193 2026_latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\R\Bestellingen\shiny\7180\7180\jorgpeter-orders7180\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A364DBBA-47B2-42B5-A1F5-270AE3F94EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B6397E-9BB1-42EA-BADC-1F4683BE6EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="131">
   <si>
     <t>EUR</t>
   </si>
@@ -409,6 +409,18 @@
   </si>
   <si>
     <t>C117993 17.06.2026 7193 Magazijn</t>
+  </si>
+  <si>
+    <t>C117993 02.07.2026 7193 Magazijn</t>
+  </si>
+  <si>
+    <t>TRIPLEA 10UL FILTER TIPS DS960ST</t>
+  </si>
+  <si>
+    <t>C101257 29.06.2026 7193 Jorn</t>
+  </si>
+  <si>
+    <t>microseal b adhes seal,100/pk (PK 100 E)</t>
   </si>
 </sst>
 </file>
@@ -846,7 +858,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -906,60 +918,60 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>1001366912</v>
+        <v>1001368508</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="1">
-        <v>704</v>
+        <v>121.84</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I2" s="3">
-        <v>46195</v>
+        <v>46205</v>
       </c>
       <c r="J2" s="4">
-        <v>0.63238425925925923</v>
+        <v>0.54736111111111108</v>
       </c>
       <c r="K2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>1001366912</v>
+        <v>1001367739</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E3" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="1">
-        <v>28</v>
+        <v>123.01</v>
       </c>
       <c r="G3" t="s">
         <v>0</v>
@@ -968,74 +980,74 @@
         <v>4</v>
       </c>
       <c r="I3" s="3">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="J3" s="4">
-        <v>0.6334953703703704</v>
+        <v>0.38149305555555557</v>
       </c>
       <c r="K3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>1001366367</v>
+        <v>1001366912</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="E4" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="1">
-        <v>322.25</v>
+        <v>704</v>
       </c>
       <c r="G4" t="s">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I4" s="3">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="J4" s="4">
-        <v>0.64398148148148149</v>
+        <v>0.63238425925925923</v>
       </c>
       <c r="K4" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="L4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>1001365392</v>
+        <v>1001366912</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="E5" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="1">
-        <v>1048</v>
+        <v>28</v>
       </c>
       <c r="G5" t="s">
         <v>0</v>
@@ -1044,36 +1056,36 @@
         <v>4</v>
       </c>
       <c r="I5" s="3">
-        <v>46184</v>
+        <v>46195</v>
       </c>
       <c r="J5" s="4">
-        <v>0.33641203703703698</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>81</v>
+        <v>0.6334953703703704</v>
+      </c>
+      <c r="K5" t="s">
+        <v>89</v>
+      </c>
+      <c r="L5" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>1001365168</v>
+        <v>1001366367</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="1">
-        <v>288.25</v>
+        <v>322.25</v>
       </c>
       <c r="G6" t="s">
         <v>0</v>
@@ -1082,36 +1094,36 @@
         <v>7</v>
       </c>
       <c r="I6" s="3">
-        <v>46182</v>
+        <v>46190</v>
       </c>
       <c r="J6" s="4">
-        <v>0.65709490740740739</v>
-      </c>
-      <c r="K6" s="10" t="s">
+        <v>0.64398148148148149</v>
+      </c>
+      <c r="K6" t="s">
         <v>82</v>
       </c>
-      <c r="L6" s="10" t="s">
+      <c r="L6" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>1001364804</v>
+        <v>1001365392</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
         <v>3</v>
       </c>
       <c r="F7" s="1">
-        <v>208.6</v>
+        <v>1048</v>
       </c>
       <c r="G7" t="s">
         <v>0</v>
@@ -1120,54 +1132,54 @@
         <v>4</v>
       </c>
       <c r="I7" s="3">
-        <v>46181</v>
+        <v>46184</v>
       </c>
       <c r="J7" s="4">
-        <v>0.45427083333333335</v>
+        <v>0.33641203703703698</v>
       </c>
       <c r="K7" s="10" t="s">
         <v>90</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>1001364804</v>
+        <v>1001365168</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
         <v>3</v>
       </c>
       <c r="F8" s="1">
-        <v>155.69999999999999</v>
+        <v>288.25</v>
       </c>
       <c r="G8" t="s">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I8" s="3">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="J8" s="4">
-        <v>0.45427083333333335</v>
+        <v>0.65709490740740739</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
@@ -1175,19 +1187,19 @@
         <v>1001364804</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
         <v>111</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
         <v>3</v>
       </c>
       <c r="F9" s="1">
-        <v>5</v>
+        <v>208.6</v>
       </c>
       <c r="G9" t="s">
         <v>0</v>
@@ -1210,22 +1222,22 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>1001364684</v>
+        <v>1001364804</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E10" t="s">
         <v>3</v>
       </c>
       <c r="F10" s="1">
-        <v>708.95</v>
+        <v>155.69999999999999</v>
       </c>
       <c r="G10" t="s">
         <v>0</v>
@@ -1234,36 +1246,36 @@
         <v>4</v>
       </c>
       <c r="I10" s="3">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="J10" s="4">
-        <v>0.55635416666666659</v>
+        <v>0.45427083333333335</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>1001364656</v>
+        <v>1001364804</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
         <v>3</v>
       </c>
       <c r="F11" s="1">
-        <v>242</v>
+        <v>5</v>
       </c>
       <c r="G11" t="s">
         <v>0</v>
@@ -1272,36 +1284,36 @@
         <v>4</v>
       </c>
       <c r="I11" s="3">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="J11" s="4">
-        <v>0.48500000000000004</v>
+        <v>0.45427083333333335</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>1001364656</v>
+        <v>1001364684</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
         <v>115</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E12" t="s">
         <v>3</v>
       </c>
       <c r="F12" s="1">
-        <v>25</v>
+        <v>708.95</v>
       </c>
       <c r="G12" t="s">
         <v>0</v>
@@ -1313,10 +1325,10 @@
         <v>46178</v>
       </c>
       <c r="J12" s="4">
-        <v>0.48591435185185183</v>
+        <v>0.55635416666666659</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L12" s="10" t="s">
         <v>79</v>
@@ -1324,98 +1336,98 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>1001362595</v>
+        <v>1001364656</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>92</v>
+        <v>14</v>
       </c>
       <c r="E13" t="s">
         <v>3</v>
       </c>
       <c r="F13" s="1">
-        <v>128.9</v>
+        <v>242</v>
       </c>
       <c r="G13" t="s">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I13" s="3">
-        <v>46164</v>
+        <v>46178</v>
       </c>
       <c r="J13" s="4">
-        <v>0.57401620370370365</v>
-      </c>
-      <c r="K13" t="s">
-        <v>82</v>
-      </c>
-      <c r="L13" t="s">
-        <v>83</v>
+        <v>0.48500000000000004</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>1001362595</v>
+        <v>1001364656</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="E14" t="s">
         <v>3</v>
       </c>
       <c r="F14" s="1">
-        <v>115.3</v>
+        <v>25</v>
       </c>
       <c r="G14" t="s">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I14" s="3">
-        <v>46164</v>
+        <v>46178</v>
       </c>
       <c r="J14" s="4">
-        <v>0.5740277777777778</v>
-      </c>
-      <c r="K14" t="s">
-        <v>82</v>
-      </c>
-      <c r="L14" t="s">
-        <v>83</v>
+        <v>0.48591435185185183</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L14" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>1001361760</v>
+        <v>1001364656</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="D15" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="E15" t="s">
         <v>3</v>
       </c>
       <c r="F15" s="1">
-        <v>2706.88</v>
+        <v>2250</v>
       </c>
       <c r="G15" t="s">
         <v>0</v>
@@ -1424,36 +1436,36 @@
         <v>4</v>
       </c>
       <c r="I15" s="3">
-        <v>46161</v>
+        <v>46178</v>
       </c>
       <c r="J15" s="4">
-        <v>0.40358796296296301</v>
-      </c>
-      <c r="K15" t="s">
-        <v>90</v>
-      </c>
-      <c r="L15" t="s">
+        <v>0.48841435185185184</v>
+      </c>
+      <c r="K15" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L15" s="10" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>1001361760</v>
+        <v>1001364656</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="D16" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="E16" t="s">
         <v>3</v>
       </c>
       <c r="F16" s="1">
-        <v>477.84</v>
+        <v>0</v>
       </c>
       <c r="G16" t="s">
         <v>0</v>
@@ -1462,36 +1474,36 @@
         <v>4</v>
       </c>
       <c r="I16" s="3">
-        <v>46161</v>
+        <v>46178</v>
       </c>
       <c r="J16" s="4">
-        <v>0.40358796296296301</v>
-      </c>
-      <c r="K16" t="s">
-        <v>90</v>
-      </c>
-      <c r="L16" t="s">
+        <v>0.48898148148148146</v>
+      </c>
+      <c r="K16" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L16" s="10" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>1001361434</v>
+        <v>1001364511</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="E17" t="s">
         <v>3</v>
       </c>
       <c r="F17" s="1">
-        <v>41.1</v>
+        <v>738</v>
       </c>
       <c r="G17" t="s">
         <v>0</v>
@@ -1500,226 +1512,226 @@
         <v>4</v>
       </c>
       <c r="I17" s="3">
-        <v>46160</v>
+        <v>46177</v>
       </c>
       <c r="J17" s="4">
-        <v>0.34767361111111111</v>
+        <v>0.63017361111111114</v>
       </c>
       <c r="K17" t="s">
         <v>82</v>
       </c>
-      <c r="L17" t="s">
-        <v>86</v>
+      <c r="L17" s="10" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>1001361434</v>
+        <v>1001362595</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D18" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E18" t="s">
         <v>3</v>
       </c>
       <c r="F18" s="1">
-        <v>82.2</v>
+        <v>128.9</v>
       </c>
       <c r="G18" t="s">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I18" s="3">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="J18" s="4">
-        <v>0.34847222222222224</v>
+        <v>0.57401620370370365</v>
       </c>
       <c r="K18" t="s">
         <v>82</v>
       </c>
       <c r="L18" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>1001361434</v>
+        <v>1001362595</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D19" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E19" t="s">
         <v>3</v>
       </c>
       <c r="F19" s="1">
-        <v>6.95</v>
+        <v>115.3</v>
       </c>
       <c r="G19" t="s">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I19" s="3">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="J19" s="4">
-        <v>0.3489814814814815</v>
+        <v>0.5740277777777778</v>
       </c>
       <c r="K19" t="s">
         <v>82</v>
       </c>
       <c r="L19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>1001361254</v>
+        <v>1001361760</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E20" t="s">
         <v>3</v>
       </c>
       <c r="F20" s="1">
-        <v>172.95</v>
+        <v>2706.88</v>
       </c>
       <c r="G20" t="s">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I20" s="3">
-        <v>46155</v>
+        <v>46161</v>
       </c>
       <c r="J20" s="4">
-        <v>0.68266203703703709</v>
+        <v>0.40358796296296301</v>
       </c>
       <c r="K20" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L20" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>1001360993</v>
+        <v>1001361760</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E21" t="s">
         <v>3</v>
       </c>
       <c r="F21" s="1">
-        <v>8763.34</v>
+        <v>477.84</v>
       </c>
       <c r="G21" t="s">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="I21" s="3">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="J21" s="4">
-        <v>0.66589120370370369</v>
+        <v>0.40358796296296301</v>
       </c>
       <c r="K21" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="L21" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>1001360993</v>
+        <v>1001361434</v>
       </c>
       <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="1">
+        <v>41.1</v>
+      </c>
+      <c r="G22" t="s">
+        <v>0</v>
+      </c>
+      <c r="H22" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3">
+        <v>46160</v>
+      </c>
+      <c r="J22" s="4">
+        <v>0.34767361111111111</v>
+      </c>
+      <c r="K22" t="s">
+        <v>82</v>
+      </c>
+      <c r="L22" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>1001361434</v>
+      </c>
+      <c r="B23">
         <v>2</v>
       </c>
-      <c r="C22" t="s">
-        <v>102</v>
-      </c>
-      <c r="D22" t="s">
-        <v>105</v>
-      </c>
-      <c r="E22" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="1">
-        <v>586.66</v>
-      </c>
-      <c r="G22" t="s">
-        <v>0</v>
-      </c>
-      <c r="H22" t="s">
-        <v>104</v>
-      </c>
-      <c r="I22" s="3">
-        <v>46154</v>
-      </c>
-      <c r="J22" s="4">
-        <v>0.6667939814814815</v>
-      </c>
-      <c r="K22" t="s">
-        <v>106</v>
-      </c>
-      <c r="L22" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="2">
-        <v>1001360515</v>
-      </c>
-      <c r="B23" s="2">
-        <v>1</v>
-      </c>
       <c r="C23" t="s">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="E23" t="s">
         <v>3</v>
       </c>
       <c r="F23" s="1">
-        <v>0</v>
+        <v>82.2</v>
       </c>
       <c r="G23" t="s">
         <v>0</v>
@@ -1728,188 +1740,188 @@
         <v>4</v>
       </c>
       <c r="I23" s="3">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="J23" s="4">
-        <v>0.43606481481481479</v>
+        <v>0.34847222222222224</v>
       </c>
       <c r="K23" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L23" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="2">
-        <v>1001359403</v>
-      </c>
-      <c r="B24" s="2">
-        <v>1</v>
+      <c r="A24">
+        <v>1001361434</v>
+      </c>
+      <c r="B24">
+        <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>5</v>
+        <v>97</v>
       </c>
       <c r="D24" t="s">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="E24" t="s">
         <v>3</v>
       </c>
       <c r="F24" s="1">
-        <v>296.16000000000003</v>
+        <v>6.95</v>
       </c>
       <c r="G24" t="s">
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I24" s="3">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="J24" s="4">
-        <v>0.35246527777777775</v>
+        <v>0.3489814814814815</v>
       </c>
       <c r="K24" t="s">
         <v>82</v>
       </c>
       <c r="L24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>1001361254</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" t="s">
+        <v>93</v>
+      </c>
+      <c r="E25" t="s">
+        <v>3</v>
+      </c>
+      <c r="F25" s="1">
+        <v>172.95</v>
+      </c>
+      <c r="G25" t="s">
+        <v>0</v>
+      </c>
+      <c r="H25" t="s">
+        <v>7</v>
+      </c>
+      <c r="I25" s="3">
+        <v>46155</v>
+      </c>
+      <c r="J25" s="4">
+        <v>0.68266203703703709</v>
+      </c>
+      <c r="K25" t="s">
+        <v>82</v>
+      </c>
+      <c r="L25" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="2">
-        <v>1001358440</v>
-      </c>
-      <c r="B25" s="2">
-        <v>1</v>
-      </c>
-      <c r="C25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" t="s">
-        <v>9</v>
-      </c>
-      <c r="E25" t="s">
-        <v>3</v>
-      </c>
-      <c r="F25" s="1">
-        <v>8211</v>
-      </c>
-      <c r="G25" t="s">
-        <v>0</v>
-      </c>
-      <c r="H25" t="s">
-        <v>4</v>
-      </c>
-      <c r="I25" s="3">
-        <v>46136</v>
-      </c>
-      <c r="J25" s="4">
-        <v>0.51320601851851855</v>
-      </c>
-      <c r="K25" t="s">
-        <v>90</v>
-      </c>
-      <c r="L25" t="s">
-        <v>79</v>
-      </c>
-    </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="2">
-        <v>1001358139</v>
-      </c>
-      <c r="B26" s="2">
+      <c r="A26">
+        <v>1001360993</v>
+      </c>
+      <c r="B26">
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="D26" t="s">
-        <v>6</v>
+        <v>103</v>
       </c>
       <c r="E26" t="s">
         <v>3</v>
       </c>
       <c r="F26" s="1">
-        <v>296.16000000000003</v>
+        <v>8763.34</v>
       </c>
       <c r="G26" t="s">
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>7</v>
+        <v>104</v>
       </c>
       <c r="I26" s="3">
-        <v>46135</v>
+        <v>46154</v>
       </c>
       <c r="J26" s="4">
-        <v>0.40256944444444448</v>
+        <v>0.66589120370370369</v>
       </c>
       <c r="K26" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="L26" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="2">
-        <v>1001357792</v>
-      </c>
-      <c r="B27" s="2">
-        <v>1</v>
+      <c r="A27">
+        <v>1001360993</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>11</v>
+        <v>102</v>
       </c>
       <c r="D27" t="s">
-        <v>12</v>
+        <v>105</v>
       </c>
       <c r="E27" t="s">
         <v>3</v>
       </c>
       <c r="F27" s="1">
-        <v>62.02</v>
+        <v>586.66</v>
       </c>
       <c r="G27" t="s">
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="I27" s="3">
-        <v>46133</v>
+        <v>46154</v>
       </c>
       <c r="J27" s="4">
-        <v>0.59369212962962969</v>
+        <v>0.6667939814814815</v>
       </c>
       <c r="K27" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="L27" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>1001357548</v>
+        <v>1001360515</v>
       </c>
       <c r="B28" s="2">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E28" t="s">
         <v>3</v>
       </c>
       <c r="F28" s="1">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="G28" t="s">
         <v>0</v>
@@ -1918,74 +1930,74 @@
         <v>4</v>
       </c>
       <c r="I28" s="3">
-        <v>46132</v>
+        <v>46153</v>
       </c>
       <c r="J28" s="4">
-        <v>0.54353009259259266</v>
+        <v>0.43606481481481479</v>
       </c>
       <c r="K28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L28" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>1001357548</v>
+        <v>1001359403</v>
       </c>
       <c r="B29" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D29" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E29" t="s">
         <v>3</v>
       </c>
       <c r="F29" s="1">
-        <v>25</v>
+        <v>296.16000000000003</v>
       </c>
       <c r="G29" t="s">
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I29" s="3">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="J29" s="4">
-        <v>0.54533564814814817</v>
+        <v>0.35246527777777775</v>
       </c>
       <c r="K29" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L29" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>1001357548</v>
+        <v>1001358440</v>
       </c>
       <c r="B30" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E30" t="s">
         <v>3</v>
       </c>
       <c r="F30" s="1">
-        <v>2250</v>
+        <v>8211</v>
       </c>
       <c r="G30" t="s">
         <v>0</v>
@@ -1994,36 +2006,36 @@
         <v>4</v>
       </c>
       <c r="I30" s="3">
-        <v>46132</v>
+        <v>46136</v>
       </c>
       <c r="J30" s="4">
-        <v>0.546412037037037</v>
+        <v>0.51320601851851855</v>
       </c>
       <c r="K30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>1001356465</v>
+        <v>1001358139</v>
       </c>
       <c r="B31" s="2">
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E31" t="s">
         <v>3</v>
       </c>
       <c r="F31" s="1">
-        <v>17.55</v>
+        <v>296.16000000000003</v>
       </c>
       <c r="G31" t="s">
         <v>0</v>
@@ -2032,74 +2044,74 @@
         <v>7</v>
       </c>
       <c r="I31" s="3">
-        <v>46125</v>
+        <v>46135</v>
       </c>
       <c r="J31" s="4">
-        <v>0.65668981481481481</v>
+        <v>0.40256944444444448</v>
       </c>
       <c r="K31" t="s">
         <v>82</v>
       </c>
       <c r="L31" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>1001356465</v>
+        <v>1001357792</v>
       </c>
       <c r="B32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E32" t="s">
         <v>3</v>
       </c>
       <c r="F32" s="1">
-        <v>17.55</v>
+        <v>62.02</v>
       </c>
       <c r="G32" t="s">
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I32" s="3">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="J32" s="4">
-        <v>0.65668981481481481</v>
+        <v>0.59369212962962969</v>
       </c>
       <c r="K32" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L32" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>1001356192</v>
+        <v>1001357548</v>
       </c>
       <c r="B33" s="2">
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E33" t="s">
         <v>3</v>
       </c>
       <c r="F33" s="1">
-        <v>270.5</v>
+        <v>242</v>
       </c>
       <c r="G33" t="s">
         <v>0</v>
@@ -2108,36 +2120,36 @@
         <v>4</v>
       </c>
       <c r="I33" s="3">
-        <v>46122</v>
+        <v>46132</v>
       </c>
       <c r="J33" s="4">
-        <v>0.58597222222222223</v>
+        <v>0.54353009259259266</v>
       </c>
       <c r="K33" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="L33" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>1001356190</v>
+        <v>1001357548</v>
       </c>
       <c r="B34" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E34" t="s">
         <v>3</v>
       </c>
       <c r="F34" s="1">
-        <v>1359.84</v>
+        <v>25</v>
       </c>
       <c r="G34" t="s">
         <v>0</v>
@@ -2146,36 +2158,36 @@
         <v>4</v>
       </c>
       <c r="I34" s="3">
-        <v>46122</v>
+        <v>46132</v>
       </c>
       <c r="J34" s="4">
-        <v>0.58506944444444442</v>
+        <v>0.54533564814814817</v>
       </c>
       <c r="K34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L34" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>1001355643</v>
+        <v>1001357548</v>
       </c>
       <c r="B35" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E35" t="s">
         <v>3</v>
       </c>
       <c r="F35" s="1">
-        <v>425.29</v>
+        <v>2250</v>
       </c>
       <c r="G35" t="s">
         <v>0</v>
@@ -2184,36 +2196,36 @@
         <v>4</v>
       </c>
       <c r="I35" s="3">
-        <v>46120</v>
+        <v>46132</v>
       </c>
       <c r="J35" s="4">
-        <v>0.58754629629629629</v>
+        <v>0.546412037037037</v>
       </c>
       <c r="K35" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="L35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>1001354025</v>
+        <v>1001356465</v>
       </c>
       <c r="B36" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D36" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E36" t="s">
         <v>3</v>
       </c>
       <c r="F36" s="1">
-        <v>247</v>
+        <v>17.55</v>
       </c>
       <c r="G36" t="s">
         <v>0</v>
@@ -2222,36 +2234,36 @@
         <v>7</v>
       </c>
       <c r="I36" s="3">
-        <v>46108</v>
+        <v>46125</v>
       </c>
       <c r="J36" s="4">
-        <v>0.54822916666666666</v>
+        <v>0.65668981481481481</v>
       </c>
       <c r="K36" t="s">
         <v>82</v>
       </c>
       <c r="L36" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>1001354025</v>
+        <v>1001356465</v>
       </c>
       <c r="B37" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D37" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E37" t="s">
         <v>3</v>
       </c>
       <c r="F37" s="1">
-        <v>41</v>
+        <v>17.55</v>
       </c>
       <c r="G37" t="s">
         <v>0</v>
@@ -2260,74 +2272,74 @@
         <v>7</v>
       </c>
       <c r="I37" s="3">
-        <v>46108</v>
+        <v>46125</v>
       </c>
       <c r="J37" s="4">
-        <v>0.54866898148148147</v>
+        <v>0.65668981481481481</v>
       </c>
       <c r="K37" t="s">
         <v>82</v>
       </c>
       <c r="L37" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>1001354025</v>
+        <v>1001356192</v>
       </c>
       <c r="B38" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D38" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E38" t="s">
         <v>3</v>
       </c>
       <c r="F38" s="1">
-        <v>732</v>
+        <v>270.5</v>
       </c>
       <c r="G38" t="s">
         <v>0</v>
       </c>
       <c r="H38" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I38" s="3">
-        <v>46108</v>
+        <v>46122</v>
       </c>
       <c r="J38" s="4">
-        <v>0.5505902777777778</v>
+        <v>0.58597222222222223</v>
       </c>
       <c r="K38" t="s">
         <v>82</v>
       </c>
       <c r="L38" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>1001351971</v>
+        <v>1001356190</v>
       </c>
       <c r="B39" s="2">
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D39" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E39" t="s">
         <v>3</v>
       </c>
       <c r="F39" s="1">
-        <v>1.9</v>
+        <v>1359.84</v>
       </c>
       <c r="G39" t="s">
         <v>0</v>
@@ -2336,36 +2348,36 @@
         <v>4</v>
       </c>
       <c r="I39" s="3">
-        <v>46098</v>
+        <v>46122</v>
       </c>
       <c r="J39" s="4">
-        <v>0.34575231481481478</v>
+        <v>0.58506944444444442</v>
       </c>
       <c r="K39" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L39" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>1001351971</v>
+        <v>1001355643</v>
       </c>
       <c r="B40" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D40" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E40" t="s">
         <v>3</v>
       </c>
       <c r="F40" s="1">
-        <v>1.8</v>
+        <v>425.29</v>
       </c>
       <c r="G40" t="s">
         <v>0</v>
@@ -2374,150 +2386,150 @@
         <v>4</v>
       </c>
       <c r="I40" s="3">
-        <v>46098</v>
+        <v>46120</v>
       </c>
       <c r="J40" s="4">
-        <v>0.34575231481481478</v>
+        <v>0.58754629629629629</v>
       </c>
       <c r="K40" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L40" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>1001351235</v>
+        <v>1001354025</v>
       </c>
       <c r="B41" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D41" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E41" t="s">
         <v>3</v>
       </c>
       <c r="F41" s="1">
-        <v>153.19999999999999</v>
+        <v>247</v>
       </c>
       <c r="G41" t="s">
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I41" s="3">
-        <v>46092</v>
+        <v>46108</v>
       </c>
       <c r="J41" s="4">
-        <v>0.66688657407407403</v>
+        <v>0.54822916666666666</v>
       </c>
       <c r="K41" t="s">
         <v>82</v>
       </c>
       <c r="L41" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>1001351075</v>
+        <v>1001354025</v>
       </c>
       <c r="B42" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C42" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D42" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E42" t="s">
         <v>3</v>
       </c>
       <c r="F42" s="1">
-        <v>127</v>
+        <v>41</v>
       </c>
       <c r="G42" t="s">
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I42" s="3">
-        <v>46092</v>
+        <v>46108</v>
       </c>
       <c r="J42" s="4">
-        <v>0.40361111111111114</v>
+        <v>0.54866898148148147</v>
       </c>
       <c r="K42" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L42" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>1001351075</v>
+        <v>1001354025</v>
       </c>
       <c r="B43" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C43" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D43" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E43" t="s">
         <v>3</v>
       </c>
       <c r="F43" s="1">
-        <v>15</v>
+        <v>732</v>
       </c>
       <c r="G43" t="s">
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I43" s="3">
-        <v>46092</v>
+        <v>46108</v>
       </c>
       <c r="J43" s="4">
-        <v>0.6585185185185185</v>
+        <v>0.5505902777777778</v>
       </c>
       <c r="K43" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L43" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>1001351001</v>
+        <v>1001351971</v>
       </c>
       <c r="B44" s="2">
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D44" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E44" t="s">
         <v>3</v>
       </c>
       <c r="F44" s="1">
-        <v>598.67999999999995</v>
+        <v>1.9</v>
       </c>
       <c r="G44" t="s">
         <v>0</v>
@@ -2526,36 +2538,36 @@
         <v>4</v>
       </c>
       <c r="I44" s="3">
-        <v>46091</v>
+        <v>46098</v>
       </c>
       <c r="J44" s="4">
-        <v>0.63434027777777779</v>
+        <v>0.34575231481481478</v>
       </c>
       <c r="K44" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L44" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>1001350675</v>
+        <v>1001351971</v>
       </c>
       <c r="B45" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D45" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E45" t="s">
         <v>3</v>
       </c>
       <c r="F45" s="1">
-        <v>600</v>
+        <v>1.8</v>
       </c>
       <c r="G45" t="s">
         <v>0</v>
@@ -2564,36 +2576,36 @@
         <v>4</v>
       </c>
       <c r="I45" s="3">
-        <v>46090</v>
+        <v>46098</v>
       </c>
       <c r="J45" s="4">
-        <v>0.54053240740740738</v>
+        <v>0.34575231481481478</v>
       </c>
       <c r="K45" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L45" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>1001350592</v>
+        <v>1001351235</v>
       </c>
       <c r="B46" s="2">
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D46" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E46" t="s">
         <v>3</v>
       </c>
       <c r="F46" s="1">
-        <v>449.01</v>
+        <v>153.19999999999999</v>
       </c>
       <c r="G46" t="s">
         <v>0</v>
@@ -2602,36 +2614,36 @@
         <v>4</v>
       </c>
       <c r="I46" s="3">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="J46" s="4">
-        <v>0.37918981481481479</v>
+        <v>0.66688657407407403</v>
       </c>
       <c r="K46" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L46" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>1001350094</v>
+        <v>1001351075</v>
       </c>
       <c r="B47" s="2">
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D47" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E47" t="s">
         <v>3</v>
       </c>
       <c r="F47" s="1">
-        <v>679.92</v>
+        <v>127</v>
       </c>
       <c r="G47" t="s">
         <v>0</v>
@@ -2640,36 +2652,36 @@
         <v>4</v>
       </c>
       <c r="I47" s="3">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="J47" s="4">
-        <v>0.39840277777777783</v>
+        <v>0.40361111111111114</v>
       </c>
       <c r="K47" t="s">
         <v>90</v>
       </c>
       <c r="L47" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>1001350094</v>
+        <v>1001351075</v>
       </c>
       <c r="B48" s="2">
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D48" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E48" t="s">
         <v>3</v>
       </c>
       <c r="F48" s="1">
-        <v>87.14</v>
+        <v>15</v>
       </c>
       <c r="G48" t="s">
         <v>0</v>
@@ -2678,36 +2690,36 @@
         <v>4</v>
       </c>
       <c r="I48" s="3">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="J48" s="4">
-        <v>0.39840277777777783</v>
+        <v>0.6585185185185185</v>
       </c>
       <c r="K48" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L48" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>1001349263</v>
+        <v>1001351001</v>
       </c>
       <c r="B49" s="2">
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D49" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E49" t="s">
         <v>3</v>
       </c>
       <c r="F49" s="1">
-        <v>14.55</v>
+        <v>598.67999999999995</v>
       </c>
       <c r="G49" t="s">
         <v>0</v>
@@ -2716,13 +2728,13 @@
         <v>4</v>
       </c>
       <c r="I49" s="3">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="J49" s="4">
-        <v>0.39340277777777777</v>
+        <v>0.63434027777777779</v>
       </c>
       <c r="K49" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L49" t="s">
         <v>79</v>
@@ -2730,22 +2742,22 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>1001349263</v>
+        <v>1001350675</v>
       </c>
       <c r="B50" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D50" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E50" t="s">
         <v>3</v>
       </c>
       <c r="F50" s="1">
-        <v>15.15</v>
+        <v>600</v>
       </c>
       <c r="G50" t="s">
         <v>0</v>
@@ -2754,36 +2766,36 @@
         <v>4</v>
       </c>
       <c r="I50" s="3">
-        <v>46083</v>
+        <v>46090</v>
       </c>
       <c r="J50" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.54053240740740738</v>
       </c>
       <c r="K50" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L50" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>1001349263</v>
+        <v>1001350592</v>
       </c>
       <c r="B51" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D51" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E51" t="s">
         <v>3</v>
       </c>
       <c r="F51" s="1">
-        <v>15.15</v>
+        <v>449.01</v>
       </c>
       <c r="G51" t="s">
         <v>0</v>
@@ -2792,13 +2804,13 @@
         <v>4</v>
       </c>
       <c r="I51" s="3">
-        <v>46083</v>
+        <v>46090</v>
       </c>
       <c r="J51" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.37918981481481479</v>
       </c>
       <c r="K51" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L51" t="s">
         <v>79</v>
@@ -2806,22 +2818,22 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>1001349263</v>
+        <v>1001350094</v>
       </c>
       <c r="B52" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D52" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E52" t="s">
         <v>3</v>
       </c>
       <c r="F52" s="1">
-        <v>14.55</v>
+        <v>679.92</v>
       </c>
       <c r="G52" t="s">
         <v>0</v>
@@ -2830,36 +2842,36 @@
         <v>4</v>
       </c>
       <c r="I52" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="J52" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.39840277777777783</v>
       </c>
       <c r="K52" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L52" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>1001349263</v>
+        <v>1001350094</v>
       </c>
       <c r="B53" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D53" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E53" t="s">
         <v>3</v>
       </c>
       <c r="F53" s="1">
-        <v>14.85</v>
+        <v>87.14</v>
       </c>
       <c r="G53" t="s">
         <v>0</v>
@@ -2868,16 +2880,16 @@
         <v>4</v>
       </c>
       <c r="I53" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="J53" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.39840277777777783</v>
       </c>
       <c r="K53" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L53" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
@@ -2885,19 +2897,19 @@
         <v>1001349263</v>
       </c>
       <c r="B54" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C54" t="s">
         <v>45</v>
       </c>
       <c r="D54" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E54" t="s">
         <v>3</v>
       </c>
       <c r="F54" s="1">
-        <v>15</v>
+        <v>14.55</v>
       </c>
       <c r="G54" t="s">
         <v>0</v>
@@ -2909,7 +2921,7 @@
         <v>46083</v>
       </c>
       <c r="J54" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.39340277777777777</v>
       </c>
       <c r="K54" t="s">
         <v>84</v>
@@ -2923,19 +2935,19 @@
         <v>1001349263</v>
       </c>
       <c r="B55" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C55" t="s">
         <v>45</v>
       </c>
       <c r="D55" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E55" t="s">
         <v>3</v>
       </c>
       <c r="F55" s="1">
-        <v>15</v>
+        <v>15.15</v>
       </c>
       <c r="G55" t="s">
         <v>0</v>
@@ -2961,19 +2973,19 @@
         <v>1001349263</v>
       </c>
       <c r="B56" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C56" t="s">
         <v>45</v>
       </c>
       <c r="D56" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E56" t="s">
         <v>3</v>
       </c>
       <c r="F56" s="1">
-        <v>14.85</v>
+        <v>15.15</v>
       </c>
       <c r="G56" t="s">
         <v>0</v>
@@ -2996,22 +3008,22 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>1001345614</v>
+        <v>1001349263</v>
       </c>
       <c r="B57" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D57" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E57" t="s">
         <v>3</v>
       </c>
       <c r="F57" s="1">
-        <v>605</v>
+        <v>14.55</v>
       </c>
       <c r="G57" t="s">
         <v>0</v>
@@ -3020,36 +3032,36 @@
         <v>4</v>
       </c>
       <c r="I57" s="3">
-        <v>46059</v>
+        <v>46083</v>
       </c>
       <c r="J57" s="4">
-        <v>0.6586805555555556</v>
+        <v>0.39341435185185186</v>
       </c>
       <c r="K57" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L57" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>1001345614</v>
+        <v>1001349263</v>
       </c>
       <c r="B58" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C58" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D58" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E58" t="s">
         <v>3</v>
       </c>
       <c r="F58" s="1">
-        <v>154</v>
+        <v>14.85</v>
       </c>
       <c r="G58" t="s">
         <v>0</v>
@@ -3058,36 +3070,36 @@
         <v>4</v>
       </c>
       <c r="I58" s="3">
-        <v>46059</v>
+        <v>46083</v>
       </c>
       <c r="J58" s="4">
-        <v>0.66027777777777774</v>
+        <v>0.39341435185185186</v>
       </c>
       <c r="K58" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L58" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>1001343034</v>
+        <v>1001349263</v>
       </c>
       <c r="B59" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C59" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D59" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E59" t="s">
         <v>3</v>
       </c>
       <c r="F59" s="1">
-        <v>208.6</v>
+        <v>15</v>
       </c>
       <c r="G59" t="s">
         <v>0</v>
@@ -3096,36 +3108,36 @@
         <v>4</v>
       </c>
       <c r="I59" s="3">
-        <v>46044</v>
+        <v>46083</v>
       </c>
       <c r="J59" s="4">
-        <v>0.65900462962962958</v>
+        <v>0.39341435185185186</v>
       </c>
       <c r="K59" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L59" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>1001343034</v>
+        <v>1001349263</v>
       </c>
       <c r="B60" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D60" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E60" t="s">
         <v>3</v>
       </c>
       <c r="F60" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G60" t="s">
         <v>0</v>
@@ -3134,36 +3146,36 @@
         <v>4</v>
       </c>
       <c r="I60" s="3">
-        <v>46044</v>
+        <v>46083</v>
       </c>
       <c r="J60" s="4">
-        <v>0.66190972222222222</v>
+        <v>0.39341435185185186</v>
       </c>
       <c r="K60" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L60" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>1001342447</v>
+        <v>1001349263</v>
       </c>
       <c r="B61" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D61" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E61" t="s">
         <v>3</v>
       </c>
       <c r="F61" s="1">
-        <v>240</v>
+        <v>14.85</v>
       </c>
       <c r="G61" t="s">
         <v>0</v>
@@ -3172,36 +3184,36 @@
         <v>4</v>
       </c>
       <c r="I61" s="3">
-        <v>46042</v>
+        <v>46083</v>
       </c>
       <c r="J61" s="4">
-        <v>0.54805555555555552</v>
+        <v>0.39341435185185186</v>
       </c>
       <c r="K61" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L61" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>1001342447</v>
+        <v>1001345614</v>
       </c>
       <c r="B62" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D62" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E62" t="s">
         <v>3</v>
       </c>
       <c r="F62" s="1">
-        <v>8.9499999999999993</v>
+        <v>605</v>
       </c>
       <c r="G62" t="s">
         <v>0</v>
@@ -3210,174 +3222,250 @@
         <v>4</v>
       </c>
       <c r="I62" s="3">
-        <v>46042</v>
+        <v>46059</v>
       </c>
       <c r="J62" s="4">
-        <v>0.54859953703703701</v>
+        <v>0.6586805555555556</v>
       </c>
       <c r="K62" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L62" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
+        <v>1001345614</v>
+      </c>
+      <c r="B63" s="2">
+        <v>2</v>
+      </c>
+      <c r="C63" t="s">
+        <v>54</v>
+      </c>
+      <c r="D63" t="s">
+        <v>56</v>
+      </c>
+      <c r="E63" t="s">
+        <v>3</v>
+      </c>
+      <c r="F63" s="1">
+        <v>154</v>
+      </c>
+      <c r="G63" t="s">
+        <v>0</v>
+      </c>
+      <c r="H63" t="s">
+        <v>4</v>
+      </c>
+      <c r="I63" s="3">
+        <v>46059</v>
+      </c>
+      <c r="J63" s="4">
+        <v>0.66027777777777774</v>
+      </c>
+      <c r="K63" t="s">
+        <v>82</v>
+      </c>
+      <c r="L63" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A64" s="2">
+        <v>1001343034</v>
+      </c>
+      <c r="B64" s="2">
+        <v>1</v>
+      </c>
+      <c r="C64" t="s">
+        <v>57</v>
+      </c>
+      <c r="D64" t="s">
+        <v>58</v>
+      </c>
+      <c r="E64" t="s">
+        <v>3</v>
+      </c>
+      <c r="F64" s="1">
+        <v>208.6</v>
+      </c>
+      <c r="G64" t="s">
+        <v>0</v>
+      </c>
+      <c r="H64" t="s">
+        <v>4</v>
+      </c>
+      <c r="I64" s="3">
+        <v>46044</v>
+      </c>
+      <c r="J64" s="4">
+        <v>0.65900462962962958</v>
+      </c>
+      <c r="K64" t="s">
+        <v>88</v>
+      </c>
+      <c r="L64" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A65" s="2">
+        <v>1001343034</v>
+      </c>
+      <c r="B65" s="2">
+        <v>2</v>
+      </c>
+      <c r="C65" t="s">
+        <v>57</v>
+      </c>
+      <c r="D65" t="s">
+        <v>59</v>
+      </c>
+      <c r="E65" t="s">
+        <v>3</v>
+      </c>
+      <c r="F65" s="1">
+        <v>20</v>
+      </c>
+      <c r="G65" t="s">
+        <v>0</v>
+      </c>
+      <c r="H65" t="s">
+        <v>4</v>
+      </c>
+      <c r="I65" s="3">
+        <v>46044</v>
+      </c>
+      <c r="J65" s="4">
+        <v>0.66190972222222222</v>
+      </c>
+      <c r="K65" t="s">
+        <v>88</v>
+      </c>
+      <c r="L65" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A66" s="2">
+        <v>1001342447</v>
+      </c>
+      <c r="B66" s="2">
+        <v>1</v>
+      </c>
+      <c r="C66" t="s">
+        <v>60</v>
+      </c>
+      <c r="D66" t="s">
+        <v>61</v>
+      </c>
+      <c r="E66" t="s">
+        <v>3</v>
+      </c>
+      <c r="F66" s="1">
+        <v>240</v>
+      </c>
+      <c r="G66" t="s">
+        <v>0</v>
+      </c>
+      <c r="H66" t="s">
+        <v>4</v>
+      </c>
+      <c r="I66" s="3">
+        <v>46042</v>
+      </c>
+      <c r="J66" s="4">
+        <v>0.54805555555555552</v>
+      </c>
+      <c r="K66" t="s">
+        <v>88</v>
+      </c>
+      <c r="L66" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A67" s="2">
+        <v>1001342447</v>
+      </c>
+      <c r="B67" s="2">
+        <v>2</v>
+      </c>
+      <c r="C67" t="s">
+        <v>60</v>
+      </c>
+      <c r="D67" t="s">
+        <v>62</v>
+      </c>
+      <c r="E67" t="s">
+        <v>3</v>
+      </c>
+      <c r="F67" s="1">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="G67" t="s">
+        <v>0</v>
+      </c>
+      <c r="H67" t="s">
+        <v>4</v>
+      </c>
+      <c r="I67" s="3">
+        <v>46042</v>
+      </c>
+      <c r="J67" s="4">
+        <v>0.54859953703703701</v>
+      </c>
+      <c r="K67" t="s">
+        <v>88</v>
+      </c>
+      <c r="L67" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A68" s="2">
         <v>1001340933</v>
       </c>
-      <c r="B63" s="2">
-        <v>1</v>
-      </c>
-      <c r="C63" t="s">
+      <c r="B68" s="2">
+        <v>1</v>
+      </c>
+      <c r="C68" t="s">
         <v>63</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D68" t="s">
         <v>64</v>
       </c>
-      <c r="E63" t="s">
-        <v>3</v>
-      </c>
-      <c r="F63" s="1">
+      <c r="E68" t="s">
+        <v>3</v>
+      </c>
+      <c r="F68" s="1">
         <v>150.47999999999999</v>
       </c>
-      <c r="G63" t="s">
-        <v>0</v>
-      </c>
-      <c r="H63" t="s">
-        <v>4</v>
-      </c>
-      <c r="I63" s="3">
+      <c r="G68" t="s">
+        <v>0</v>
+      </c>
+      <c r="H68" t="s">
+        <v>4</v>
+      </c>
+      <c r="I68" s="3">
         <v>46034</v>
       </c>
-      <c r="J63" s="4">
+      <c r="J68" s="4">
         <v>0.40950231481481486</v>
       </c>
-      <c r="K63" t="s">
+      <c r="K68" t="s">
         <v>90</v>
       </c>
-      <c r="L63" t="s">
+      <c r="L68" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A64">
-        <v>1001364656</v>
-      </c>
-      <c r="B64">
-        <v>3</v>
-      </c>
-      <c r="C64" t="s">
-        <v>115</v>
-      </c>
-      <c r="D64" t="s">
-        <v>118</v>
-      </c>
-      <c r="E64" t="s">
-        <v>3</v>
-      </c>
-      <c r="F64" s="1">
-        <v>2250</v>
-      </c>
-      <c r="G64" t="s">
-        <v>0</v>
-      </c>
-      <c r="H64" t="s">
-        <v>4</v>
-      </c>
-      <c r="I64" s="3">
-        <v>46178</v>
-      </c>
-      <c r="J64" s="4">
-        <v>0.48841435185185184</v>
-      </c>
-      <c r="K64" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="L64" s="10" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A65">
-        <v>1001364656</v>
-      </c>
-      <c r="B65">
-        <v>4</v>
-      </c>
-      <c r="C65" t="s">
-        <v>115</v>
-      </c>
-      <c r="D65" t="s">
-        <v>119</v>
-      </c>
-      <c r="E65" t="s">
-        <v>3</v>
-      </c>
-      <c r="F65" s="1">
-        <v>0</v>
-      </c>
-      <c r="G65" t="s">
-        <v>0</v>
-      </c>
-      <c r="H65" t="s">
-        <v>4</v>
-      </c>
-      <c r="I65" s="3">
-        <v>46178</v>
-      </c>
-      <c r="J65" s="4">
-        <v>0.48898148148148146</v>
-      </c>
-      <c r="K65" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="L65" s="10" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A66">
-        <v>1001364511</v>
-      </c>
-      <c r="B66">
-        <v>1</v>
-      </c>
-      <c r="C66" t="s">
-        <v>120</v>
-      </c>
-      <c r="D66" t="s">
-        <v>121</v>
-      </c>
-      <c r="E66" t="s">
-        <v>3</v>
-      </c>
-      <c r="F66" s="1">
-        <v>738</v>
-      </c>
-      <c r="G66" t="s">
-        <v>0</v>
-      </c>
-      <c r="H66" t="s">
-        <v>4</v>
-      </c>
-      <c r="I66" s="3">
-        <v>46177</v>
-      </c>
-      <c r="J66" s="4">
-        <v>0.63017361111111114</v>
-      </c>
-      <c r="K66" t="s">
-        <v>82</v>
-      </c>
-      <c r="L66" s="10" t="s">
-        <v>78</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M66" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M66">
-      <sortCondition descending="1" ref="A1:A63"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M68">
+      <sortCondition descending="1" ref="A1:A66"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="0" type="noConversion"/>

--- a/data/bestellingen 7193 2026_latest.xlsx
+++ b/data/bestellingen 7193 2026_latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\R\Bestellingen\shiny\7180\7180\jorgpeter-orders7180\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B6397E-9BB1-42EA-BADC-1F4683BE6EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E6D559-F649-4505-AD65-E1AE431E2BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="143">
   <si>
     <t>EUR</t>
   </si>
@@ -421,6 +421,42 @@
   </si>
   <si>
     <t>microseal b adhes seal,100/pk (PK 100 E)</t>
+  </si>
+  <si>
+    <t>C101257 31.07.2026 7193 Xanthe</t>
+  </si>
+  <si>
+    <t>invitrogen qubit assay tubes, (EA)</t>
+  </si>
+  <si>
+    <t>C117993 22.07.2026 7193 Magazijn</t>
+  </si>
+  <si>
+    <t>C101257 16.07.2026 7193 Hilde</t>
+  </si>
+  <si>
+    <t>Onder goedkeuring</t>
+  </si>
+  <si>
+    <t>C101257 15.07.2026 7193 Jorn</t>
+  </si>
+  <si>
+    <t>Microtube 2ml SafeSeal transparant (EH:</t>
+  </si>
+  <si>
+    <t>C101257 14.07.2026 7193 Nam</t>
+  </si>
+  <si>
+    <t>lecithin (EA)</t>
+  </si>
+  <si>
+    <t>C101257 10.07.2026 7193 Nam</t>
+  </si>
+  <si>
+    <t>cholesterol, powder, bioreagen (EA)</t>
+  </si>
+  <si>
+    <t>calcium-magnesium phytate [361 (0.5 kg)</t>
   </si>
 </sst>
 </file>
@@ -858,7 +894,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -918,98 +954,98 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>1001368508</v>
+        <v>1001372863</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="1">
-        <v>121.84</v>
+        <v>87.14</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I2" s="3">
-        <v>46205</v>
+        <v>46234</v>
       </c>
       <c r="J2" s="4">
-        <v>0.54736111111111108</v>
+        <v>0.53832175925925929</v>
       </c>
       <c r="K2" t="s">
         <v>82</v>
       </c>
       <c r="L2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>1001367739</v>
+        <v>1001371561</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E3" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="1">
-        <v>123.01</v>
+        <v>60.92</v>
       </c>
       <c r="G3" t="s">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I3" s="3">
-        <v>46202</v>
+        <v>46225</v>
       </c>
       <c r="J3" s="4">
-        <v>0.38149305555555557</v>
+        <v>0.64002314814814809</v>
       </c>
       <c r="K3" t="s">
         <v>82</v>
       </c>
       <c r="L3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>1001366912</v>
+        <v>1001370654</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="D4" t="s">
         <v>124</v>
       </c>
       <c r="E4" t="s">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="F4" s="1">
-        <v>704</v>
+        <v>10880</v>
       </c>
       <c r="G4" t="s">
         <v>0</v>
@@ -1018,10 +1054,10 @@
         <v>4</v>
       </c>
       <c r="I4" s="3">
-        <v>46195</v>
+        <v>46219</v>
       </c>
       <c r="J4" s="4">
-        <v>0.63238425925925923</v>
+        <v>0.48186342592592596</v>
       </c>
       <c r="K4" t="s">
         <v>89</v>
@@ -1032,22 +1068,22 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>1001366912</v>
+        <v>1001370654</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="D5" t="s">
         <v>125</v>
       </c>
       <c r="E5" t="s">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="F5" s="1">
-        <v>28</v>
+        <v>198</v>
       </c>
       <c r="G5" t="s">
         <v>0</v>
@@ -1056,10 +1092,10 @@
         <v>4</v>
       </c>
       <c r="I5" s="3">
-        <v>46195</v>
+        <v>46219</v>
       </c>
       <c r="J5" s="4">
-        <v>0.6334953703703704</v>
+        <v>0.48271990740740739</v>
       </c>
       <c r="K5" t="s">
         <v>89</v>
@@ -1070,60 +1106,60 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>1001366367</v>
+        <v>1001370526</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="E6" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="1">
-        <v>322.25</v>
+        <v>138.4</v>
       </c>
       <c r="G6" t="s">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I6" s="3">
-        <v>46190</v>
+        <v>46218</v>
       </c>
       <c r="J6" s="4">
-        <v>0.64398148148148149</v>
+        <v>0.63928240740740738</v>
       </c>
       <c r="K6" t="s">
         <v>82</v>
       </c>
       <c r="L6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>1001365392</v>
+        <v>1001370183</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="E7" t="s">
         <v>3</v>
       </c>
       <c r="F7" s="1">
-        <v>1048</v>
+        <v>84.51</v>
       </c>
       <c r="G7" t="s">
         <v>0</v>
@@ -1132,74 +1168,74 @@
         <v>4</v>
       </c>
       <c r="I7" s="3">
-        <v>46184</v>
+        <v>46217</v>
       </c>
       <c r="J7" s="4">
-        <v>0.33641203703703698</v>
-      </c>
-      <c r="K7" s="10" t="s">
+        <v>0.46013888888888888</v>
+      </c>
+      <c r="K7" t="s">
         <v>90</v>
       </c>
-      <c r="L7" s="10" t="s">
-        <v>81</v>
+      <c r="L7" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>1001365168</v>
+        <v>1001370183</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="E8" t="s">
         <v>3</v>
       </c>
       <c r="F8" s="1">
-        <v>288.25</v>
+        <v>5</v>
       </c>
       <c r="G8" t="s">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I8" s="3">
-        <v>46182</v>
+        <v>46217</v>
       </c>
       <c r="J8" s="4">
-        <v>0.65709490740740739</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="L8" s="10" t="s">
-        <v>83</v>
+        <v>0.46013888888888888</v>
+      </c>
+      <c r="K8" t="s">
+        <v>90</v>
+      </c>
+      <c r="L8" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>1001364804</v>
+        <v>1001369827</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="E9" t="s">
         <v>3</v>
       </c>
       <c r="F9" s="1">
-        <v>208.6</v>
+        <v>89.25</v>
       </c>
       <c r="G9" t="s">
         <v>0</v>
@@ -1208,36 +1244,36 @@
         <v>4</v>
       </c>
       <c r="I9" s="3">
-        <v>46181</v>
+        <v>46213</v>
       </c>
       <c r="J9" s="4">
-        <v>0.45427083333333335</v>
-      </c>
-      <c r="K9" s="10" t="s">
+        <v>0.60623842592592592</v>
+      </c>
+      <c r="K9" t="s">
         <v>90</v>
       </c>
-      <c r="L9" s="10" t="s">
-        <v>122</v>
+      <c r="L9" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>1001364804</v>
+        <v>1001369827</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E10" t="s">
         <v>3</v>
       </c>
       <c r="F10" s="1">
-        <v>155.69999999999999</v>
+        <v>5</v>
       </c>
       <c r="G10" t="s">
         <v>0</v>
@@ -1246,36 +1282,36 @@
         <v>4</v>
       </c>
       <c r="I10" s="3">
-        <v>46181</v>
+        <v>46213</v>
       </c>
       <c r="J10" s="4">
-        <v>0.45427083333333335</v>
-      </c>
-      <c r="K10" s="10" t="s">
+        <v>0.60623842592592592</v>
+      </c>
+      <c r="K10" t="s">
         <v>90</v>
       </c>
-      <c r="L10" s="10" t="s">
-        <v>122</v>
+      <c r="L10" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>1001364804</v>
+        <v>1001369807</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="D11" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="E11" t="s">
         <v>3</v>
       </c>
       <c r="F11" s="1">
-        <v>5</v>
+        <v>172</v>
       </c>
       <c r="G11" t="s">
         <v>0</v>
@@ -1284,74 +1320,74 @@
         <v>4</v>
       </c>
       <c r="I11" s="3">
-        <v>46181</v>
+        <v>46213</v>
       </c>
       <c r="J11" s="4">
-        <v>0.45427083333333335</v>
-      </c>
-      <c r="K11" s="10" t="s">
+        <v>0.56239583333333332</v>
+      </c>
+      <c r="K11" t="s">
         <v>90</v>
       </c>
-      <c r="L11" s="10" t="s">
-        <v>122</v>
+      <c r="L11" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>1001364684</v>
+        <v>1001368508</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="E12" t="s">
         <v>3</v>
       </c>
       <c r="F12" s="1">
-        <v>708.95</v>
+        <v>121.84</v>
       </c>
       <c r="G12" t="s">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I12" s="3">
-        <v>46178</v>
+        <v>46205</v>
       </c>
       <c r="J12" s="4">
-        <v>0.55635416666666659</v>
-      </c>
-      <c r="K12" s="10" t="s">
+        <v>0.54736111111111108</v>
+      </c>
+      <c r="K12" t="s">
         <v>82</v>
       </c>
-      <c r="L12" s="10" t="s">
-        <v>79</v>
+      <c r="L12" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>1001364656</v>
+        <v>1001367739</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
+        <v>130</v>
       </c>
       <c r="E13" t="s">
         <v>3</v>
       </c>
       <c r="F13" s="1">
-        <v>242</v>
+        <v>123.01</v>
       </c>
       <c r="G13" t="s">
         <v>0</v>
@@ -1360,36 +1396,36 @@
         <v>4</v>
       </c>
       <c r="I13" s="3">
-        <v>46178</v>
+        <v>46202</v>
       </c>
       <c r="J13" s="4">
-        <v>0.48500000000000004</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="L13" s="10" t="s">
+        <v>0.38149305555555557</v>
+      </c>
+      <c r="K13" t="s">
+        <v>82</v>
+      </c>
+      <c r="L13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>1001364656</v>
+        <v>1001366912</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D14" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E14" t="s">
         <v>3</v>
       </c>
       <c r="F14" s="1">
-        <v>25</v>
+        <v>704</v>
       </c>
       <c r="G14" t="s">
         <v>0</v>
@@ -1398,36 +1434,36 @@
         <v>4</v>
       </c>
       <c r="I14" s="3">
-        <v>46178</v>
+        <v>46195</v>
       </c>
       <c r="J14" s="4">
-        <v>0.48591435185185183</v>
-      </c>
-      <c r="K14" s="10" t="s">
+        <v>0.63238425925925923</v>
+      </c>
+      <c r="K14" t="s">
         <v>89</v>
       </c>
-      <c r="L14" s="10" t="s">
-        <v>79</v>
+      <c r="L14" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>1001364656</v>
+        <v>1001366912</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="E15" t="s">
         <v>3</v>
       </c>
       <c r="F15" s="1">
-        <v>2250</v>
+        <v>28</v>
       </c>
       <c r="G15" t="s">
         <v>0</v>
@@ -1436,74 +1472,74 @@
         <v>4</v>
       </c>
       <c r="I15" s="3">
-        <v>46178</v>
+        <v>46195</v>
       </c>
       <c r="J15" s="4">
-        <v>0.48841435185185184</v>
-      </c>
-      <c r="K15" s="10" t="s">
+        <v>0.6334953703703704</v>
+      </c>
+      <c r="K15" t="s">
         <v>89</v>
       </c>
-      <c r="L15" s="10" t="s">
-        <v>79</v>
+      <c r="L15" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>1001364656</v>
+        <v>1001366367</v>
       </c>
       <c r="B16">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="D16" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="E16" t="s">
         <v>3</v>
       </c>
       <c r="F16" s="1">
-        <v>0</v>
+        <v>322.25</v>
       </c>
       <c r="G16" t="s">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I16" s="3">
-        <v>46178</v>
+        <v>46190</v>
       </c>
       <c r="J16" s="4">
-        <v>0.48898148148148146</v>
-      </c>
-      <c r="K16" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="L16" s="10" t="s">
-        <v>79</v>
+        <v>0.64398148148148149</v>
+      </c>
+      <c r="K16" t="s">
+        <v>82</v>
+      </c>
+      <c r="L16" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>1001364511</v>
+        <v>1001365392</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E17" t="s">
         <v>3</v>
       </c>
       <c r="F17" s="1">
-        <v>738</v>
+        <v>1048</v>
       </c>
       <c r="G17" t="s">
         <v>0</v>
@@ -1512,36 +1548,36 @@
         <v>4</v>
       </c>
       <c r="I17" s="3">
-        <v>46177</v>
+        <v>46184</v>
       </c>
       <c r="J17" s="4">
-        <v>0.63017361111111114</v>
-      </c>
-      <c r="K17" t="s">
-        <v>82</v>
+        <v>0.33641203703703698</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>90</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>1001362595</v>
+        <v>1001365168</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="D18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E18" t="s">
         <v>3</v>
       </c>
       <c r="F18" s="1">
-        <v>128.9</v>
+        <v>288.25</v>
       </c>
       <c r="G18" t="s">
         <v>0</v>
@@ -1550,74 +1586,74 @@
         <v>7</v>
       </c>
       <c r="I18" s="3">
-        <v>46164</v>
+        <v>46182</v>
       </c>
       <c r="J18" s="4">
-        <v>0.57401620370370365</v>
-      </c>
-      <c r="K18" t="s">
+        <v>0.65709490740740739</v>
+      </c>
+      <c r="K18" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="L18" t="s">
+      <c r="L18" s="10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>1001362595</v>
+        <v>1001364804</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="D19" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="E19" t="s">
         <v>3</v>
       </c>
       <c r="F19" s="1">
-        <v>115.3</v>
+        <v>208.6</v>
       </c>
       <c r="G19" t="s">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I19" s="3">
-        <v>46164</v>
+        <v>46181</v>
       </c>
       <c r="J19" s="4">
-        <v>0.5740277777777778</v>
-      </c>
-      <c r="K19" t="s">
-        <v>82</v>
-      </c>
-      <c r="L19" t="s">
-        <v>83</v>
+        <v>0.45427083333333335</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="L19" s="10" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>1001361760</v>
+        <v>1001364804</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="D20" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="E20" t="s">
         <v>3</v>
       </c>
       <c r="F20" s="1">
-        <v>2706.88</v>
+        <v>155.69999999999999</v>
       </c>
       <c r="G20" t="s">
         <v>0</v>
@@ -1626,36 +1662,36 @@
         <v>4</v>
       </c>
       <c r="I20" s="3">
-        <v>46161</v>
+        <v>46181</v>
       </c>
       <c r="J20" s="4">
-        <v>0.40358796296296301</v>
-      </c>
-      <c r="K20" t="s">
+        <v>0.45427083333333335</v>
+      </c>
+      <c r="K20" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="L20" t="s">
-        <v>79</v>
+      <c r="L20" s="10" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>1001361760</v>
+        <v>1001364804</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="D21" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="E21" t="s">
         <v>3</v>
       </c>
       <c r="F21" s="1">
-        <v>477.84</v>
+        <v>5</v>
       </c>
       <c r="G21" t="s">
         <v>0</v>
@@ -1664,36 +1700,36 @@
         <v>4</v>
       </c>
       <c r="I21" s="3">
-        <v>46161</v>
+        <v>46181</v>
       </c>
       <c r="J21" s="4">
-        <v>0.40358796296296301</v>
-      </c>
-      <c r="K21" t="s">
+        <v>0.45427083333333335</v>
+      </c>
+      <c r="K21" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="L21" t="s">
-        <v>79</v>
+      <c r="L21" s="10" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>1001361434</v>
+        <v>1001364684</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="D22" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="E22" t="s">
         <v>3</v>
       </c>
       <c r="F22" s="1">
-        <v>41.1</v>
+        <v>708.95</v>
       </c>
       <c r="G22" t="s">
         <v>0</v>
@@ -1702,36 +1738,36 @@
         <v>4</v>
       </c>
       <c r="I22" s="3">
-        <v>46160</v>
+        <v>46178</v>
       </c>
       <c r="J22" s="4">
-        <v>0.34767361111111111</v>
-      </c>
-      <c r="K22" t="s">
+        <v>0.55635416666666659</v>
+      </c>
+      <c r="K22" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="L22" t="s">
-        <v>86</v>
+      <c r="L22" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>1001361434</v>
+        <v>1001364656</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="E23" t="s">
         <v>3</v>
       </c>
       <c r="F23" s="1">
-        <v>82.2</v>
+        <v>242</v>
       </c>
       <c r="G23" t="s">
         <v>0</v>
@@ -1740,36 +1776,36 @@
         <v>4</v>
       </c>
       <c r="I23" s="3">
-        <v>46160</v>
+        <v>46178</v>
       </c>
       <c r="J23" s="4">
-        <v>0.34847222222222224</v>
-      </c>
-      <c r="K23" t="s">
-        <v>82</v>
-      </c>
-      <c r="L23" t="s">
-        <v>86</v>
+        <v>0.48500000000000004</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>1001361434</v>
+        <v>1001364656</v>
       </c>
       <c r="B24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="D24" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="E24" t="s">
         <v>3</v>
       </c>
       <c r="F24" s="1">
-        <v>6.95</v>
+        <v>25</v>
       </c>
       <c r="G24" t="s">
         <v>0</v>
@@ -1778,188 +1814,188 @@
         <v>4</v>
       </c>
       <c r="I24" s="3">
-        <v>46160</v>
+        <v>46178</v>
       </c>
       <c r="J24" s="4">
-        <v>0.3489814814814815</v>
-      </c>
-      <c r="K24" t="s">
-        <v>82</v>
-      </c>
-      <c r="L24" t="s">
-        <v>85</v>
+        <v>0.48591435185185183</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L24" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>1001361254</v>
+        <v>1001364656</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="E25" t="s">
         <v>3</v>
       </c>
       <c r="F25" s="1">
-        <v>172.95</v>
+        <v>2250</v>
       </c>
       <c r="G25" t="s">
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I25" s="3">
-        <v>46155</v>
+        <v>46178</v>
       </c>
       <c r="J25" s="4">
-        <v>0.68266203703703709</v>
-      </c>
-      <c r="K25" t="s">
-        <v>82</v>
-      </c>
-      <c r="L25" t="s">
-        <v>83</v>
+        <v>0.48841435185185184</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L25" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>1001360993</v>
+        <v>1001364656</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="E26" t="s">
         <v>3</v>
       </c>
       <c r="F26" s="1">
-        <v>8763.34</v>
+        <v>0</v>
       </c>
       <c r="G26" t="s">
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="I26" s="3">
-        <v>46154</v>
+        <v>46178</v>
       </c>
       <c r="J26" s="4">
-        <v>0.66589120370370369</v>
-      </c>
-      <c r="K26" t="s">
-        <v>106</v>
-      </c>
-      <c r="L26" t="s">
-        <v>107</v>
+        <v>0.48898148148148146</v>
+      </c>
+      <c r="K26" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L26" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>1001360993</v>
+        <v>1001364511</v>
       </c>
       <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>120</v>
+      </c>
+      <c r="D27" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="1">
+        <v>738</v>
+      </c>
+      <c r="G27" t="s">
+        <v>0</v>
+      </c>
+      <c r="H27" t="s">
+        <v>4</v>
+      </c>
+      <c r="I27" s="3">
+        <v>46177</v>
+      </c>
+      <c r="J27" s="4">
+        <v>0.63017361111111114</v>
+      </c>
+      <c r="K27" t="s">
+        <v>82</v>
+      </c>
+      <c r="L27" s="10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>1001362595</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" t="s">
+        <v>92</v>
+      </c>
+      <c r="E28" t="s">
+        <v>3</v>
+      </c>
+      <c r="F28" s="1">
+        <v>128.9</v>
+      </c>
+      <c r="G28" t="s">
+        <v>0</v>
+      </c>
+      <c r="H28" t="s">
+        <v>7</v>
+      </c>
+      <c r="I28" s="3">
+        <v>46164</v>
+      </c>
+      <c r="J28" s="4">
+        <v>0.57401620370370365</v>
+      </c>
+      <c r="K28" t="s">
+        <v>82</v>
+      </c>
+      <c r="L28" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>1001362595</v>
+      </c>
+      <c r="B29">
         <v>2</v>
       </c>
-      <c r="C27" t="s">
-        <v>102</v>
-      </c>
-      <c r="D27" t="s">
-        <v>105</v>
-      </c>
-      <c r="E27" t="s">
-        <v>3</v>
-      </c>
-      <c r="F27" s="1">
-        <v>586.66</v>
-      </c>
-      <c r="G27" t="s">
-        <v>0</v>
-      </c>
-      <c r="H27" t="s">
-        <v>104</v>
-      </c>
-      <c r="I27" s="3">
-        <v>46154</v>
-      </c>
-      <c r="J27" s="4">
-        <v>0.6667939814814815</v>
-      </c>
-      <c r="K27" t="s">
-        <v>106</v>
-      </c>
-      <c r="L27" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="2">
-        <v>1001360515</v>
-      </c>
-      <c r="B28" s="2">
-        <v>1</v>
-      </c>
-      <c r="C28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D28" t="s">
-        <v>2</v>
-      </c>
-      <c r="E28" t="s">
-        <v>3</v>
-      </c>
-      <c r="F28" s="1">
-        <v>0</v>
-      </c>
-      <c r="G28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H28" t="s">
-        <v>4</v>
-      </c>
-      <c r="I28" s="3">
-        <v>46153</v>
-      </c>
-      <c r="J28" s="4">
-        <v>0.43606481481481479</v>
-      </c>
-      <c r="K28" t="s">
-        <v>90</v>
-      </c>
-      <c r="L28" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="2">
-        <v>1001359403</v>
-      </c>
-      <c r="B29" s="2">
-        <v>1</v>
-      </c>
       <c r="C29" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="E29" t="s">
         <v>3</v>
       </c>
       <c r="F29" s="1">
-        <v>296.16000000000003</v>
+        <v>115.3</v>
       </c>
       <c r="G29" t="s">
         <v>0</v>
@@ -1968,10 +2004,10 @@
         <v>7</v>
       </c>
       <c r="I29" s="3">
-        <v>46146</v>
+        <v>46164</v>
       </c>
       <c r="J29" s="4">
-        <v>0.35246527777777775</v>
+        <v>0.5740277777777778</v>
       </c>
       <c r="K29" t="s">
         <v>82</v>
@@ -1981,23 +2017,23 @@
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="2">
-        <v>1001358440</v>
-      </c>
-      <c r="B30" s="2">
+      <c r="A30">
+        <v>1001361760</v>
+      </c>
+      <c r="B30">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="D30" t="s">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="E30" t="s">
         <v>3</v>
       </c>
       <c r="F30" s="1">
-        <v>8211</v>
+        <v>2706.88</v>
       </c>
       <c r="G30" t="s">
         <v>0</v>
@@ -2006,10 +2042,10 @@
         <v>4</v>
       </c>
       <c r="I30" s="3">
-        <v>46136</v>
+        <v>46161</v>
       </c>
       <c r="J30" s="4">
-        <v>0.51320601851851855</v>
+        <v>0.40358796296296301</v>
       </c>
       <c r="K30" t="s">
         <v>90</v>
@@ -2019,289 +2055,289 @@
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="2">
-        <v>1001358139</v>
-      </c>
-      <c r="B31" s="2">
-        <v>1</v>
+      <c r="A31">
+        <v>1001361760</v>
+      </c>
+      <c r="B31">
+        <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="D31" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="E31" t="s">
         <v>3</v>
       </c>
       <c r="F31" s="1">
-        <v>296.16000000000003</v>
+        <v>477.84</v>
       </c>
       <c r="G31" t="s">
         <v>0</v>
       </c>
       <c r="H31" t="s">
+        <v>4</v>
+      </c>
+      <c r="I31" s="3">
+        <v>46161</v>
+      </c>
+      <c r="J31" s="4">
+        <v>0.40358796296296301</v>
+      </c>
+      <c r="K31" t="s">
+        <v>90</v>
+      </c>
+      <c r="L31" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>1001361434</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>97</v>
+      </c>
+      <c r="D32" t="s">
+        <v>98</v>
+      </c>
+      <c r="E32" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="1">
+        <v>41.1</v>
+      </c>
+      <c r="G32" t="s">
+        <v>0</v>
+      </c>
+      <c r="H32" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3">
+        <v>46160</v>
+      </c>
+      <c r="J32" s="4">
+        <v>0.34767361111111111</v>
+      </c>
+      <c r="K32" t="s">
+        <v>82</v>
+      </c>
+      <c r="L32" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>1001361434</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33" t="s">
+        <v>97</v>
+      </c>
+      <c r="D33" t="s">
+        <v>99</v>
+      </c>
+      <c r="E33" t="s">
+        <v>3</v>
+      </c>
+      <c r="F33" s="1">
+        <v>82.2</v>
+      </c>
+      <c r="G33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H33" t="s">
+        <v>4</v>
+      </c>
+      <c r="I33" s="3">
+        <v>46160</v>
+      </c>
+      <c r="J33" s="4">
+        <v>0.34847222222222224</v>
+      </c>
+      <c r="K33" t="s">
+        <v>82</v>
+      </c>
+      <c r="L33" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>1001361434</v>
+      </c>
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34" t="s">
+        <v>97</v>
+      </c>
+      <c r="D34" t="s">
+        <v>100</v>
+      </c>
+      <c r="E34" t="s">
+        <v>3</v>
+      </c>
+      <c r="F34" s="1">
+        <v>6.95</v>
+      </c>
+      <c r="G34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H34" t="s">
+        <v>4</v>
+      </c>
+      <c r="I34" s="3">
+        <v>46160</v>
+      </c>
+      <c r="J34" s="4">
+        <v>0.3489814814814815</v>
+      </c>
+      <c r="K34" t="s">
+        <v>82</v>
+      </c>
+      <c r="L34" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>1001361254</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s">
+        <v>101</v>
+      </c>
+      <c r="D35" t="s">
+        <v>93</v>
+      </c>
+      <c r="E35" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="1">
+        <v>172.95</v>
+      </c>
+      <c r="G35" t="s">
+        <v>0</v>
+      </c>
+      <c r="H35" t="s">
         <v>7</v>
       </c>
-      <c r="I31" s="3">
-        <v>46135</v>
-      </c>
-      <c r="J31" s="4">
-        <v>0.40256944444444448</v>
-      </c>
-      <c r="K31" t="s">
+      <c r="I35" s="3">
+        <v>46155</v>
+      </c>
+      <c r="J35" s="4">
+        <v>0.68266203703703709</v>
+      </c>
+      <c r="K35" t="s">
         <v>82</v>
       </c>
-      <c r="L31" t="s">
+      <c r="L35" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="2">
-        <v>1001357792</v>
-      </c>
-      <c r="B32" s="2">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="1">
-        <v>62.02</v>
-      </c>
-      <c r="G32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H32" t="s">
-        <v>4</v>
-      </c>
-      <c r="I32" s="3">
-        <v>46133</v>
-      </c>
-      <c r="J32" s="4">
-        <v>0.59369212962962969</v>
-      </c>
-      <c r="K32" t="s">
-        <v>90</v>
-      </c>
-      <c r="L32" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="2">
-        <v>1001357548</v>
-      </c>
-      <c r="B33" s="2">
-        <v>1</v>
-      </c>
-      <c r="C33" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33" t="s">
-        <v>3</v>
-      </c>
-      <c r="F33" s="1">
-        <v>242</v>
-      </c>
-      <c r="G33" t="s">
-        <v>0</v>
-      </c>
-      <c r="H33" t="s">
-        <v>4</v>
-      </c>
-      <c r="I33" s="3">
-        <v>46132</v>
-      </c>
-      <c r="J33" s="4">
-        <v>0.54353009259259266</v>
-      </c>
-      <c r="K33" t="s">
-        <v>89</v>
-      </c>
-      <c r="L33" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="2">
-        <v>1001357548</v>
-      </c>
-      <c r="B34" s="2">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>1001360993</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>102</v>
+      </c>
+      <c r="D36" t="s">
+        <v>103</v>
+      </c>
+      <c r="E36" t="s">
+        <v>3</v>
+      </c>
+      <c r="F36" s="1">
+        <v>8763.34</v>
+      </c>
+      <c r="G36" t="s">
+        <v>0</v>
+      </c>
+      <c r="H36" t="s">
+        <v>104</v>
+      </c>
+      <c r="I36" s="3">
+        <v>46154</v>
+      </c>
+      <c r="J36" s="4">
+        <v>0.66589120370370369</v>
+      </c>
+      <c r="K36" t="s">
+        <v>106</v>
+      </c>
+      <c r="L36" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>1001360993</v>
+      </c>
+      <c r="B37">
         <v>2</v>
       </c>
-      <c r="C34" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" t="s">
-        <v>15</v>
-      </c>
-      <c r="E34" t="s">
-        <v>3</v>
-      </c>
-      <c r="F34" s="1">
-        <v>25</v>
-      </c>
-      <c r="G34" t="s">
-        <v>0</v>
-      </c>
-      <c r="H34" t="s">
-        <v>4</v>
-      </c>
-      <c r="I34" s="3">
-        <v>46132</v>
-      </c>
-      <c r="J34" s="4">
-        <v>0.54533564814814817</v>
-      </c>
-      <c r="K34" t="s">
-        <v>89</v>
-      </c>
-      <c r="L34" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A35" s="2">
-        <v>1001357548</v>
-      </c>
-      <c r="B35" s="2">
-        <v>3</v>
-      </c>
-      <c r="C35" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" t="s">
-        <v>16</v>
-      </c>
-      <c r="E35" t="s">
-        <v>3</v>
-      </c>
-      <c r="F35" s="1">
-        <v>2250</v>
-      </c>
-      <c r="G35" t="s">
-        <v>0</v>
-      </c>
-      <c r="H35" t="s">
-        <v>4</v>
-      </c>
-      <c r="I35" s="3">
-        <v>46132</v>
-      </c>
-      <c r="J35" s="4">
-        <v>0.546412037037037</v>
-      </c>
-      <c r="K35" t="s">
-        <v>89</v>
-      </c>
-      <c r="L35" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A36" s="2">
-        <v>1001356465</v>
-      </c>
-      <c r="B36" s="2">
-        <v>1</v>
-      </c>
-      <c r="C36" t="s">
-        <v>17</v>
-      </c>
-      <c r="D36" t="s">
-        <v>18</v>
-      </c>
-      <c r="E36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F36" s="1">
-        <v>17.55</v>
-      </c>
-      <c r="G36" t="s">
-        <v>0</v>
-      </c>
-      <c r="H36" t="s">
-        <v>7</v>
-      </c>
-      <c r="I36" s="3">
-        <v>46125</v>
-      </c>
-      <c r="J36" s="4">
-        <v>0.65668981481481481</v>
-      </c>
-      <c r="K36" t="s">
-        <v>82</v>
-      </c>
-      <c r="L36" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A37" s="2">
-        <v>1001356465</v>
-      </c>
-      <c r="B37" s="2">
-        <v>2</v>
-      </c>
       <c r="C37" t="s">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c r="D37" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="E37" t="s">
         <v>3</v>
       </c>
       <c r="F37" s="1">
-        <v>17.55</v>
+        <v>586.66</v>
       </c>
       <c r="G37" t="s">
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>7</v>
+        <v>104</v>
       </c>
       <c r="I37" s="3">
-        <v>46125</v>
+        <v>46154</v>
       </c>
       <c r="J37" s="4">
-        <v>0.65668981481481481</v>
+        <v>0.6667939814814815</v>
       </c>
       <c r="K37" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="L37" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>1001356192</v>
+        <v>1001360515</v>
       </c>
       <c r="B38" s="2">
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E38" t="s">
         <v>3</v>
       </c>
       <c r="F38" s="1">
-        <v>270.5</v>
+        <v>0</v>
       </c>
       <c r="G38" t="s">
         <v>0</v>
@@ -2310,74 +2346,74 @@
         <v>4</v>
       </c>
       <c r="I38" s="3">
-        <v>46122</v>
+        <v>46153</v>
       </c>
       <c r="J38" s="4">
-        <v>0.58597222222222223</v>
+        <v>0.43606481481481479</v>
       </c>
       <c r="K38" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>1001356190</v>
+        <v>1001359403</v>
       </c>
       <c r="B39" s="2">
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D39" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E39" t="s">
         <v>3</v>
       </c>
       <c r="F39" s="1">
-        <v>1359.84</v>
+        <v>296.16000000000003</v>
       </c>
       <c r="G39" t="s">
         <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I39" s="3">
-        <v>46122</v>
+        <v>46146</v>
       </c>
       <c r="J39" s="4">
-        <v>0.58506944444444442</v>
+        <v>0.35246527777777775</v>
       </c>
       <c r="K39" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L39" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>1001355643</v>
+        <v>1001358440</v>
       </c>
       <c r="B40" s="2">
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D40" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E40" t="s">
         <v>3</v>
       </c>
       <c r="F40" s="1">
-        <v>425.29</v>
+        <v>8211</v>
       </c>
       <c r="G40" t="s">
         <v>0</v>
@@ -2386,36 +2422,36 @@
         <v>4</v>
       </c>
       <c r="I40" s="3">
-        <v>46120</v>
+        <v>46136</v>
       </c>
       <c r="J40" s="4">
-        <v>0.58754629629629629</v>
+        <v>0.51320601851851855</v>
       </c>
       <c r="K40" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>1001354025</v>
+        <v>1001358139</v>
       </c>
       <c r="B41" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D41" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="E41" t="s">
         <v>3</v>
       </c>
       <c r="F41" s="1">
-        <v>247</v>
+        <v>296.16000000000003</v>
       </c>
       <c r="G41" t="s">
         <v>0</v>
@@ -2424,10 +2460,10 @@
         <v>7</v>
       </c>
       <c r="I41" s="3">
-        <v>46108</v>
+        <v>46135</v>
       </c>
       <c r="J41" s="4">
-        <v>0.54822916666666666</v>
+        <v>0.40256944444444448</v>
       </c>
       <c r="K41" t="s">
         <v>82</v>
@@ -2438,98 +2474,98 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>1001354025</v>
+        <v>1001357792</v>
       </c>
       <c r="B42" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D42" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E42" t="s">
         <v>3</v>
       </c>
       <c r="F42" s="1">
-        <v>41</v>
+        <v>62.02</v>
       </c>
       <c r="G42" t="s">
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I42" s="3">
-        <v>46108</v>
+        <v>46133</v>
       </c>
       <c r="J42" s="4">
-        <v>0.54866898148148147</v>
+        <v>0.59369212962962969</v>
       </c>
       <c r="K42" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L42" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>1001354025</v>
+        <v>1001357548</v>
       </c>
       <c r="B43" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D43" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E43" t="s">
         <v>3</v>
       </c>
       <c r="F43" s="1">
-        <v>732</v>
+        <v>242</v>
       </c>
       <c r="G43" t="s">
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I43" s="3">
-        <v>46108</v>
+        <v>46132</v>
       </c>
       <c r="J43" s="4">
-        <v>0.5505902777777778</v>
+        <v>0.54353009259259266</v>
       </c>
       <c r="K43" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="L43" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>1001351971</v>
+        <v>1001357548</v>
       </c>
       <c r="B44" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D44" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E44" t="s">
         <v>3</v>
       </c>
       <c r="F44" s="1">
-        <v>1.9</v>
+        <v>25</v>
       </c>
       <c r="G44" t="s">
         <v>0</v>
@@ -2538,36 +2574,36 @@
         <v>4</v>
       </c>
       <c r="I44" s="3">
-        <v>46098</v>
+        <v>46132</v>
       </c>
       <c r="J44" s="4">
-        <v>0.34575231481481478</v>
+        <v>0.54533564814814817</v>
       </c>
       <c r="K44" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L44" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>1001351971</v>
+        <v>1001357548</v>
       </c>
       <c r="B45" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="E45" t="s">
         <v>3</v>
       </c>
       <c r="F45" s="1">
-        <v>1.8</v>
+        <v>2250</v>
       </c>
       <c r="G45" t="s">
         <v>0</v>
@@ -2576,112 +2612,112 @@
         <v>4</v>
       </c>
       <c r="I45" s="3">
-        <v>46098</v>
+        <v>46132</v>
       </c>
       <c r="J45" s="4">
-        <v>0.34575231481481478</v>
+        <v>0.546412037037037</v>
       </c>
       <c r="K45" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L45" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>1001351235</v>
+        <v>1001356465</v>
       </c>
       <c r="B46" s="2">
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D46" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E46" t="s">
         <v>3</v>
       </c>
       <c r="F46" s="1">
-        <v>153.19999999999999</v>
+        <v>17.55</v>
       </c>
       <c r="G46" t="s">
         <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I46" s="3">
-        <v>46092</v>
+        <v>46125</v>
       </c>
       <c r="J46" s="4">
-        <v>0.66688657407407403</v>
+        <v>0.65668981481481481</v>
       </c>
       <c r="K46" t="s">
         <v>82</v>
       </c>
       <c r="L46" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>1001351075</v>
+        <v>1001356465</v>
       </c>
       <c r="B47" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E47" t="s">
         <v>3</v>
       </c>
       <c r="F47" s="1">
-        <v>127</v>
+        <v>17.55</v>
       </c>
       <c r="G47" t="s">
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I47" s="3">
-        <v>46092</v>
+        <v>46125</v>
       </c>
       <c r="J47" s="4">
-        <v>0.40361111111111114</v>
+        <v>0.65668981481481481</v>
       </c>
       <c r="K47" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L47" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>1001351075</v>
+        <v>1001356192</v>
       </c>
       <c r="B48" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D48" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E48" t="s">
         <v>3</v>
       </c>
       <c r="F48" s="1">
-        <v>15</v>
+        <v>270.5</v>
       </c>
       <c r="G48" t="s">
         <v>0</v>
@@ -2690,36 +2726,36 @@
         <v>4</v>
       </c>
       <c r="I48" s="3">
-        <v>46092</v>
+        <v>46122</v>
       </c>
       <c r="J48" s="4">
-        <v>0.6585185185185185</v>
+        <v>0.58597222222222223</v>
       </c>
       <c r="K48" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L48" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>1001351001</v>
+        <v>1001356190</v>
       </c>
       <c r="B49" s="2">
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D49" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="E49" t="s">
         <v>3</v>
       </c>
       <c r="F49" s="1">
-        <v>598.67999999999995</v>
+        <v>1359.84</v>
       </c>
       <c r="G49" t="s">
         <v>0</v>
@@ -2728,10 +2764,10 @@
         <v>4</v>
       </c>
       <c r="I49" s="3">
-        <v>46091</v>
+        <v>46122</v>
       </c>
       <c r="J49" s="4">
-        <v>0.63434027777777779</v>
+        <v>0.58506944444444442</v>
       </c>
       <c r="K49" t="s">
         <v>90</v>
@@ -2742,22 +2778,22 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>1001350675</v>
+        <v>1001355643</v>
       </c>
       <c r="B50" s="2">
         <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="D50" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E50" t="s">
         <v>3</v>
       </c>
       <c r="F50" s="1">
-        <v>600</v>
+        <v>425.29</v>
       </c>
       <c r="G50" t="s">
         <v>0</v>
@@ -2766,150 +2802,150 @@
         <v>4</v>
       </c>
       <c r="I50" s="3">
-        <v>46090</v>
+        <v>46120</v>
       </c>
       <c r="J50" s="4">
-        <v>0.54053240740740738</v>
+        <v>0.58754629629629629</v>
       </c>
       <c r="K50" t="s">
         <v>82</v>
       </c>
       <c r="L50" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>1001350592</v>
+        <v>1001354025</v>
       </c>
       <c r="B51" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D51" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E51" t="s">
         <v>3</v>
       </c>
       <c r="F51" s="1">
-        <v>449.01</v>
+        <v>247</v>
       </c>
       <c r="G51" t="s">
         <v>0</v>
       </c>
       <c r="H51" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I51" s="3">
-        <v>46090</v>
+        <v>46108</v>
       </c>
       <c r="J51" s="4">
-        <v>0.37918981481481479</v>
+        <v>0.54822916666666666</v>
       </c>
       <c r="K51" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L51" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>1001350094</v>
+        <v>1001354025</v>
       </c>
       <c r="B52" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C52" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D52" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="E52" t="s">
         <v>3</v>
       </c>
       <c r="F52" s="1">
-        <v>679.92</v>
+        <v>41</v>
       </c>
       <c r="G52" t="s">
         <v>0</v>
       </c>
       <c r="H52" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I52" s="3">
-        <v>46086</v>
+        <v>46108</v>
       </c>
       <c r="J52" s="4">
-        <v>0.39840277777777783</v>
+        <v>0.54866898148148147</v>
       </c>
       <c r="K52" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L52" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>1001350094</v>
+        <v>1001354025</v>
       </c>
       <c r="B53" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C53" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D53" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E53" t="s">
         <v>3</v>
       </c>
       <c r="F53" s="1">
-        <v>87.14</v>
+        <v>732</v>
       </c>
       <c r="G53" t="s">
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I53" s="3">
-        <v>46086</v>
+        <v>46108</v>
       </c>
       <c r="J53" s="4">
-        <v>0.39840277777777783</v>
+        <v>0.5505902777777778</v>
       </c>
       <c r="K53" t="s">
         <v>82</v>
       </c>
       <c r="L53" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>1001349263</v>
+        <v>1001351971</v>
       </c>
       <c r="B54" s="2">
         <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D54" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="E54" t="s">
         <v>3</v>
       </c>
       <c r="F54" s="1">
-        <v>14.55</v>
+        <v>1.9</v>
       </c>
       <c r="G54" t="s">
         <v>0</v>
@@ -2918,36 +2954,36 @@
         <v>4</v>
       </c>
       <c r="I54" s="3">
-        <v>46083</v>
+        <v>46098</v>
       </c>
       <c r="J54" s="4">
-        <v>0.39340277777777777</v>
+        <v>0.34575231481481478</v>
       </c>
       <c r="K54" t="s">
         <v>84</v>
       </c>
       <c r="L54" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>1001349263</v>
+        <v>1001351971</v>
       </c>
       <c r="B55" s="2">
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D55" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="E55" t="s">
         <v>3</v>
       </c>
       <c r="F55" s="1">
-        <v>15.15</v>
+        <v>1.8</v>
       </c>
       <c r="G55" t="s">
         <v>0</v>
@@ -2956,36 +2992,36 @@
         <v>4</v>
       </c>
       <c r="I55" s="3">
-        <v>46083</v>
+        <v>46098</v>
       </c>
       <c r="J55" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.34575231481481478</v>
       </c>
       <c r="K55" t="s">
         <v>84</v>
       </c>
       <c r="L55" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>1001349263</v>
+        <v>1001351235</v>
       </c>
       <c r="B56" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C56" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D56" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E56" t="s">
         <v>3</v>
       </c>
       <c r="F56" s="1">
-        <v>15.15</v>
+        <v>153.19999999999999</v>
       </c>
       <c r="G56" t="s">
         <v>0</v>
@@ -2994,36 +3030,36 @@
         <v>4</v>
       </c>
       <c r="I56" s="3">
-        <v>46083</v>
+        <v>46092</v>
       </c>
       <c r="J56" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.66688657407407403</v>
       </c>
       <c r="K56" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L56" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>1001349263</v>
+        <v>1001351075</v>
       </c>
       <c r="B57" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D57" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="E57" t="s">
         <v>3</v>
       </c>
       <c r="F57" s="1">
-        <v>14.55</v>
+        <v>127</v>
       </c>
       <c r="G57" t="s">
         <v>0</v>
@@ -3032,36 +3068,36 @@
         <v>4</v>
       </c>
       <c r="I57" s="3">
-        <v>46083</v>
+        <v>46092</v>
       </c>
       <c r="J57" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.40361111111111114</v>
       </c>
       <c r="K57" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L57" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>1001349263</v>
+        <v>1001351075</v>
       </c>
       <c r="B58" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D58" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E58" t="s">
         <v>3</v>
       </c>
       <c r="F58" s="1">
-        <v>14.85</v>
+        <v>15</v>
       </c>
       <c r="G58" t="s">
         <v>0</v>
@@ -3070,36 +3106,36 @@
         <v>4</v>
       </c>
       <c r="I58" s="3">
-        <v>46083</v>
+        <v>46092</v>
       </c>
       <c r="J58" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.6585185185185185</v>
       </c>
       <c r="K58" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L58" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>1001349263</v>
+        <v>1001351001</v>
       </c>
       <c r="B59" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D59" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="E59" t="s">
         <v>3</v>
       </c>
       <c r="F59" s="1">
-        <v>15</v>
+        <v>598.67999999999995</v>
       </c>
       <c r="G59" t="s">
         <v>0</v>
@@ -3108,13 +3144,13 @@
         <v>4</v>
       </c>
       <c r="I59" s="3">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="J59" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.63434027777777779</v>
       </c>
       <c r="K59" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L59" t="s">
         <v>79</v>
@@ -3122,22 +3158,22 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>1001349263</v>
+        <v>1001350675</v>
       </c>
       <c r="B60" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C60" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D60" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E60" t="s">
         <v>3</v>
       </c>
       <c r="F60" s="1">
-        <v>15</v>
+        <v>600</v>
       </c>
       <c r="G60" t="s">
         <v>0</v>
@@ -3146,36 +3182,36 @@
         <v>4</v>
       </c>
       <c r="I60" s="3">
-        <v>46083</v>
+        <v>46090</v>
       </c>
       <c r="J60" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.54053240740740738</v>
       </c>
       <c r="K60" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L60" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>1001349263</v>
+        <v>1001350592</v>
       </c>
       <c r="B61" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C61" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D61" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E61" t="s">
         <v>3</v>
       </c>
       <c r="F61" s="1">
-        <v>14.85</v>
+        <v>449.01</v>
       </c>
       <c r="G61" t="s">
         <v>0</v>
@@ -3184,13 +3220,13 @@
         <v>4</v>
       </c>
       <c r="I61" s="3">
-        <v>46083</v>
+        <v>46090</v>
       </c>
       <c r="J61" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.37918981481481479</v>
       </c>
       <c r="K61" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L61" t="s">
         <v>79</v>
@@ -3198,22 +3234,22 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>1001345614</v>
+        <v>1001350094</v>
       </c>
       <c r="B62" s="2">
         <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D62" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E62" t="s">
         <v>3</v>
       </c>
       <c r="F62" s="1">
-        <v>605</v>
+        <v>679.92</v>
       </c>
       <c r="G62" t="s">
         <v>0</v>
@@ -3222,13 +3258,13 @@
         <v>4</v>
       </c>
       <c r="I62" s="3">
-        <v>46059</v>
+        <v>46086</v>
       </c>
       <c r="J62" s="4">
-        <v>0.6586805555555556</v>
+        <v>0.39840277777777783</v>
       </c>
       <c r="K62" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L62" t="s">
         <v>81</v>
@@ -3236,22 +3272,22 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>1001345614</v>
+        <v>1001350094</v>
       </c>
       <c r="B63" s="2">
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D63" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E63" t="s">
         <v>3</v>
       </c>
       <c r="F63" s="1">
-        <v>154</v>
+        <v>87.14</v>
       </c>
       <c r="G63" t="s">
         <v>0</v>
@@ -3260,10 +3296,10 @@
         <v>4</v>
       </c>
       <c r="I63" s="3">
-        <v>46059</v>
+        <v>46086</v>
       </c>
       <c r="J63" s="4">
-        <v>0.66027777777777774</v>
+        <v>0.39840277777777783</v>
       </c>
       <c r="K63" t="s">
         <v>82</v>
@@ -3274,22 +3310,22 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>1001343034</v>
+        <v>1001349263</v>
       </c>
       <c r="B64" s="2">
         <v>1</v>
       </c>
       <c r="C64" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D64" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E64" t="s">
         <v>3</v>
       </c>
       <c r="F64" s="1">
-        <v>208.6</v>
+        <v>14.55</v>
       </c>
       <c r="G64" t="s">
         <v>0</v>
@@ -3298,36 +3334,36 @@
         <v>4</v>
       </c>
       <c r="I64" s="3">
-        <v>46044</v>
+        <v>46083</v>
       </c>
       <c r="J64" s="4">
-        <v>0.65900462962962958</v>
+        <v>0.39340277777777777</v>
       </c>
       <c r="K64" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L64" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>1001343034</v>
+        <v>1001349263</v>
       </c>
       <c r="B65" s="2">
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D65" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="E65" t="s">
         <v>3</v>
       </c>
       <c r="F65" s="1">
-        <v>20</v>
+        <v>15.15</v>
       </c>
       <c r="G65" t="s">
         <v>0</v>
@@ -3336,36 +3372,36 @@
         <v>4</v>
       </c>
       <c r="I65" s="3">
-        <v>46044</v>
+        <v>46083</v>
       </c>
       <c r="J65" s="4">
-        <v>0.66190972222222222</v>
+        <v>0.39341435185185186</v>
       </c>
       <c r="K65" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L65" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>1001342447</v>
+        <v>1001349263</v>
       </c>
       <c r="B66" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C66" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D66" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="E66" t="s">
         <v>3</v>
       </c>
       <c r="F66" s="1">
-        <v>240</v>
+        <v>15.15</v>
       </c>
       <c r="G66" t="s">
         <v>0</v>
@@ -3374,36 +3410,36 @@
         <v>4</v>
       </c>
       <c r="I66" s="3">
-        <v>46042</v>
+        <v>46083</v>
       </c>
       <c r="J66" s="4">
-        <v>0.54805555555555552</v>
+        <v>0.39341435185185186</v>
       </c>
       <c r="K66" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L66" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
-        <v>1001342447</v>
+        <v>1001349263</v>
       </c>
       <c r="B67" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C67" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D67" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="E67" t="s">
         <v>3</v>
       </c>
       <c r="F67" s="1">
-        <v>8.9499999999999993</v>
+        <v>14.55</v>
       </c>
       <c r="G67" t="s">
         <v>0</v>
@@ -3412,36 +3448,36 @@
         <v>4</v>
       </c>
       <c r="I67" s="3">
-        <v>46042</v>
+        <v>46083</v>
       </c>
       <c r="J67" s="4">
-        <v>0.54859953703703701</v>
+        <v>0.39341435185185186</v>
       </c>
       <c r="K67" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L67" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
-        <v>1001340933</v>
+        <v>1001349263</v>
       </c>
       <c r="B68" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C68" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D68" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E68" t="s">
         <v>3</v>
       </c>
       <c r="F68" s="1">
-        <v>150.47999999999999</v>
+        <v>14.85</v>
       </c>
       <c r="G68" t="s">
         <v>0</v>
@@ -3450,21 +3486,401 @@
         <v>4</v>
       </c>
       <c r="I68" s="3">
-        <v>46034</v>
+        <v>46083</v>
       </c>
       <c r="J68" s="4">
-        <v>0.40950231481481486</v>
+        <v>0.39341435185185186</v>
       </c>
       <c r="K68" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L68" t="s">
         <v>79</v>
       </c>
     </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A69" s="2">
+        <v>1001349263</v>
+      </c>
+      <c r="B69" s="2">
+        <v>6</v>
+      </c>
+      <c r="C69" t="s">
+        <v>45</v>
+      </c>
+      <c r="D69" t="s">
+        <v>51</v>
+      </c>
+      <c r="E69" t="s">
+        <v>3</v>
+      </c>
+      <c r="F69" s="1">
+        <v>15</v>
+      </c>
+      <c r="G69" t="s">
+        <v>0</v>
+      </c>
+      <c r="H69" t="s">
+        <v>4</v>
+      </c>
+      <c r="I69" s="3">
+        <v>46083</v>
+      </c>
+      <c r="J69" s="4">
+        <v>0.39341435185185186</v>
+      </c>
+      <c r="K69" t="s">
+        <v>84</v>
+      </c>
+      <c r="L69" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A70" s="2">
+        <v>1001349263</v>
+      </c>
+      <c r="B70" s="2">
+        <v>7</v>
+      </c>
+      <c r="C70" t="s">
+        <v>45</v>
+      </c>
+      <c r="D70" t="s">
+        <v>52</v>
+      </c>
+      <c r="E70" t="s">
+        <v>3</v>
+      </c>
+      <c r="F70" s="1">
+        <v>15</v>
+      </c>
+      <c r="G70" t="s">
+        <v>0</v>
+      </c>
+      <c r="H70" t="s">
+        <v>4</v>
+      </c>
+      <c r="I70" s="3">
+        <v>46083</v>
+      </c>
+      <c r="J70" s="4">
+        <v>0.39341435185185186</v>
+      </c>
+      <c r="K70" t="s">
+        <v>84</v>
+      </c>
+      <c r="L70" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A71" s="2">
+        <v>1001349263</v>
+      </c>
+      <c r="B71" s="2">
+        <v>8</v>
+      </c>
+      <c r="C71" t="s">
+        <v>45</v>
+      </c>
+      <c r="D71" t="s">
+        <v>53</v>
+      </c>
+      <c r="E71" t="s">
+        <v>3</v>
+      </c>
+      <c r="F71" s="1">
+        <v>14.85</v>
+      </c>
+      <c r="G71" t="s">
+        <v>0</v>
+      </c>
+      <c r="H71" t="s">
+        <v>4</v>
+      </c>
+      <c r="I71" s="3">
+        <v>46083</v>
+      </c>
+      <c r="J71" s="4">
+        <v>0.39341435185185186</v>
+      </c>
+      <c r="K71" t="s">
+        <v>84</v>
+      </c>
+      <c r="L71" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A72" s="2">
+        <v>1001345614</v>
+      </c>
+      <c r="B72" s="2">
+        <v>1</v>
+      </c>
+      <c r="C72" t="s">
+        <v>54</v>
+      </c>
+      <c r="D72" t="s">
+        <v>55</v>
+      </c>
+      <c r="E72" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="1">
+        <v>605</v>
+      </c>
+      <c r="G72" t="s">
+        <v>0</v>
+      </c>
+      <c r="H72" t="s">
+        <v>4</v>
+      </c>
+      <c r="I72" s="3">
+        <v>46059</v>
+      </c>
+      <c r="J72" s="4">
+        <v>0.6586805555555556</v>
+      </c>
+      <c r="K72" t="s">
+        <v>82</v>
+      </c>
+      <c r="L72" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A73" s="2">
+        <v>1001345614</v>
+      </c>
+      <c r="B73" s="2">
+        <v>2</v>
+      </c>
+      <c r="C73" t="s">
+        <v>54</v>
+      </c>
+      <c r="D73" t="s">
+        <v>56</v>
+      </c>
+      <c r="E73" t="s">
+        <v>3</v>
+      </c>
+      <c r="F73" s="1">
+        <v>154</v>
+      </c>
+      <c r="G73" t="s">
+        <v>0</v>
+      </c>
+      <c r="H73" t="s">
+        <v>4</v>
+      </c>
+      <c r="I73" s="3">
+        <v>46059</v>
+      </c>
+      <c r="J73" s="4">
+        <v>0.66027777777777774</v>
+      </c>
+      <c r="K73" t="s">
+        <v>82</v>
+      </c>
+      <c r="L73" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A74" s="2">
+        <v>1001343034</v>
+      </c>
+      <c r="B74" s="2">
+        <v>1</v>
+      </c>
+      <c r="C74" t="s">
+        <v>57</v>
+      </c>
+      <c r="D74" t="s">
+        <v>58</v>
+      </c>
+      <c r="E74" t="s">
+        <v>3</v>
+      </c>
+      <c r="F74" s="1">
+        <v>208.6</v>
+      </c>
+      <c r="G74" t="s">
+        <v>0</v>
+      </c>
+      <c r="H74" t="s">
+        <v>4</v>
+      </c>
+      <c r="I74" s="3">
+        <v>46044</v>
+      </c>
+      <c r="J74" s="4">
+        <v>0.65900462962962958</v>
+      </c>
+      <c r="K74" t="s">
+        <v>88</v>
+      </c>
+      <c r="L74" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A75" s="2">
+        <v>1001343034</v>
+      </c>
+      <c r="B75" s="2">
+        <v>2</v>
+      </c>
+      <c r="C75" t="s">
+        <v>57</v>
+      </c>
+      <c r="D75" t="s">
+        <v>59</v>
+      </c>
+      <c r="E75" t="s">
+        <v>3</v>
+      </c>
+      <c r="F75" s="1">
+        <v>20</v>
+      </c>
+      <c r="G75" t="s">
+        <v>0</v>
+      </c>
+      <c r="H75" t="s">
+        <v>4</v>
+      </c>
+      <c r="I75" s="3">
+        <v>46044</v>
+      </c>
+      <c r="J75" s="4">
+        <v>0.66190972222222222</v>
+      </c>
+      <c r="K75" t="s">
+        <v>88</v>
+      </c>
+      <c r="L75" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A76" s="2">
+        <v>1001342447</v>
+      </c>
+      <c r="B76" s="2">
+        <v>1</v>
+      </c>
+      <c r="C76" t="s">
+        <v>60</v>
+      </c>
+      <c r="D76" t="s">
+        <v>61</v>
+      </c>
+      <c r="E76" t="s">
+        <v>3</v>
+      </c>
+      <c r="F76" s="1">
+        <v>240</v>
+      </c>
+      <c r="G76" t="s">
+        <v>0</v>
+      </c>
+      <c r="H76" t="s">
+        <v>4</v>
+      </c>
+      <c r="I76" s="3">
+        <v>46042</v>
+      </c>
+      <c r="J76" s="4">
+        <v>0.54805555555555552</v>
+      </c>
+      <c r="K76" t="s">
+        <v>88</v>
+      </c>
+      <c r="L76" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A77" s="2">
+        <v>1001342447</v>
+      </c>
+      <c r="B77" s="2">
+        <v>2</v>
+      </c>
+      <c r="C77" t="s">
+        <v>60</v>
+      </c>
+      <c r="D77" t="s">
+        <v>62</v>
+      </c>
+      <c r="E77" t="s">
+        <v>3</v>
+      </c>
+      <c r="F77" s="1">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="G77" t="s">
+        <v>0</v>
+      </c>
+      <c r="H77" t="s">
+        <v>4</v>
+      </c>
+      <c r="I77" s="3">
+        <v>46042</v>
+      </c>
+      <c r="J77" s="4">
+        <v>0.54859953703703701</v>
+      </c>
+      <c r="K77" t="s">
+        <v>88</v>
+      </c>
+      <c r="L77" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A78" s="2">
+        <v>1001340933</v>
+      </c>
+      <c r="B78" s="2">
+        <v>1</v>
+      </c>
+      <c r="C78" t="s">
+        <v>63</v>
+      </c>
+      <c r="D78" t="s">
+        <v>64</v>
+      </c>
+      <c r="E78" t="s">
+        <v>3</v>
+      </c>
+      <c r="F78" s="1">
+        <v>150.47999999999999</v>
+      </c>
+      <c r="G78" t="s">
+        <v>0</v>
+      </c>
+      <c r="H78" t="s">
+        <v>4</v>
+      </c>
+      <c r="I78" s="3">
+        <v>46034</v>
+      </c>
+      <c r="J78" s="4">
+        <v>0.40950231481481486</v>
+      </c>
+      <c r="K78" t="s">
+        <v>90</v>
+      </c>
+      <c r="L78" t="s">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M66" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M68">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M78">
       <sortCondition descending="1" ref="A1:A66"/>
     </sortState>
   </autoFilter>

--- a/data/bestellingen 7193 2026_latest.xlsx
+++ b/data/bestellingen 7193 2026_latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\R\Bestellingen\shiny\7180\7180\jorgpeter-orders7180\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E6D559-F649-4505-AD65-E1AE431E2BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0EA621D-D103-450F-823D-4BB87231315A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$80</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="145">
   <si>
     <t>EUR</t>
   </si>
@@ -457,6 +457,12 @@
   </si>
   <si>
     <t>calcium-magnesium phytate [361 (0.5 kg)</t>
+  </si>
+  <si>
+    <t>C117993 18.08.2026 7193 Magazijn</t>
+  </si>
+  <si>
+    <t>C117993 10.08.2026 7193 Magazijn</t>
   </si>
 </sst>
 </file>
@@ -894,7 +900,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -954,51 +960,51 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>1001372863</v>
+        <v>1001375362</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="D2" t="s">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="1">
-        <v>87.14</v>
+        <v>247.88</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I2" s="3">
-        <v>46234</v>
+        <v>46252</v>
       </c>
       <c r="J2" s="4">
-        <v>0.53832175925925929</v>
+        <v>0.45155092592592588</v>
       </c>
       <c r="K2" t="s">
         <v>82</v>
       </c>
       <c r="L2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>1001371561</v>
+        <v>1001373989</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="D3" t="s">
         <v>128</v>
@@ -1007,7 +1013,7 @@
         <v>3</v>
       </c>
       <c r="F3" s="1">
-        <v>60.92</v>
+        <v>121.84</v>
       </c>
       <c r="G3" t="s">
         <v>0</v>
@@ -1016,10 +1022,10 @@
         <v>7</v>
       </c>
       <c r="I3" s="3">
-        <v>46225</v>
+        <v>46244</v>
       </c>
       <c r="J3" s="4">
-        <v>0.64002314814814809</v>
+        <v>0.40568287037037037</v>
       </c>
       <c r="K3" t="s">
         <v>82</v>
@@ -1030,22 +1036,22 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>1001370654</v>
+        <v>1001372863</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="E4" t="s">
-        <v>135</v>
+        <v>3</v>
       </c>
       <c r="F4" s="1">
-        <v>10880</v>
+        <v>87.14</v>
       </c>
       <c r="G4" t="s">
         <v>0</v>
@@ -1054,74 +1060,74 @@
         <v>4</v>
       </c>
       <c r="I4" s="3">
-        <v>46219</v>
+        <v>46234</v>
       </c>
       <c r="J4" s="4">
-        <v>0.48186342592592596</v>
+        <v>0.53832175925925929</v>
       </c>
       <c r="K4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>1001370654</v>
+        <v>1001371561</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E5" t="s">
-        <v>135</v>
+        <v>3</v>
       </c>
       <c r="F5" s="1">
-        <v>198</v>
+        <v>60.92</v>
       </c>
       <c r="G5" t="s">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I5" s="3">
-        <v>46219</v>
+        <v>46225</v>
       </c>
       <c r="J5" s="4">
-        <v>0.48271990740740739</v>
+        <v>0.64002314814814809</v>
       </c>
       <c r="K5" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>1001370526</v>
+        <v>1001370654</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D6" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E6" t="s">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="F6" s="1">
-        <v>138.4</v>
+        <v>10880</v>
       </c>
       <c r="G6" t="s">
         <v>0</v>
@@ -1130,36 +1136,36 @@
         <v>4</v>
       </c>
       <c r="I6" s="3">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="J6" s="4">
-        <v>0.63928240740740738</v>
+        <v>0.48186342592592596</v>
       </c>
       <c r="K6" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="L6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>1001370183</v>
+        <v>1001370654</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D7" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="E7" t="s">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="F7" s="1">
-        <v>84.51</v>
+        <v>198</v>
       </c>
       <c r="G7" t="s">
         <v>0</v>
@@ -1168,36 +1174,36 @@
         <v>4</v>
       </c>
       <c r="I7" s="3">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="J7" s="4">
-        <v>0.46013888888888888</v>
+        <v>0.48271990740740739</v>
       </c>
       <c r="K7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>1001370183</v>
+        <v>1001370526</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="E8" t="s">
         <v>3</v>
       </c>
       <c r="F8" s="1">
-        <v>5</v>
+        <v>138.4</v>
       </c>
       <c r="G8" t="s">
         <v>0</v>
@@ -1206,36 +1212,36 @@
         <v>4</v>
       </c>
       <c r="I8" s="3">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="J8" s="4">
-        <v>0.46013888888888888</v>
+        <v>0.63928240740740738</v>
       </c>
       <c r="K8" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L8" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>1001369827</v>
+        <v>1001370183</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D9" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E9" t="s">
         <v>3</v>
       </c>
       <c r="F9" s="1">
-        <v>89.25</v>
+        <v>84.51</v>
       </c>
       <c r="G9" t="s">
         <v>0</v>
@@ -1244,10 +1250,10 @@
         <v>4</v>
       </c>
       <c r="I9" s="3">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="J9" s="4">
-        <v>0.60623842592592592</v>
+        <v>0.46013888888888888</v>
       </c>
       <c r="K9" t="s">
         <v>90</v>
@@ -1258,13 +1264,13 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>1001369827</v>
+        <v>1001370183</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D10" t="s">
         <v>114</v>
@@ -1282,10 +1288,10 @@
         <v>4</v>
       </c>
       <c r="I10" s="3">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="J10" s="4">
-        <v>0.60623842592592592</v>
+        <v>0.46013888888888888</v>
       </c>
       <c r="K10" t="s">
         <v>90</v>
@@ -1296,7 +1302,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>1001369807</v>
+        <v>1001369827</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -1305,13 +1311,13 @@
         <v>140</v>
       </c>
       <c r="D11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E11" t="s">
         <v>3</v>
       </c>
       <c r="F11" s="1">
-        <v>172</v>
+        <v>89.25</v>
       </c>
       <c r="G11" t="s">
         <v>0</v>
@@ -1323,7 +1329,7 @@
         <v>46213</v>
       </c>
       <c r="J11" s="4">
-        <v>0.56239583333333332</v>
+        <v>0.60623842592592592</v>
       </c>
       <c r="K11" t="s">
         <v>90</v>
@@ -1334,40 +1340,40 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>1001368508</v>
+        <v>1001369827</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="D12" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
         <v>3</v>
       </c>
       <c r="F12" s="1">
-        <v>121.84</v>
+        <v>5</v>
       </c>
       <c r="G12" t="s">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I12" s="3">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="J12" s="4">
-        <v>0.54736111111111108</v>
+        <v>0.60623842592592592</v>
       </c>
       <c r="K12" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
@@ -3878,10 +3884,86 @@
         <v>79</v>
       </c>
     </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>1001369807</v>
+      </c>
+      <c r="B79">
+        <v>1</v>
+      </c>
+      <c r="C79" t="s">
+        <v>140</v>
+      </c>
+      <c r="D79" t="s">
+        <v>142</v>
+      </c>
+      <c r="E79" t="s">
+        <v>3</v>
+      </c>
+      <c r="F79" s="1">
+        <v>172</v>
+      </c>
+      <c r="G79" t="s">
+        <v>0</v>
+      </c>
+      <c r="H79" t="s">
+        <v>4</v>
+      </c>
+      <c r="I79" s="3">
+        <v>46213</v>
+      </c>
+      <c r="J79" s="4">
+        <v>0.56239583333333332</v>
+      </c>
+      <c r="K79" t="s">
+        <v>90</v>
+      </c>
+      <c r="L79" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>1001368508</v>
+      </c>
+      <c r="B80">
+        <v>1</v>
+      </c>
+      <c r="C80" t="s">
+        <v>127</v>
+      </c>
+      <c r="D80" t="s">
+        <v>128</v>
+      </c>
+      <c r="E80" t="s">
+        <v>3</v>
+      </c>
+      <c r="F80" s="1">
+        <v>121.84</v>
+      </c>
+      <c r="G80" t="s">
+        <v>0</v>
+      </c>
+      <c r="H80" t="s">
+        <v>7</v>
+      </c>
+      <c r="I80" s="3">
+        <v>46205</v>
+      </c>
+      <c r="J80" s="4">
+        <v>0.54736111111111108</v>
+      </c>
+      <c r="K80" t="s">
+        <v>82</v>
+      </c>
+      <c r="L80" t="s">
+        <v>83</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M66" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M78">
-      <sortCondition descending="1" ref="A1:A66"/>
+  <autoFilter ref="A1:M80" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M80">
+      <sortCondition descending="1" ref="A1:A78"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="0" type="noConversion"/>

--- a/data/bestellingen 7193 2026_latest.xlsx
+++ b/data/bestellingen 7193 2026_latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\R\Bestellingen\shiny\7180\7180\jorgpeter-orders7180\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0EA621D-D103-450F-823D-4BB87231315A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B9E815D-3A3E-4875-9E8F-8A6C7C0663C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="147">
   <si>
     <t>EUR</t>
   </si>
@@ -463,6 +463,12 @@
   </si>
   <si>
     <t>C117993 10.08.2026 7193 Magazijn</t>
+  </si>
+  <si>
+    <t>C117993 07.09.2026 7193 magazijn</t>
+  </si>
+  <si>
+    <t>C101257 03.09.2026 7193 Xanthe</t>
   </si>
 </sst>
 </file>
@@ -900,7 +906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -960,13 +966,13 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>1001375362</v>
+        <v>1001378453</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D2" t="s">
         <v>93</v>
@@ -975,7 +981,7 @@
         <v>3</v>
       </c>
       <c r="F2" s="1">
-        <v>247.88</v>
+        <v>123.94</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
@@ -984,10 +990,10 @@
         <v>7</v>
       </c>
       <c r="I2" s="3">
-        <v>46252</v>
+        <v>46272</v>
       </c>
       <c r="J2" s="4">
-        <v>0.45155092592592588</v>
+        <v>0.39587962962962964</v>
       </c>
       <c r="K2" t="s">
         <v>82</v>
@@ -998,13 +1004,13 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>1001373989</v>
+        <v>1001378453</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D3" t="s">
         <v>128</v>
@@ -1013,7 +1019,7 @@
         <v>3</v>
       </c>
       <c r="F3" s="1">
-        <v>121.84</v>
+        <v>243.68</v>
       </c>
       <c r="G3" t="s">
         <v>0</v>
@@ -1022,10 +1028,10 @@
         <v>7</v>
       </c>
       <c r="I3" s="3">
-        <v>46244</v>
+        <v>46272</v>
       </c>
       <c r="J3" s="4">
-        <v>0.40568287037037037</v>
+        <v>0.39587962962962964</v>
       </c>
       <c r="K3" t="s">
         <v>82</v>
@@ -1036,22 +1042,22 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>1001372863</v>
+        <v>1001378010</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="D4" t="s">
-        <v>132</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="1">
-        <v>87.14</v>
+        <v>150.47999999999999</v>
       </c>
       <c r="G4" t="s">
         <v>0</v>
@@ -1060,13 +1066,13 @@
         <v>4</v>
       </c>
       <c r="I4" s="3">
-        <v>46234</v>
+        <v>46268</v>
       </c>
       <c r="J4" s="4">
-        <v>0.53832175925925929</v>
+        <v>0.40054398148148151</v>
       </c>
       <c r="K4" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L4" t="s">
         <v>81</v>
@@ -1074,22 +1080,22 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>1001371561</v>
+        <v>1001375362</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="1">
-        <v>60.92</v>
+        <v>247.88</v>
       </c>
       <c r="G5" t="s">
         <v>0</v>
@@ -1098,10 +1104,10 @@
         <v>7</v>
       </c>
       <c r="I5" s="3">
-        <v>46225</v>
+        <v>46252</v>
       </c>
       <c r="J5" s="4">
-        <v>0.64002314814814809</v>
+        <v>0.45155092592592588</v>
       </c>
       <c r="K5" t="s">
         <v>82</v>
@@ -1112,60 +1118,60 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>1001370654</v>
+        <v>1001373989</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="D6" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E6" t="s">
-        <v>135</v>
+        <v>3</v>
       </c>
       <c r="F6" s="1">
-        <v>10880</v>
+        <v>121.84</v>
       </c>
       <c r="G6" t="s">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I6" s="3">
-        <v>46219</v>
+        <v>46244</v>
       </c>
       <c r="J6" s="4">
-        <v>0.48186342592592596</v>
+        <v>0.40568287037037037</v>
       </c>
       <c r="K6" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>1001370654</v>
+        <v>1001372863</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D7" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="E7" t="s">
-        <v>135</v>
+        <v>3</v>
       </c>
       <c r="F7" s="1">
-        <v>198</v>
+        <v>87.14</v>
       </c>
       <c r="G7" t="s">
         <v>0</v>
@@ -1174,74 +1180,74 @@
         <v>4</v>
       </c>
       <c r="I7" s="3">
-        <v>46219</v>
+        <v>46234</v>
       </c>
       <c r="J7" s="4">
-        <v>0.48271990740740739</v>
+        <v>0.53832175925925929</v>
       </c>
       <c r="K7" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>1001370526</v>
+        <v>1001371561</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D8" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="E8" t="s">
         <v>3</v>
       </c>
       <c r="F8" s="1">
-        <v>138.4</v>
+        <v>60.92</v>
       </c>
       <c r="G8" t="s">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I8" s="3">
-        <v>46218</v>
+        <v>46225</v>
       </c>
       <c r="J8" s="4">
-        <v>0.63928240740740738</v>
+        <v>0.64002314814814809</v>
       </c>
       <c r="K8" t="s">
         <v>82</v>
       </c>
       <c r="L8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>1001370183</v>
+        <v>1001370654</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D9" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="E9" t="s">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="F9" s="1">
-        <v>84.51</v>
+        <v>10880</v>
       </c>
       <c r="G9" t="s">
         <v>0</v>
@@ -1250,36 +1256,36 @@
         <v>4</v>
       </c>
       <c r="I9" s="3">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="J9" s="4">
-        <v>0.46013888888888888</v>
+        <v>0.48186342592592596</v>
       </c>
       <c r="K9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>1001370183</v>
+        <v>1001370654</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E10" t="s">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="F10" s="1">
-        <v>5</v>
+        <v>198</v>
       </c>
       <c r="G10" t="s">
         <v>0</v>
@@ -1288,36 +1294,36 @@
         <v>4</v>
       </c>
       <c r="I10" s="3">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="J10" s="4">
-        <v>0.46013888888888888</v>
+        <v>0.48271990740740739</v>
       </c>
       <c r="K10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L10" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>1001369827</v>
+        <v>1001370526</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D11" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E11" t="s">
         <v>3</v>
       </c>
       <c r="F11" s="1">
-        <v>89.25</v>
+        <v>138.4</v>
       </c>
       <c r="G11" t="s">
         <v>0</v>
@@ -1326,36 +1332,36 @@
         <v>4</v>
       </c>
       <c r="I11" s="3">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="J11" s="4">
-        <v>0.60623842592592592</v>
+        <v>0.63928240740740738</v>
       </c>
       <c r="K11" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>1001369827</v>
+        <v>1001370183</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="E12" t="s">
         <v>3</v>
       </c>
       <c r="F12" s="1">
-        <v>5</v>
+        <v>84.51</v>
       </c>
       <c r="G12" t="s">
         <v>0</v>
@@ -1364,36 +1370,36 @@
         <v>4</v>
       </c>
       <c r="I12" s="3">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="J12" s="4">
-        <v>0.60623842592592592</v>
+        <v>0.46013888888888888</v>
       </c>
       <c r="K12" t="s">
         <v>90</v>
       </c>
       <c r="L12" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>1001367739</v>
+        <v>1001370183</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="D13" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="E13" t="s">
         <v>3</v>
       </c>
       <c r="F13" s="1">
-        <v>123.01</v>
+        <v>5</v>
       </c>
       <c r="G13" t="s">
         <v>0</v>
@@ -1402,36 +1408,36 @@
         <v>4</v>
       </c>
       <c r="I13" s="3">
-        <v>46202</v>
+        <v>46217</v>
       </c>
       <c r="J13" s="4">
-        <v>0.38149305555555557</v>
+        <v>0.46013888888888888</v>
       </c>
       <c r="K13" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L13" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>1001366912</v>
+        <v>1001369827</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="D14" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="E14" t="s">
         <v>3</v>
       </c>
       <c r="F14" s="1">
-        <v>704</v>
+        <v>89.25</v>
       </c>
       <c r="G14" t="s">
         <v>0</v>
@@ -1440,36 +1446,36 @@
         <v>4</v>
       </c>
       <c r="I14" s="3">
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="J14" s="4">
-        <v>0.63238425925925923</v>
+        <v>0.60623842592592592</v>
       </c>
       <c r="K14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>1001366912</v>
+        <v>1001369827</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
         <v>3</v>
       </c>
       <c r="F15" s="1">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G15" t="s">
         <v>0</v>
@@ -1478,150 +1484,150 @@
         <v>4</v>
       </c>
       <c r="I15" s="3">
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="J15" s="4">
-        <v>0.6334953703703704</v>
+        <v>0.60623842592592592</v>
       </c>
       <c r="K15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L15" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>1001366367</v>
+        <v>1001369807</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="E16" t="s">
         <v>3</v>
       </c>
       <c r="F16" s="1">
-        <v>322.25</v>
+        <v>172</v>
       </c>
       <c r="G16" t="s">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I16" s="3">
-        <v>46190</v>
+        <v>46213</v>
       </c>
       <c r="J16" s="4">
-        <v>0.64398148148148149</v>
+        <v>0.56239583333333332</v>
       </c>
       <c r="K16" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L16" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>1001365392</v>
+        <v>1001368508</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="D17" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="E17" t="s">
         <v>3</v>
       </c>
       <c r="F17" s="1">
-        <v>1048</v>
+        <v>121.84</v>
       </c>
       <c r="G17" t="s">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I17" s="3">
-        <v>46184</v>
+        <v>46205</v>
       </c>
       <c r="J17" s="4">
-        <v>0.33641203703703698</v>
-      </c>
-      <c r="K17" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="L17" s="10" t="s">
-        <v>81</v>
+        <v>0.54736111111111108</v>
+      </c>
+      <c r="K17" t="s">
+        <v>82</v>
+      </c>
+      <c r="L17" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>1001365168</v>
+        <v>1001367739</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="D18" t="s">
-        <v>93</v>
+        <v>130</v>
       </c>
       <c r="E18" t="s">
         <v>3</v>
       </c>
       <c r="F18" s="1">
-        <v>288.25</v>
+        <v>123.01</v>
       </c>
       <c r="G18" t="s">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I18" s="3">
-        <v>46182</v>
+        <v>46202</v>
       </c>
       <c r="J18" s="4">
-        <v>0.65709490740740739</v>
-      </c>
-      <c r="K18" s="10" t="s">
+        <v>0.38149305555555557</v>
+      </c>
+      <c r="K18" t="s">
         <v>82</v>
       </c>
-      <c r="L18" s="10" t="s">
-        <v>83</v>
+      <c r="L18" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>1001364804</v>
+        <v>1001366912</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="D19" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="E19" t="s">
         <v>3</v>
       </c>
       <c r="F19" s="1">
-        <v>208.6</v>
+        <v>704</v>
       </c>
       <c r="G19" t="s">
         <v>0</v>
@@ -1630,36 +1636,36 @@
         <v>4</v>
       </c>
       <c r="I19" s="3">
-        <v>46181</v>
+        <v>46195</v>
       </c>
       <c r="J19" s="4">
-        <v>0.45427083333333335</v>
-      </c>
-      <c r="K19" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="L19" s="10" t="s">
-        <v>122</v>
+        <v>0.63238425925925923</v>
+      </c>
+      <c r="K19" t="s">
+        <v>89</v>
+      </c>
+      <c r="L19" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>1001364804</v>
+        <v>1001366912</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="D20" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E20" t="s">
         <v>3</v>
       </c>
       <c r="F20" s="1">
-        <v>155.69999999999999</v>
+        <v>28</v>
       </c>
       <c r="G20" t="s">
         <v>0</v>
@@ -1668,74 +1674,74 @@
         <v>4</v>
       </c>
       <c r="I20" s="3">
-        <v>46181</v>
+        <v>46195</v>
       </c>
       <c r="J20" s="4">
-        <v>0.45427083333333335</v>
-      </c>
-      <c r="K20" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="L20" s="10" t="s">
-        <v>122</v>
+        <v>0.6334953703703704</v>
+      </c>
+      <c r="K20" t="s">
+        <v>89</v>
+      </c>
+      <c r="L20" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>1001364804</v>
+        <v>1001366367</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="D21" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="E21" t="s">
         <v>3</v>
       </c>
       <c r="F21" s="1">
-        <v>5</v>
+        <v>322.25</v>
       </c>
       <c r="G21" t="s">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I21" s="3">
-        <v>46181</v>
+        <v>46190</v>
       </c>
       <c r="J21" s="4">
-        <v>0.45427083333333335</v>
-      </c>
-      <c r="K21" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="L21" s="10" t="s">
-        <v>122</v>
+        <v>0.64398148148148149</v>
+      </c>
+      <c r="K21" t="s">
+        <v>82</v>
+      </c>
+      <c r="L21" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>1001364684</v>
+        <v>1001365392</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E22" t="s">
         <v>3</v>
       </c>
       <c r="F22" s="1">
-        <v>708.95</v>
+        <v>1048</v>
       </c>
       <c r="G22" t="s">
         <v>0</v>
@@ -1744,74 +1750,74 @@
         <v>4</v>
       </c>
       <c r="I22" s="3">
-        <v>46178</v>
+        <v>46184</v>
       </c>
       <c r="J22" s="4">
-        <v>0.55635416666666659</v>
+        <v>0.33641203703703698</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>1001364656</v>
+        <v>1001365168</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D23" t="s">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="E23" t="s">
         <v>3</v>
       </c>
       <c r="F23" s="1">
-        <v>242</v>
+        <v>288.25</v>
       </c>
       <c r="G23" t="s">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I23" s="3">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="J23" s="4">
-        <v>0.48500000000000004</v>
+        <v>0.65709490740740739</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>1001364656</v>
+        <v>1001364804</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D24" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E24" t="s">
         <v>3</v>
       </c>
       <c r="F24" s="1">
-        <v>25</v>
+        <v>208.6</v>
       </c>
       <c r="G24" t="s">
         <v>0</v>
@@ -1820,36 +1826,36 @@
         <v>4</v>
       </c>
       <c r="I24" s="3">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="J24" s="4">
-        <v>0.48591435185185183</v>
+        <v>0.45427083333333335</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>1001364656</v>
+        <v>1001364804</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D25" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E25" t="s">
         <v>3</v>
       </c>
       <c r="F25" s="1">
-        <v>2250</v>
+        <v>155.69999999999999</v>
       </c>
       <c r="G25" t="s">
         <v>0</v>
@@ -1858,36 +1864,36 @@
         <v>4</v>
       </c>
       <c r="I25" s="3">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="J25" s="4">
-        <v>0.48841435185185184</v>
+        <v>0.45427083333333335</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>1001364656</v>
+        <v>1001364804</v>
       </c>
       <c r="B26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D26" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E26" t="s">
         <v>3</v>
       </c>
       <c r="F26" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G26" t="s">
         <v>0</v>
@@ -1896,36 +1902,36 @@
         <v>4</v>
       </c>
       <c r="I26" s="3">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="J26" s="4">
-        <v>0.48898148148148146</v>
+        <v>0.45427083333333335</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L26" s="10" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>1001364511</v>
+        <v>1001364684</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D27" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E27" t="s">
         <v>3</v>
       </c>
       <c r="F27" s="1">
-        <v>738</v>
+        <v>708.95</v>
       </c>
       <c r="G27" t="s">
         <v>0</v>
@@ -1934,112 +1940,112 @@
         <v>4</v>
       </c>
       <c r="I27" s="3">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="J27" s="4">
-        <v>0.63017361111111114</v>
-      </c>
-      <c r="K27" t="s">
+        <v>0.55635416666666659</v>
+      </c>
+      <c r="K27" s="10" t="s">
         <v>82</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>1001362595</v>
+        <v>1001364656</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>92</v>
+        <v>14</v>
       </c>
       <c r="E28" t="s">
         <v>3</v>
       </c>
       <c r="F28" s="1">
-        <v>128.9</v>
+        <v>242</v>
       </c>
       <c r="G28" t="s">
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I28" s="3">
-        <v>46164</v>
+        <v>46178</v>
       </c>
       <c r="J28" s="4">
-        <v>0.57401620370370365</v>
-      </c>
-      <c r="K28" t="s">
-        <v>82</v>
-      </c>
-      <c r="L28" t="s">
-        <v>83</v>
+        <v>0.48500000000000004</v>
+      </c>
+      <c r="K28" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L28" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>1001362595</v>
+        <v>1001364656</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
       <c r="C29" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="D29" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="E29" t="s">
         <v>3</v>
       </c>
       <c r="F29" s="1">
-        <v>115.3</v>
+        <v>25</v>
       </c>
       <c r="G29" t="s">
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I29" s="3">
-        <v>46164</v>
+        <v>46178</v>
       </c>
       <c r="J29" s="4">
-        <v>0.5740277777777778</v>
-      </c>
-      <c r="K29" t="s">
-        <v>82</v>
-      </c>
-      <c r="L29" t="s">
-        <v>83</v>
+        <v>0.48591435185185183</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L29" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>1001361760</v>
+        <v>1001364656</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C30" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="E30" t="s">
         <v>3</v>
       </c>
       <c r="F30" s="1">
-        <v>2706.88</v>
+        <v>2250</v>
       </c>
       <c r="G30" t="s">
         <v>0</v>
@@ -2048,36 +2054,36 @@
         <v>4</v>
       </c>
       <c r="I30" s="3">
-        <v>46161</v>
+        <v>46178</v>
       </c>
       <c r="J30" s="4">
-        <v>0.40358796296296301</v>
-      </c>
-      <c r="K30" t="s">
-        <v>90</v>
-      </c>
-      <c r="L30" t="s">
+        <v>0.48841435185185184</v>
+      </c>
+      <c r="K30" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L30" s="10" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>1001361760</v>
+        <v>1001364656</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="D31" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="E31" t="s">
         <v>3</v>
       </c>
       <c r="F31" s="1">
-        <v>477.84</v>
+        <v>0</v>
       </c>
       <c r="G31" t="s">
         <v>0</v>
@@ -2086,36 +2092,36 @@
         <v>4</v>
       </c>
       <c r="I31" s="3">
-        <v>46161</v>
+        <v>46178</v>
       </c>
       <c r="J31" s="4">
-        <v>0.40358796296296301</v>
-      </c>
-      <c r="K31" t="s">
-        <v>90</v>
-      </c>
-      <c r="L31" t="s">
+        <v>0.48898148148148146</v>
+      </c>
+      <c r="K31" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L31" s="10" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>1001361434</v>
+        <v>1001364511</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="D32" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="E32" t="s">
         <v>3</v>
       </c>
       <c r="F32" s="1">
-        <v>41.1</v>
+        <v>738</v>
       </c>
       <c r="G32" t="s">
         <v>0</v>
@@ -2124,226 +2130,226 @@
         <v>4</v>
       </c>
       <c r="I32" s="3">
-        <v>46160</v>
+        <v>46177</v>
       </c>
       <c r="J32" s="4">
-        <v>0.34767361111111111</v>
+        <v>0.63017361111111114</v>
       </c>
       <c r="K32" t="s">
         <v>82</v>
       </c>
-      <c r="L32" t="s">
-        <v>86</v>
+      <c r="L32" s="10" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>1001361434</v>
+        <v>1001362595</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D33" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E33" t="s">
         <v>3</v>
       </c>
       <c r="F33" s="1">
-        <v>82.2</v>
+        <v>128.9</v>
       </c>
       <c r="G33" t="s">
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I33" s="3">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="J33" s="4">
-        <v>0.34847222222222224</v>
+        <v>0.57401620370370365</v>
       </c>
       <c r="K33" t="s">
         <v>82</v>
       </c>
       <c r="L33" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>1001361434</v>
+        <v>1001362595</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D34" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E34" t="s">
         <v>3</v>
       </c>
       <c r="F34" s="1">
-        <v>6.95</v>
+        <v>115.3</v>
       </c>
       <c r="G34" t="s">
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I34" s="3">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="J34" s="4">
-        <v>0.3489814814814815</v>
+        <v>0.5740277777777778</v>
       </c>
       <c r="K34" t="s">
         <v>82</v>
       </c>
       <c r="L34" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>1001361254</v>
+        <v>1001361760</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E35" t="s">
         <v>3</v>
       </c>
       <c r="F35" s="1">
-        <v>172.95</v>
+        <v>2706.88</v>
       </c>
       <c r="G35" t="s">
         <v>0</v>
       </c>
       <c r="H35" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I35" s="3">
-        <v>46155</v>
+        <v>46161</v>
       </c>
       <c r="J35" s="4">
-        <v>0.68266203703703709</v>
+        <v>0.40358796296296301</v>
       </c>
       <c r="K35" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L35" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>1001360993</v>
+        <v>1001361760</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D36" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E36" t="s">
         <v>3</v>
       </c>
       <c r="F36" s="1">
-        <v>8763.34</v>
+        <v>477.84</v>
       </c>
       <c r="G36" t="s">
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="I36" s="3">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="J36" s="4">
-        <v>0.66589120370370369</v>
+        <v>0.40358796296296301</v>
       </c>
       <c r="K36" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="L36" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>1001360993</v>
+        <v>1001361434</v>
       </c>
       <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>97</v>
+      </c>
+      <c r="D37" t="s">
+        <v>98</v>
+      </c>
+      <c r="E37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F37" s="1">
+        <v>41.1</v>
+      </c>
+      <c r="G37" t="s">
+        <v>0</v>
+      </c>
+      <c r="H37" t="s">
+        <v>4</v>
+      </c>
+      <c r="I37" s="3">
+        <v>46160</v>
+      </c>
+      <c r="J37" s="4">
+        <v>0.34767361111111111</v>
+      </c>
+      <c r="K37" t="s">
+        <v>82</v>
+      </c>
+      <c r="L37" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>1001361434</v>
+      </c>
+      <c r="B38">
         <v>2</v>
       </c>
-      <c r="C37" t="s">
-        <v>102</v>
-      </c>
-      <c r="D37" t="s">
-        <v>105</v>
-      </c>
-      <c r="E37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F37" s="1">
-        <v>586.66</v>
-      </c>
-      <c r="G37" t="s">
-        <v>0</v>
-      </c>
-      <c r="H37" t="s">
-        <v>104</v>
-      </c>
-      <c r="I37" s="3">
-        <v>46154</v>
-      </c>
-      <c r="J37" s="4">
-        <v>0.6667939814814815</v>
-      </c>
-      <c r="K37" t="s">
-        <v>106</v>
-      </c>
-      <c r="L37" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A38" s="2">
-        <v>1001360515</v>
-      </c>
-      <c r="B38" s="2">
-        <v>1</v>
-      </c>
       <c r="C38" t="s">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="D38" t="s">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="E38" t="s">
         <v>3</v>
       </c>
       <c r="F38" s="1">
-        <v>0</v>
+        <v>82.2</v>
       </c>
       <c r="G38" t="s">
         <v>0</v>
@@ -2352,188 +2358,188 @@
         <v>4</v>
       </c>
       <c r="I38" s="3">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="J38" s="4">
-        <v>0.43606481481481479</v>
+        <v>0.34847222222222224</v>
       </c>
       <c r="K38" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L38" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A39" s="2">
-        <v>1001359403</v>
-      </c>
-      <c r="B39" s="2">
-        <v>1</v>
+      <c r="A39">
+        <v>1001361434</v>
+      </c>
+      <c r="B39">
+        <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>5</v>
+        <v>97</v>
       </c>
       <c r="D39" t="s">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="E39" t="s">
         <v>3</v>
       </c>
       <c r="F39" s="1">
-        <v>296.16000000000003</v>
+        <v>6.95</v>
       </c>
       <c r="G39" t="s">
         <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I39" s="3">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="J39" s="4">
-        <v>0.35246527777777775</v>
+        <v>0.3489814814814815</v>
       </c>
       <c r="K39" t="s">
         <v>82</v>
       </c>
       <c r="L39" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>1001361254</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
+        <v>101</v>
+      </c>
+      <c r="D40" t="s">
+        <v>93</v>
+      </c>
+      <c r="E40" t="s">
+        <v>3</v>
+      </c>
+      <c r="F40" s="1">
+        <v>172.95</v>
+      </c>
+      <c r="G40" t="s">
+        <v>0</v>
+      </c>
+      <c r="H40" t="s">
+        <v>7</v>
+      </c>
+      <c r="I40" s="3">
+        <v>46155</v>
+      </c>
+      <c r="J40" s="4">
+        <v>0.68266203703703709</v>
+      </c>
+      <c r="K40" t="s">
+        <v>82</v>
+      </c>
+      <c r="L40" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A40" s="2">
-        <v>1001358440</v>
-      </c>
-      <c r="B40" s="2">
-        <v>1</v>
-      </c>
-      <c r="C40" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" t="s">
-        <v>3</v>
-      </c>
-      <c r="F40" s="1">
-        <v>8211</v>
-      </c>
-      <c r="G40" t="s">
-        <v>0</v>
-      </c>
-      <c r="H40" t="s">
-        <v>4</v>
-      </c>
-      <c r="I40" s="3">
-        <v>46136</v>
-      </c>
-      <c r="J40" s="4">
-        <v>0.51320601851851855</v>
-      </c>
-      <c r="K40" t="s">
-        <v>90</v>
-      </c>
-      <c r="L40" t="s">
-        <v>79</v>
-      </c>
-    </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A41" s="2">
-        <v>1001358139</v>
-      </c>
-      <c r="B41" s="2">
+      <c r="A41">
+        <v>1001360993</v>
+      </c>
+      <c r="B41">
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="D41" t="s">
-        <v>6</v>
+        <v>103</v>
       </c>
       <c r="E41" t="s">
         <v>3</v>
       </c>
       <c r="F41" s="1">
-        <v>296.16000000000003</v>
+        <v>8763.34</v>
       </c>
       <c r="G41" t="s">
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>7</v>
+        <v>104</v>
       </c>
       <c r="I41" s="3">
-        <v>46135</v>
+        <v>46154</v>
       </c>
       <c r="J41" s="4">
-        <v>0.40256944444444448</v>
+        <v>0.66589120370370369</v>
       </c>
       <c r="K41" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="L41" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A42" s="2">
-        <v>1001357792</v>
-      </c>
-      <c r="B42" s="2">
-        <v>1</v>
+      <c r="A42">
+        <v>1001360993</v>
+      </c>
+      <c r="B42">
+        <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>11</v>
+        <v>102</v>
       </c>
       <c r="D42" t="s">
-        <v>12</v>
+        <v>105</v>
       </c>
       <c r="E42" t="s">
         <v>3</v>
       </c>
       <c r="F42" s="1">
-        <v>62.02</v>
+        <v>586.66</v>
       </c>
       <c r="G42" t="s">
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="I42" s="3">
-        <v>46133</v>
+        <v>46154</v>
       </c>
       <c r="J42" s="4">
-        <v>0.59369212962962969</v>
+        <v>0.6667939814814815</v>
       </c>
       <c r="K42" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="L42" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>1001357548</v>
+        <v>1001360515</v>
       </c>
       <c r="B43" s="2">
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D43" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E43" t="s">
         <v>3</v>
       </c>
       <c r="F43" s="1">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="G43" t="s">
         <v>0</v>
@@ -2542,74 +2548,74 @@
         <v>4</v>
       </c>
       <c r="I43" s="3">
-        <v>46132</v>
+        <v>46153</v>
       </c>
       <c r="J43" s="4">
-        <v>0.54353009259259266</v>
+        <v>0.43606481481481479</v>
       </c>
       <c r="K43" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L43" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>1001357548</v>
+        <v>1001359403</v>
       </c>
       <c r="B44" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D44" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E44" t="s">
         <v>3</v>
       </c>
       <c r="F44" s="1">
-        <v>25</v>
+        <v>296.16000000000003</v>
       </c>
       <c r="G44" t="s">
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I44" s="3">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="J44" s="4">
-        <v>0.54533564814814817</v>
+        <v>0.35246527777777775</v>
       </c>
       <c r="K44" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L44" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>1001357548</v>
+        <v>1001358440</v>
       </c>
       <c r="B45" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E45" t="s">
         <v>3</v>
       </c>
       <c r="F45" s="1">
-        <v>2250</v>
+        <v>8211</v>
       </c>
       <c r="G45" t="s">
         <v>0</v>
@@ -2618,36 +2624,36 @@
         <v>4</v>
       </c>
       <c r="I45" s="3">
-        <v>46132</v>
+        <v>46136</v>
       </c>
       <c r="J45" s="4">
-        <v>0.546412037037037</v>
+        <v>0.51320601851851855</v>
       </c>
       <c r="K45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L45" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>1001356465</v>
+        <v>1001358139</v>
       </c>
       <c r="B46" s="2">
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D46" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E46" t="s">
         <v>3</v>
       </c>
       <c r="F46" s="1">
-        <v>17.55</v>
+        <v>296.16000000000003</v>
       </c>
       <c r="G46" t="s">
         <v>0</v>
@@ -2656,74 +2662,74 @@
         <v>7</v>
       </c>
       <c r="I46" s="3">
-        <v>46125</v>
+        <v>46135</v>
       </c>
       <c r="J46" s="4">
-        <v>0.65668981481481481</v>
+        <v>0.40256944444444448</v>
       </c>
       <c r="K46" t="s">
         <v>82</v>
       </c>
       <c r="L46" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>1001356465</v>
+        <v>1001357792</v>
       </c>
       <c r="B47" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E47" t="s">
         <v>3</v>
       </c>
       <c r="F47" s="1">
-        <v>17.55</v>
+        <v>62.02</v>
       </c>
       <c r="G47" t="s">
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I47" s="3">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="J47" s="4">
-        <v>0.65668981481481481</v>
+        <v>0.59369212962962969</v>
       </c>
       <c r="K47" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L47" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>1001356192</v>
+        <v>1001357548</v>
       </c>
       <c r="B48" s="2">
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D48" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E48" t="s">
         <v>3</v>
       </c>
       <c r="F48" s="1">
-        <v>270.5</v>
+        <v>242</v>
       </c>
       <c r="G48" t="s">
         <v>0</v>
@@ -2732,36 +2738,36 @@
         <v>4</v>
       </c>
       <c r="I48" s="3">
-        <v>46122</v>
+        <v>46132</v>
       </c>
       <c r="J48" s="4">
-        <v>0.58597222222222223</v>
+        <v>0.54353009259259266</v>
       </c>
       <c r="K48" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="L48" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>1001356190</v>
+        <v>1001357548</v>
       </c>
       <c r="B49" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E49" t="s">
         <v>3</v>
       </c>
       <c r="F49" s="1">
-        <v>1359.84</v>
+        <v>25</v>
       </c>
       <c r="G49" t="s">
         <v>0</v>
@@ -2770,36 +2776,36 @@
         <v>4</v>
       </c>
       <c r="I49" s="3">
-        <v>46122</v>
+        <v>46132</v>
       </c>
       <c r="J49" s="4">
-        <v>0.58506944444444442</v>
+        <v>0.54533564814814817</v>
       </c>
       <c r="K49" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L49" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>1001355643</v>
+        <v>1001357548</v>
       </c>
       <c r="B50" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C50" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D50" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E50" t="s">
         <v>3</v>
       </c>
       <c r="F50" s="1">
-        <v>425.29</v>
+        <v>2250</v>
       </c>
       <c r="G50" t="s">
         <v>0</v>
@@ -2808,36 +2814,36 @@
         <v>4</v>
       </c>
       <c r="I50" s="3">
-        <v>46120</v>
+        <v>46132</v>
       </c>
       <c r="J50" s="4">
-        <v>0.58754629629629629</v>
+        <v>0.546412037037037</v>
       </c>
       <c r="K50" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="L50" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>1001354025</v>
+        <v>1001356465</v>
       </c>
       <c r="B51" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D51" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E51" t="s">
         <v>3</v>
       </c>
       <c r="F51" s="1">
-        <v>247</v>
+        <v>17.55</v>
       </c>
       <c r="G51" t="s">
         <v>0</v>
@@ -2846,36 +2852,36 @@
         <v>7</v>
       </c>
       <c r="I51" s="3">
-        <v>46108</v>
+        <v>46125</v>
       </c>
       <c r="J51" s="4">
-        <v>0.54822916666666666</v>
+        <v>0.65668981481481481</v>
       </c>
       <c r="K51" t="s">
         <v>82</v>
       </c>
       <c r="L51" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>1001354025</v>
+        <v>1001356465</v>
       </c>
       <c r="B52" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D52" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E52" t="s">
         <v>3</v>
       </c>
       <c r="F52" s="1">
-        <v>41</v>
+        <v>17.55</v>
       </c>
       <c r="G52" t="s">
         <v>0</v>
@@ -2884,74 +2890,74 @@
         <v>7</v>
       </c>
       <c r="I52" s="3">
-        <v>46108</v>
+        <v>46125</v>
       </c>
       <c r="J52" s="4">
-        <v>0.54866898148148147</v>
+        <v>0.65668981481481481</v>
       </c>
       <c r="K52" t="s">
         <v>82</v>
       </c>
       <c r="L52" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>1001354025</v>
+        <v>1001356192</v>
       </c>
       <c r="B53" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D53" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E53" t="s">
         <v>3</v>
       </c>
       <c r="F53" s="1">
-        <v>732</v>
+        <v>270.5</v>
       </c>
       <c r="G53" t="s">
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I53" s="3">
-        <v>46108</v>
+        <v>46122</v>
       </c>
       <c r="J53" s="4">
-        <v>0.5505902777777778</v>
+        <v>0.58597222222222223</v>
       </c>
       <c r="K53" t="s">
         <v>82</v>
       </c>
       <c r="L53" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>1001351971</v>
+        <v>1001356190</v>
       </c>
       <c r="B54" s="2">
         <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D54" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E54" t="s">
         <v>3</v>
       </c>
       <c r="F54" s="1">
-        <v>1.9</v>
+        <v>1359.84</v>
       </c>
       <c r="G54" t="s">
         <v>0</v>
@@ -2960,36 +2966,36 @@
         <v>4</v>
       </c>
       <c r="I54" s="3">
-        <v>46098</v>
+        <v>46122</v>
       </c>
       <c r="J54" s="4">
-        <v>0.34575231481481478</v>
+        <v>0.58506944444444442</v>
       </c>
       <c r="K54" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L54" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>1001351971</v>
+        <v>1001355643</v>
       </c>
       <c r="B55" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D55" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E55" t="s">
         <v>3</v>
       </c>
       <c r="F55" s="1">
-        <v>1.8</v>
+        <v>425.29</v>
       </c>
       <c r="G55" t="s">
         <v>0</v>
@@ -2998,150 +3004,150 @@
         <v>4</v>
       </c>
       <c r="I55" s="3">
-        <v>46098</v>
+        <v>46120</v>
       </c>
       <c r="J55" s="4">
-        <v>0.34575231481481478</v>
+        <v>0.58754629629629629</v>
       </c>
       <c r="K55" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L55" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>1001351235</v>
+        <v>1001354025</v>
       </c>
       <c r="B56" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D56" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E56" t="s">
         <v>3</v>
       </c>
       <c r="F56" s="1">
-        <v>153.19999999999999</v>
+        <v>247</v>
       </c>
       <c r="G56" t="s">
         <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I56" s="3">
-        <v>46092</v>
+        <v>46108</v>
       </c>
       <c r="J56" s="4">
-        <v>0.66688657407407403</v>
+        <v>0.54822916666666666</v>
       </c>
       <c r="K56" t="s">
         <v>82</v>
       </c>
       <c r="L56" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>1001351075</v>
+        <v>1001354025</v>
       </c>
       <c r="B57" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C57" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D57" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E57" t="s">
         <v>3</v>
       </c>
       <c r="F57" s="1">
-        <v>127</v>
+        <v>41</v>
       </c>
       <c r="G57" t="s">
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I57" s="3">
-        <v>46092</v>
+        <v>46108</v>
       </c>
       <c r="J57" s="4">
-        <v>0.40361111111111114</v>
+        <v>0.54866898148148147</v>
       </c>
       <c r="K57" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L57" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>1001351075</v>
+        <v>1001354025</v>
       </c>
       <c r="B58" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C58" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D58" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E58" t="s">
         <v>3</v>
       </c>
       <c r="F58" s="1">
-        <v>15</v>
+        <v>732</v>
       </c>
       <c r="G58" t="s">
         <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I58" s="3">
-        <v>46092</v>
+        <v>46108</v>
       </c>
       <c r="J58" s="4">
-        <v>0.6585185185185185</v>
+        <v>0.5505902777777778</v>
       </c>
       <c r="K58" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L58" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>1001351001</v>
+        <v>1001351971</v>
       </c>
       <c r="B59" s="2">
         <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D59" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E59" t="s">
         <v>3</v>
       </c>
       <c r="F59" s="1">
-        <v>598.67999999999995</v>
+        <v>1.9</v>
       </c>
       <c r="G59" t="s">
         <v>0</v>
@@ -3150,36 +3156,36 @@
         <v>4</v>
       </c>
       <c r="I59" s="3">
-        <v>46091</v>
+        <v>46098</v>
       </c>
       <c r="J59" s="4">
-        <v>0.63434027777777779</v>
+        <v>0.34575231481481478</v>
       </c>
       <c r="K59" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L59" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>1001350675</v>
+        <v>1001351971</v>
       </c>
       <c r="B60" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D60" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E60" t="s">
         <v>3</v>
       </c>
       <c r="F60" s="1">
-        <v>600</v>
+        <v>1.8</v>
       </c>
       <c r="G60" t="s">
         <v>0</v>
@@ -3188,36 +3194,36 @@
         <v>4</v>
       </c>
       <c r="I60" s="3">
-        <v>46090</v>
+        <v>46098</v>
       </c>
       <c r="J60" s="4">
-        <v>0.54053240740740738</v>
+        <v>0.34575231481481478</v>
       </c>
       <c r="K60" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L60" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>1001350592</v>
+        <v>1001351235</v>
       </c>
       <c r="B61" s="2">
         <v>1</v>
       </c>
       <c r="C61" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D61" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E61" t="s">
         <v>3</v>
       </c>
       <c r="F61" s="1">
-        <v>449.01</v>
+        <v>153.19999999999999</v>
       </c>
       <c r="G61" t="s">
         <v>0</v>
@@ -3226,36 +3232,36 @@
         <v>4</v>
       </c>
       <c r="I61" s="3">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="J61" s="4">
-        <v>0.37918981481481479</v>
+        <v>0.66688657407407403</v>
       </c>
       <c r="K61" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L61" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>1001350094</v>
+        <v>1001351075</v>
       </c>
       <c r="B62" s="2">
         <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D62" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E62" t="s">
         <v>3</v>
       </c>
       <c r="F62" s="1">
-        <v>679.92</v>
+        <v>127</v>
       </c>
       <c r="G62" t="s">
         <v>0</v>
@@ -3264,36 +3270,36 @@
         <v>4</v>
       </c>
       <c r="I62" s="3">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="J62" s="4">
-        <v>0.39840277777777783</v>
+        <v>0.40361111111111114</v>
       </c>
       <c r="K62" t="s">
         <v>90</v>
       </c>
       <c r="L62" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>1001350094</v>
+        <v>1001351075</v>
       </c>
       <c r="B63" s="2">
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D63" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E63" t="s">
         <v>3</v>
       </c>
       <c r="F63" s="1">
-        <v>87.14</v>
+        <v>15</v>
       </c>
       <c r="G63" t="s">
         <v>0</v>
@@ -3302,36 +3308,36 @@
         <v>4</v>
       </c>
       <c r="I63" s="3">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="J63" s="4">
-        <v>0.39840277777777783</v>
+        <v>0.6585185185185185</v>
       </c>
       <c r="K63" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="L63" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>1001349263</v>
+        <v>1001351001</v>
       </c>
       <c r="B64" s="2">
         <v>1</v>
       </c>
       <c r="C64" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D64" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E64" t="s">
         <v>3</v>
       </c>
       <c r="F64" s="1">
-        <v>14.55</v>
+        <v>598.67999999999995</v>
       </c>
       <c r="G64" t="s">
         <v>0</v>
@@ -3340,13 +3346,13 @@
         <v>4</v>
       </c>
       <c r="I64" s="3">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="J64" s="4">
-        <v>0.39340277777777777</v>
+        <v>0.63434027777777779</v>
       </c>
       <c r="K64" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L64" t="s">
         <v>79</v>
@@ -3354,22 +3360,22 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>1001349263</v>
+        <v>1001350675</v>
       </c>
       <c r="B65" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D65" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E65" t="s">
         <v>3</v>
       </c>
       <c r="F65" s="1">
-        <v>15.15</v>
+        <v>600</v>
       </c>
       <c r="G65" t="s">
         <v>0</v>
@@ -3378,36 +3384,36 @@
         <v>4</v>
       </c>
       <c r="I65" s="3">
-        <v>46083</v>
+        <v>46090</v>
       </c>
       <c r="J65" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.54053240740740738</v>
       </c>
       <c r="K65" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L65" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>1001349263</v>
+        <v>1001350592</v>
       </c>
       <c r="B66" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C66" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D66" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E66" t="s">
         <v>3</v>
       </c>
       <c r="F66" s="1">
-        <v>15.15</v>
+        <v>449.01</v>
       </c>
       <c r="G66" t="s">
         <v>0</v>
@@ -3416,13 +3422,13 @@
         <v>4</v>
       </c>
       <c r="I66" s="3">
-        <v>46083</v>
+        <v>46090</v>
       </c>
       <c r="J66" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.37918981481481479</v>
       </c>
       <c r="K66" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L66" t="s">
         <v>79</v>
@@ -3430,22 +3436,22 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
-        <v>1001349263</v>
+        <v>1001350094</v>
       </c>
       <c r="B67" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C67" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D67" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E67" t="s">
         <v>3</v>
       </c>
       <c r="F67" s="1">
-        <v>14.55</v>
+        <v>679.92</v>
       </c>
       <c r="G67" t="s">
         <v>0</v>
@@ -3454,36 +3460,36 @@
         <v>4</v>
       </c>
       <c r="I67" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="J67" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.39840277777777783</v>
       </c>
       <c r="K67" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L67" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
-        <v>1001349263</v>
+        <v>1001350094</v>
       </c>
       <c r="B68" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D68" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E68" t="s">
         <v>3</v>
       </c>
       <c r="F68" s="1">
-        <v>14.85</v>
+        <v>87.14</v>
       </c>
       <c r="G68" t="s">
         <v>0</v>
@@ -3492,16 +3498,16 @@
         <v>4</v>
       </c>
       <c r="I68" s="3">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="J68" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.39840277777777783</v>
       </c>
       <c r="K68" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L68" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
@@ -3509,19 +3515,19 @@
         <v>1001349263</v>
       </c>
       <c r="B69" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C69" t="s">
         <v>45</v>
       </c>
       <c r="D69" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E69" t="s">
         <v>3</v>
       </c>
       <c r="F69" s="1">
-        <v>15</v>
+        <v>14.55</v>
       </c>
       <c r="G69" t="s">
         <v>0</v>
@@ -3533,7 +3539,7 @@
         <v>46083</v>
       </c>
       <c r="J69" s="4">
-        <v>0.39341435185185186</v>
+        <v>0.39340277777777777</v>
       </c>
       <c r="K69" t="s">
         <v>84</v>
@@ -3547,19 +3553,19 @@
         <v>1001349263</v>
       </c>
       <c r="B70" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C70" t="s">
         <v>45</v>
       </c>
       <c r="D70" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E70" t="s">
         <v>3</v>
       </c>
       <c r="F70" s="1">
-        <v>15</v>
+        <v>15.15</v>
       </c>
       <c r="G70" t="s">
         <v>0</v>
@@ -3585,19 +3591,19 @@
         <v>1001349263</v>
       </c>
       <c r="B71" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C71" t="s">
         <v>45</v>
       </c>
       <c r="D71" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E71" t="s">
         <v>3</v>
       </c>
       <c r="F71" s="1">
-        <v>14.85</v>
+        <v>15.15</v>
       </c>
       <c r="G71" t="s">
         <v>0</v>
@@ -3620,22 +3626,22 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
-        <v>1001345614</v>
+        <v>1001349263</v>
       </c>
       <c r="B72" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C72" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D72" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E72" t="s">
         <v>3</v>
       </c>
       <c r="F72" s="1">
-        <v>605</v>
+        <v>14.55</v>
       </c>
       <c r="G72" t="s">
         <v>0</v>
@@ -3644,36 +3650,36 @@
         <v>4</v>
       </c>
       <c r="I72" s="3">
-        <v>46059</v>
+        <v>46083</v>
       </c>
       <c r="J72" s="4">
-        <v>0.6586805555555556</v>
+        <v>0.39341435185185186</v>
       </c>
       <c r="K72" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L72" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
-        <v>1001345614</v>
+        <v>1001349263</v>
       </c>
       <c r="B73" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C73" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D73" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E73" t="s">
         <v>3</v>
       </c>
       <c r="F73" s="1">
-        <v>154</v>
+        <v>14.85</v>
       </c>
       <c r="G73" t="s">
         <v>0</v>
@@ -3682,36 +3688,36 @@
         <v>4</v>
       </c>
       <c r="I73" s="3">
-        <v>46059</v>
+        <v>46083</v>
       </c>
       <c r="J73" s="4">
-        <v>0.66027777777777774</v>
+        <v>0.39341435185185186</v>
       </c>
       <c r="K73" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L73" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
-        <v>1001343034</v>
+        <v>1001349263</v>
       </c>
       <c r="B74" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C74" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D74" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E74" t="s">
         <v>3</v>
       </c>
       <c r="F74" s="1">
-        <v>208.6</v>
+        <v>15</v>
       </c>
       <c r="G74" t="s">
         <v>0</v>
@@ -3720,36 +3726,36 @@
         <v>4</v>
       </c>
       <c r="I74" s="3">
-        <v>46044</v>
+        <v>46083</v>
       </c>
       <c r="J74" s="4">
-        <v>0.65900462962962958</v>
+        <v>0.39341435185185186</v>
       </c>
       <c r="K74" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L74" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
-        <v>1001343034</v>
+        <v>1001349263</v>
       </c>
       <c r="B75" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C75" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D75" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E75" t="s">
         <v>3</v>
       </c>
       <c r="F75" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G75" t="s">
         <v>0</v>
@@ -3758,36 +3764,36 @@
         <v>4</v>
       </c>
       <c r="I75" s="3">
-        <v>46044</v>
+        <v>46083</v>
       </c>
       <c r="J75" s="4">
-        <v>0.66190972222222222</v>
+        <v>0.39341435185185186</v>
       </c>
       <c r="K75" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L75" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
-        <v>1001342447</v>
+        <v>1001349263</v>
       </c>
       <c r="B76" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C76" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D76" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E76" t="s">
         <v>3</v>
       </c>
       <c r="F76" s="1">
-        <v>240</v>
+        <v>14.85</v>
       </c>
       <c r="G76" t="s">
         <v>0</v>
@@ -3796,36 +3802,36 @@
         <v>4</v>
       </c>
       <c r="I76" s="3">
-        <v>46042</v>
+        <v>46083</v>
       </c>
       <c r="J76" s="4">
-        <v>0.54805555555555552</v>
+        <v>0.39341435185185186</v>
       </c>
       <c r="K76" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L76" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
-        <v>1001342447</v>
+        <v>1001345614</v>
       </c>
       <c r="B77" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D77" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E77" t="s">
         <v>3</v>
       </c>
       <c r="F77" s="1">
-        <v>8.9499999999999993</v>
+        <v>605</v>
       </c>
       <c r="G77" t="s">
         <v>0</v>
@@ -3834,36 +3840,36 @@
         <v>4</v>
       </c>
       <c r="I77" s="3">
-        <v>46042</v>
+        <v>46059</v>
       </c>
       <c r="J77" s="4">
-        <v>0.54859953703703701</v>
+        <v>0.6586805555555556</v>
       </c>
       <c r="K77" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L77" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
-        <v>1001340933</v>
+        <v>1001345614</v>
       </c>
       <c r="B78" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D78" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E78" t="s">
         <v>3</v>
       </c>
       <c r="F78" s="1">
-        <v>150.47999999999999</v>
+        <v>154</v>
       </c>
       <c r="G78" t="s">
         <v>0</v>
@@ -3872,36 +3878,36 @@
         <v>4</v>
       </c>
       <c r="I78" s="3">
-        <v>46034</v>
+        <v>46059</v>
       </c>
       <c r="J78" s="4">
-        <v>0.40950231481481486</v>
+        <v>0.66027777777777774</v>
       </c>
       <c r="K78" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="L78" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A79">
-        <v>1001369807</v>
-      </c>
-      <c r="B79">
+      <c r="A79" s="2">
+        <v>1001343034</v>
+      </c>
+      <c r="B79" s="2">
         <v>1</v>
       </c>
       <c r="C79" t="s">
-        <v>140</v>
+        <v>57</v>
       </c>
       <c r="D79" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="E79" t="s">
         <v>3</v>
       </c>
       <c r="F79" s="1">
-        <v>172</v>
+        <v>208.6</v>
       </c>
       <c r="G79" t="s">
         <v>0</v>
@@ -3910,60 +3916,174 @@
         <v>4</v>
       </c>
       <c r="I79" s="3">
-        <v>46213</v>
+        <v>46044</v>
       </c>
       <c r="J79" s="4">
-        <v>0.56239583333333332</v>
+        <v>0.65900462962962958</v>
       </c>
       <c r="K79" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L79" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A80">
-        <v>1001368508</v>
-      </c>
-      <c r="B80">
-        <v>1</v>
+      <c r="A80" s="2">
+        <v>1001343034</v>
+      </c>
+      <c r="B80" s="2">
+        <v>2</v>
       </c>
       <c r="C80" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="D80" t="s">
-        <v>128</v>
+        <v>59</v>
       </c>
       <c r="E80" t="s">
         <v>3</v>
       </c>
       <c r="F80" s="1">
-        <v>121.84</v>
+        <v>20</v>
       </c>
       <c r="G80" t="s">
         <v>0</v>
       </c>
       <c r="H80" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I80" s="3">
-        <v>46205</v>
+        <v>46044</v>
       </c>
       <c r="J80" s="4">
-        <v>0.54736111111111108</v>
+        <v>0.66190972222222222</v>
       </c>
       <c r="K80" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="L80" t="s">
-        <v>83</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A81" s="2">
+        <v>1001342447</v>
+      </c>
+      <c r="B81" s="2">
+        <v>1</v>
+      </c>
+      <c r="C81" t="s">
+        <v>60</v>
+      </c>
+      <c r="D81" t="s">
+        <v>61</v>
+      </c>
+      <c r="E81" t="s">
+        <v>3</v>
+      </c>
+      <c r="F81" s="1">
+        <v>240</v>
+      </c>
+      <c r="G81" t="s">
+        <v>0</v>
+      </c>
+      <c r="H81" t="s">
+        <v>4</v>
+      </c>
+      <c r="I81" s="3">
+        <v>46042</v>
+      </c>
+      <c r="J81" s="4">
+        <v>0.54805555555555552</v>
+      </c>
+      <c r="K81" t="s">
+        <v>88</v>
+      </c>
+      <c r="L81" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A82" s="2">
+        <v>1001342447</v>
+      </c>
+      <c r="B82" s="2">
+        <v>2</v>
+      </c>
+      <c r="C82" t="s">
+        <v>60</v>
+      </c>
+      <c r="D82" t="s">
+        <v>62</v>
+      </c>
+      <c r="E82" t="s">
+        <v>3</v>
+      </c>
+      <c r="F82" s="1">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="G82" t="s">
+        <v>0</v>
+      </c>
+      <c r="H82" t="s">
+        <v>4</v>
+      </c>
+      <c r="I82" s="3">
+        <v>46042</v>
+      </c>
+      <c r="J82" s="4">
+        <v>0.54859953703703701</v>
+      </c>
+      <c r="K82" t="s">
+        <v>88</v>
+      </c>
+      <c r="L82" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A83" s="2">
+        <v>1001340933</v>
+      </c>
+      <c r="B83" s="2">
+        <v>1</v>
+      </c>
+      <c r="C83" t="s">
+        <v>63</v>
+      </c>
+      <c r="D83" t="s">
+        <v>64</v>
+      </c>
+      <c r="E83" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="1">
+        <v>150.47999999999999</v>
+      </c>
+      <c r="G83" t="s">
+        <v>0</v>
+      </c>
+      <c r="H83" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3">
+        <v>46034</v>
+      </c>
+      <c r="J83" s="4">
+        <v>0.40950231481481486</v>
+      </c>
+      <c r="K83" t="s">
+        <v>90</v>
+      </c>
+      <c r="L83" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M80" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M80">
-      <sortCondition descending="1" ref="A1:A78"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M83">
+      <sortCondition descending="1" ref="A1:A80"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="0" type="noConversion"/>

--- a/data/bestellingen 7193 2026_latest.xlsx
+++ b/data/bestellingen 7193 2026_latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\R\Bestellingen\shiny\7180\7180\jorgpeter-orders7180\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B9E815D-3A3E-4875-9E8F-8A6C7C0663C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC5D047-4CA2-402E-85C9-C000E68B0A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$88</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="155">
   <si>
     <t>EUR</t>
   </si>
@@ -469,6 +469,30 @@
   </si>
   <si>
     <t>C101257 03.09.2026 7193 Xanthe</t>
+  </si>
+  <si>
+    <t>C117993 30.09.2026 7193 Magazijn</t>
+  </si>
+  <si>
+    <t>TIP SAPPHIRE 1000-1250µL F S DS10x96ST</t>
+  </si>
+  <si>
+    <t>C117993 28.09.2026 7193 Jorn/Mark</t>
+  </si>
+  <si>
+    <t>Procurement of 20112859 next gen</t>
+  </si>
+  <si>
+    <t>quatitation and cluster generation</t>
+  </si>
+  <si>
+    <t>Illumina MiSeq 2*250 bp sequencing</t>
+  </si>
+  <si>
+    <t>C101257 16.09.2026 7193 Xanthe</t>
+  </si>
+  <si>
+    <t>eppendorf combitips advanced b (EA)</t>
   </si>
 </sst>
 </file>
@@ -906,7 +930,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -966,22 +990,22 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>1001378453</v>
+        <v>1001382123</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="1">
-        <v>123.94</v>
+        <v>227.67</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
@@ -990,36 +1014,36 @@
         <v>7</v>
       </c>
       <c r="I2" s="3">
-        <v>46272</v>
+        <v>46295</v>
       </c>
       <c r="J2" s="4">
-        <v>0.39587962962962964</v>
-      </c>
-      <c r="K2" t="s">
+        <v>0.40187499999999998</v>
+      </c>
+      <c r="K2" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>1001378453</v>
+        <v>1001381738</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="E3" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="1">
-        <v>243.68</v>
+        <v>242</v>
       </c>
       <c r="G3" t="s">
         <v>0</v>
@@ -1028,74 +1052,74 @@
         <v>7</v>
       </c>
       <c r="I3" s="3">
-        <v>46272</v>
+        <v>46293</v>
       </c>
       <c r="J3" s="4">
-        <v>0.39587962962962964</v>
-      </c>
-      <c r="K3" t="s">
-        <v>82</v>
-      </c>
-      <c r="L3" t="s">
-        <v>83</v>
+        <v>0.54571759259259256</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>1001378010</v>
+        <v>1001381738</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>151</v>
       </c>
       <c r="E4" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="1">
-        <v>150.47999999999999</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I4" s="3">
-        <v>46268</v>
+        <v>46293</v>
       </c>
       <c r="J4" s="4">
-        <v>0.40054398148148151</v>
-      </c>
-      <c r="K4" t="s">
-        <v>90</v>
-      </c>
-      <c r="L4" t="s">
-        <v>81</v>
+        <v>0.54656249999999995</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>1001375362</v>
+        <v>1001381738</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>152</v>
       </c>
       <c r="E5" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="1">
-        <v>247.88</v>
+        <v>2250</v>
       </c>
       <c r="G5" t="s">
         <v>0</v>
@@ -1104,54 +1128,54 @@
         <v>7</v>
       </c>
       <c r="I5" s="3">
-        <v>46252</v>
+        <v>46293</v>
       </c>
       <c r="J5" s="4">
-        <v>0.45155092592592588</v>
-      </c>
-      <c r="K5" t="s">
-        <v>82</v>
-      </c>
-      <c r="L5" t="s">
-        <v>83</v>
+        <v>0.5473958333333333</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>1001373989</v>
+        <v>1001380074</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="D6" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="E6" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="1">
-        <v>121.84</v>
+        <v>159.24</v>
       </c>
       <c r="G6" t="s">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I6" s="3">
-        <v>46244</v>
+        <v>46281</v>
       </c>
       <c r="J6" s="4">
-        <v>0.40568287037037037</v>
-      </c>
-      <c r="K6" t="s">
+        <v>0.53032407407407411</v>
+      </c>
+      <c r="K6" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="L6" t="s">
-        <v>83</v>
+      <c r="L6" s="10" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -4080,10 +4104,200 @@
         <v>79</v>
       </c>
     </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>1001378453</v>
+      </c>
+      <c r="B84">
+        <v>1</v>
+      </c>
+      <c r="C84" t="s">
+        <v>145</v>
+      </c>
+      <c r="D84" t="s">
+        <v>93</v>
+      </c>
+      <c r="E84" t="s">
+        <v>3</v>
+      </c>
+      <c r="F84" s="1">
+        <v>123.94</v>
+      </c>
+      <c r="G84" t="s">
+        <v>0</v>
+      </c>
+      <c r="H84" t="s">
+        <v>7</v>
+      </c>
+      <c r="I84" s="3">
+        <v>46272</v>
+      </c>
+      <c r="J84" s="4">
+        <v>0.39587962962962964</v>
+      </c>
+      <c r="K84" t="s">
+        <v>82</v>
+      </c>
+      <c r="L84" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>1001378453</v>
+      </c>
+      <c r="B85">
+        <v>2</v>
+      </c>
+      <c r="C85" t="s">
+        <v>145</v>
+      </c>
+      <c r="D85" t="s">
+        <v>128</v>
+      </c>
+      <c r="E85" t="s">
+        <v>3</v>
+      </c>
+      <c r="F85" s="1">
+        <v>243.68</v>
+      </c>
+      <c r="G85" t="s">
+        <v>0</v>
+      </c>
+      <c r="H85" t="s">
+        <v>7</v>
+      </c>
+      <c r="I85" s="3">
+        <v>46272</v>
+      </c>
+      <c r="J85" s="4">
+        <v>0.39587962962962964</v>
+      </c>
+      <c r="K85" t="s">
+        <v>82</v>
+      </c>
+      <c r="L85" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>1001378010</v>
+      </c>
+      <c r="B86">
+        <v>1</v>
+      </c>
+      <c r="C86" t="s">
+        <v>146</v>
+      </c>
+      <c r="D86" t="s">
+        <v>64</v>
+      </c>
+      <c r="E86" t="s">
+        <v>3</v>
+      </c>
+      <c r="F86" s="1">
+        <v>150.47999999999999</v>
+      </c>
+      <c r="G86" t="s">
+        <v>0</v>
+      </c>
+      <c r="H86" t="s">
+        <v>4</v>
+      </c>
+      <c r="I86" s="3">
+        <v>46268</v>
+      </c>
+      <c r="J86" s="4">
+        <v>0.40054398148148151</v>
+      </c>
+      <c r="K86" t="s">
+        <v>90</v>
+      </c>
+      <c r="L86" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>1001375362</v>
+      </c>
+      <c r="B87">
+        <v>1</v>
+      </c>
+      <c r="C87" t="s">
+        <v>143</v>
+      </c>
+      <c r="D87" t="s">
+        <v>93</v>
+      </c>
+      <c r="E87" t="s">
+        <v>3</v>
+      </c>
+      <c r="F87" s="1">
+        <v>247.88</v>
+      </c>
+      <c r="G87" t="s">
+        <v>0</v>
+      </c>
+      <c r="H87" t="s">
+        <v>7</v>
+      </c>
+      <c r="I87" s="3">
+        <v>46252</v>
+      </c>
+      <c r="J87" s="4">
+        <v>0.45155092592592588</v>
+      </c>
+      <c r="K87" t="s">
+        <v>82</v>
+      </c>
+      <c r="L87" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>1001373989</v>
+      </c>
+      <c r="B88">
+        <v>1</v>
+      </c>
+      <c r="C88" t="s">
+        <v>144</v>
+      </c>
+      <c r="D88" t="s">
+        <v>128</v>
+      </c>
+      <c r="E88" t="s">
+        <v>3</v>
+      </c>
+      <c r="F88" s="1">
+        <v>121.84</v>
+      </c>
+      <c r="G88" t="s">
+        <v>0</v>
+      </c>
+      <c r="H88" t="s">
+        <v>7</v>
+      </c>
+      <c r="I88" s="3">
+        <v>46244</v>
+      </c>
+      <c r="J88" s="4">
+        <v>0.40568287037037037</v>
+      </c>
+      <c r="K88" t="s">
+        <v>82</v>
+      </c>
+      <c r="L88" t="s">
+        <v>83</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M80" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M83">
-      <sortCondition descending="1" ref="A1:A80"/>
+  <autoFilter ref="A1:M88" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M88">
+      <sortCondition descending="1" ref="A1:A83"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="0" type="noConversion"/>

--- a/data/bestellingen 7193 2026_latest.xlsx
+++ b/data/bestellingen 7193 2026_latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\R\Bestellingen\shiny\7180\7180\jorgpeter-orders7180\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC5D047-4CA2-402E-85C9-C000E68B0A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E7294E-A161-4BAF-9D49-A940F7940D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$92</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="160">
   <si>
     <t>EUR</t>
   </si>
@@ -493,6 +493,21 @@
   </si>
   <si>
     <t>eppendorf combitips advanced b (EA)</t>
+  </si>
+  <si>
+    <t>C117993 12.10.2026 7193 Magazijn</t>
+  </si>
+  <si>
+    <t>C117993 06.10.2026 7193 Nam/Stefan</t>
+  </si>
+  <si>
+    <t>AE.9855-L0.55x c-Mount adapter for Leica</t>
+  </si>
+  <si>
+    <t>Ultra HD/4K high def camera with 1/18 in</t>
+  </si>
+  <si>
+    <t>Microscope</t>
   </si>
 </sst>
 </file>
@@ -930,7 +945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M92"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -990,13 +1005,13 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>1001382123</v>
+        <v>1001383950</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D2" t="s">
         <v>148</v>
@@ -1005,7 +1020,7 @@
         <v>3</v>
       </c>
       <c r="F2" s="1">
-        <v>227.67</v>
+        <v>117.5</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
@@ -1014,36 +1029,36 @@
         <v>7</v>
       </c>
       <c r="I2" s="3">
-        <v>46295</v>
+        <v>46307</v>
       </c>
       <c r="J2" s="4">
-        <v>0.40187499999999998</v>
-      </c>
-      <c r="K2" s="10" t="s">
+        <v>0.37842592592592594</v>
+      </c>
+      <c r="K2" t="s">
         <v>82</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>1001381738</v>
+        <v>1001383950</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D3" t="s">
-        <v>150</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="1">
-        <v>242</v>
+        <v>123.94</v>
       </c>
       <c r="G3" t="s">
         <v>0</v>
@@ -1052,36 +1067,36 @@
         <v>7</v>
       </c>
       <c r="I3" s="3">
-        <v>46293</v>
+        <v>46307</v>
       </c>
       <c r="J3" s="4">
-        <v>0.54571759259259256</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="L3" s="10" t="s">
-        <v>79</v>
+        <v>0.37842592592592594</v>
+      </c>
+      <c r="K3" t="s">
+        <v>82</v>
+      </c>
+      <c r="L3" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>1001381738</v>
+        <v>1001383037</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="D4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E4" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="1">
-        <v>25</v>
+        <v>261</v>
       </c>
       <c r="G4" t="s">
         <v>0</v>
@@ -1090,36 +1105,36 @@
         <v>7</v>
       </c>
       <c r="I4" s="3">
-        <v>46293</v>
+        <v>46301</v>
       </c>
       <c r="J4" s="4">
-        <v>0.54656249999999995</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>79</v>
+        <v>0.39663194444444444</v>
+      </c>
+      <c r="K4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L4" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>1001381738</v>
+        <v>1001383037</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="D5" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E5" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="1">
-        <v>2250</v>
+        <v>1143</v>
       </c>
       <c r="G5" t="s">
         <v>0</v>
@@ -1128,54 +1143,54 @@
         <v>7</v>
       </c>
       <c r="I5" s="3">
-        <v>46293</v>
+        <v>46301</v>
       </c>
       <c r="J5" s="4">
-        <v>0.5473958333333333</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>79</v>
+        <v>0.39804398148148151</v>
+      </c>
+      <c r="K5" t="s">
+        <v>106</v>
+      </c>
+      <c r="L5" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>1001380074</v>
+        <v>1001382123</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E6" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="1">
-        <v>159.24</v>
+        <v>227.67</v>
       </c>
       <c r="G6" t="s">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I6" s="3">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="J6" s="4">
-        <v>0.53032407407407411</v>
+        <v>0.40187499999999998</v>
       </c>
       <c r="K6" s="10" t="s">
         <v>82</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -4106,22 +4121,22 @@
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84">
-        <v>1001378453</v>
+        <v>1001381738</v>
       </c>
       <c r="B84">
         <v>1</v>
       </c>
       <c r="C84" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D84" t="s">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="E84" t="s">
         <v>3</v>
       </c>
       <c r="F84" s="1">
-        <v>123.94</v>
+        <v>242</v>
       </c>
       <c r="G84" t="s">
         <v>0</v>
@@ -4130,36 +4145,36 @@
         <v>7</v>
       </c>
       <c r="I84" s="3">
-        <v>46272</v>
+        <v>46293</v>
       </c>
       <c r="J84" s="4">
-        <v>0.39587962962962964</v>
-      </c>
-      <c r="K84" t="s">
-        <v>82</v>
-      </c>
-      <c r="L84" t="s">
-        <v>83</v>
+        <v>0.54571759259259256</v>
+      </c>
+      <c r="K84" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L84" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85">
-        <v>1001378453</v>
+        <v>1001381738</v>
       </c>
       <c r="B85">
         <v>2</v>
       </c>
       <c r="C85" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D85" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="E85" t="s">
         <v>3</v>
       </c>
       <c r="F85" s="1">
-        <v>243.68</v>
+        <v>25</v>
       </c>
       <c r="G85" t="s">
         <v>0</v>
@@ -4168,112 +4183,112 @@
         <v>7</v>
       </c>
       <c r="I85" s="3">
-        <v>46272</v>
+        <v>46293</v>
       </c>
       <c r="J85" s="4">
-        <v>0.39587962962962964</v>
-      </c>
-      <c r="K85" t="s">
-        <v>82</v>
-      </c>
-      <c r="L85" t="s">
-        <v>83</v>
+        <v>0.54656249999999995</v>
+      </c>
+      <c r="K85" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L85" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86">
-        <v>1001378010</v>
+        <v>1001381738</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D86" t="s">
-        <v>64</v>
+        <v>152</v>
       </c>
       <c r="E86" t="s">
         <v>3</v>
       </c>
       <c r="F86" s="1">
-        <v>150.47999999999999</v>
+        <v>2250</v>
       </c>
       <c r="G86" t="s">
         <v>0</v>
       </c>
       <c r="H86" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I86" s="3">
-        <v>46268</v>
+        <v>46293</v>
       </c>
       <c r="J86" s="4">
-        <v>0.40054398148148151</v>
-      </c>
-      <c r="K86" t="s">
-        <v>90</v>
-      </c>
-      <c r="L86" t="s">
-        <v>81</v>
+        <v>0.5473958333333333</v>
+      </c>
+      <c r="K86" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="L86" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87">
-        <v>1001375362</v>
+        <v>1001380074</v>
       </c>
       <c r="B87">
         <v>1</v>
       </c>
       <c r="C87" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D87" t="s">
-        <v>93</v>
+        <v>154</v>
       </c>
       <c r="E87" t="s">
         <v>3</v>
       </c>
       <c r="F87" s="1">
-        <v>247.88</v>
+        <v>159.24</v>
       </c>
       <c r="G87" t="s">
         <v>0</v>
       </c>
       <c r="H87" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I87" s="3">
-        <v>46252</v>
+        <v>46281</v>
       </c>
       <c r="J87" s="4">
-        <v>0.45155092592592588</v>
-      </c>
-      <c r="K87" t="s">
+        <v>0.53032407407407411</v>
+      </c>
+      <c r="K87" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="L87" t="s">
-        <v>83</v>
+      <c r="L87" s="10" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88">
-        <v>1001373989</v>
+        <v>1001378453</v>
       </c>
       <c r="B88">
         <v>1</v>
       </c>
       <c r="C88" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D88" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="E88" t="s">
         <v>3</v>
       </c>
       <c r="F88" s="1">
-        <v>121.84</v>
+        <v>123.94</v>
       </c>
       <c r="G88" t="s">
         <v>0</v>
@@ -4282,10 +4297,10 @@
         <v>7</v>
       </c>
       <c r="I88" s="3">
-        <v>46244</v>
+        <v>46272</v>
       </c>
       <c r="J88" s="4">
-        <v>0.40568287037037037</v>
+        <v>0.39587962962962964</v>
       </c>
       <c r="K88" t="s">
         <v>82</v>
@@ -4294,10 +4309,162 @@
         <v>83</v>
       </c>
     </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>1001378453</v>
+      </c>
+      <c r="B89">
+        <v>2</v>
+      </c>
+      <c r="C89" t="s">
+        <v>145</v>
+      </c>
+      <c r="D89" t="s">
+        <v>128</v>
+      </c>
+      <c r="E89" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="1">
+        <v>243.68</v>
+      </c>
+      <c r="G89" t="s">
+        <v>0</v>
+      </c>
+      <c r="H89" t="s">
+        <v>7</v>
+      </c>
+      <c r="I89" s="3">
+        <v>46272</v>
+      </c>
+      <c r="J89" s="4">
+        <v>0.39587962962962964</v>
+      </c>
+      <c r="K89" t="s">
+        <v>82</v>
+      </c>
+      <c r="L89" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>1001378010</v>
+      </c>
+      <c r="B90">
+        <v>1</v>
+      </c>
+      <c r="C90" t="s">
+        <v>146</v>
+      </c>
+      <c r="D90" t="s">
+        <v>64</v>
+      </c>
+      <c r="E90" t="s">
+        <v>3</v>
+      </c>
+      <c r="F90" s="1">
+        <v>150.47999999999999</v>
+      </c>
+      <c r="G90" t="s">
+        <v>0</v>
+      </c>
+      <c r="H90" t="s">
+        <v>4</v>
+      </c>
+      <c r="I90" s="3">
+        <v>46268</v>
+      </c>
+      <c r="J90" s="4">
+        <v>0.40054398148148151</v>
+      </c>
+      <c r="K90" t="s">
+        <v>90</v>
+      </c>
+      <c r="L90" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>1001375362</v>
+      </c>
+      <c r="B91">
+        <v>1</v>
+      </c>
+      <c r="C91" t="s">
+        <v>143</v>
+      </c>
+      <c r="D91" t="s">
+        <v>93</v>
+      </c>
+      <c r="E91" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="1">
+        <v>247.88</v>
+      </c>
+      <c r="G91" t="s">
+        <v>0</v>
+      </c>
+      <c r="H91" t="s">
+        <v>7</v>
+      </c>
+      <c r="I91" s="3">
+        <v>46252</v>
+      </c>
+      <c r="J91" s="4">
+        <v>0.45155092592592588</v>
+      </c>
+      <c r="K91" t="s">
+        <v>82</v>
+      </c>
+      <c r="L91" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>1001373989</v>
+      </c>
+      <c r="B92">
+        <v>1</v>
+      </c>
+      <c r="C92" t="s">
+        <v>144</v>
+      </c>
+      <c r="D92" t="s">
+        <v>128</v>
+      </c>
+      <c r="E92" t="s">
+        <v>3</v>
+      </c>
+      <c r="F92" s="1">
+        <v>121.84</v>
+      </c>
+      <c r="G92" t="s">
+        <v>0</v>
+      </c>
+      <c r="H92" t="s">
+        <v>7</v>
+      </c>
+      <c r="I92" s="3">
+        <v>46244</v>
+      </c>
+      <c r="J92" s="4">
+        <v>0.40568287037037037</v>
+      </c>
+      <c r="K92" t="s">
+        <v>82</v>
+      </c>
+      <c r="L92" t="s">
+        <v>83</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M88" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M88">
-      <sortCondition descending="1" ref="A1:A83"/>
+  <autoFilter ref="A1:M92" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M92">
+      <sortCondition descending="1" ref="A1:A88"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="0" type="noConversion"/>
